--- a/STOK RANK/Rank Dealer/RANK LSP.xlsx
+++ b/STOK RANK/Rank Dealer/RANK LSP.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807F9304-C789-40AB-99D1-271F12B6FA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5958A4F1-F54C-44C1-92A9-1A7F5E1CAE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
   <sheets>
     <sheet name="rankparts" sheetId="1" r:id="rId1"/>
+    <sheet name="avg6bulan" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="585">
   <si>
     <t>Sum of Qty</t>
   </si>
@@ -1458,6 +1459,339 @@
   </si>
   <si>
     <t>86645K2FNA0ZA</t>
+  </si>
+  <si>
+    <t>Sum 6 Bulan</t>
+  </si>
+  <si>
+    <t>AVG 6 Bulan</t>
+  </si>
+  <si>
+    <t>082342MBK0LZ9</t>
+  </si>
+  <si>
+    <t>08294M99K8LN9</t>
+  </si>
+  <si>
+    <t>082322MBK5LN9</t>
+  </si>
+  <si>
+    <t>81110H02BLA</t>
+  </si>
+  <si>
+    <t>082342MBK0LZ0</t>
+  </si>
+  <si>
+    <t>082322MBK6LN9</t>
+  </si>
+  <si>
+    <t>082322MAK0LN9</t>
+  </si>
+  <si>
+    <t>08234M99K8LN9</t>
+  </si>
+  <si>
+    <t>ACG10GR</t>
+  </si>
+  <si>
+    <t>082322MAK8LN9</t>
+  </si>
+  <si>
+    <t>HBF50ML</t>
+  </si>
+  <si>
+    <t>64300K1AL00</t>
+  </si>
+  <si>
+    <t>082322MAK1LN9</t>
+  </si>
+  <si>
+    <t>64300K2FP00</t>
+  </si>
+  <si>
+    <t>64300K2SA00</t>
+  </si>
+  <si>
+    <t>HPC480ML</t>
+  </si>
+  <si>
+    <t>64300K2VG00</t>
+  </si>
+  <si>
+    <t>TBC500ML</t>
+  </si>
+  <si>
+    <t>772A0K1AA00</t>
+  </si>
+  <si>
+    <t>64300K3VA00</t>
+  </si>
+  <si>
+    <t>ACL70ML</t>
+  </si>
+  <si>
+    <t>OSC70ML</t>
+  </si>
+  <si>
+    <t>61304K2FP00SLV</t>
+  </si>
+  <si>
+    <t>08F88K2FP00SLV</t>
+  </si>
+  <si>
+    <t>08F88K0JA00</t>
+  </si>
+  <si>
+    <t>87100LXBLUL</t>
+  </si>
+  <si>
+    <t>64300K1ZV00</t>
+  </si>
+  <si>
+    <t>08234M99K8LZ0</t>
+  </si>
+  <si>
+    <t>87100PRLWHTL</t>
+  </si>
+  <si>
+    <t>772A0K2VG00</t>
+  </si>
+  <si>
+    <t>17200K2FA00</t>
+  </si>
+  <si>
+    <t>17200K1AL00</t>
+  </si>
+  <si>
+    <t>08P71MCMRED</t>
+  </si>
+  <si>
+    <t>87100LXBLKL</t>
+  </si>
+  <si>
+    <t>87100HFFABXL</t>
+  </si>
+  <si>
+    <t>AHGK0010007</t>
+  </si>
+  <si>
+    <t>64301K2FP00SLV</t>
+  </si>
+  <si>
+    <t>3310AK3VA00</t>
+  </si>
+  <si>
+    <t>03512K1ZGRE</t>
+  </si>
+  <si>
+    <t>03512K1ZGBL</t>
+  </si>
+  <si>
+    <t>03512K1ZGCP</t>
+  </si>
+  <si>
+    <t>AHGK0010015</t>
+  </si>
+  <si>
+    <t>87100LXWHTXL</t>
+  </si>
+  <si>
+    <t>87100LXBLUM</t>
+  </si>
+  <si>
+    <t>772A0K2SA00</t>
+  </si>
+  <si>
+    <t>08F47K2FP00SLV</t>
+  </si>
+  <si>
+    <t>08F44K2FP00SLV</t>
+  </si>
+  <si>
+    <t>03512SKRCBL</t>
+  </si>
+  <si>
+    <t>08F88K1AL00</t>
+  </si>
+  <si>
+    <t>03512SKRCRE</t>
+  </si>
+  <si>
+    <t>87100LXBLUXL</t>
+  </si>
+  <si>
+    <t>AHPS0205012</t>
+  </si>
+  <si>
+    <t>AHPS0305012</t>
+  </si>
+  <si>
+    <t>AHTS0301051</t>
+  </si>
+  <si>
+    <t>AHPS0005012</t>
+  </si>
+  <si>
+    <t>08R80K2FP00</t>
+  </si>
+  <si>
+    <t>03512SKRCCP</t>
+  </si>
+  <si>
+    <t>08F88K2SA00</t>
+  </si>
+  <si>
+    <t>AHPS0105012</t>
+  </si>
+  <si>
+    <t>AHPS0304012</t>
+  </si>
+  <si>
+    <t>87100HFCLSLVM</t>
+  </si>
+  <si>
+    <t>87100LXWHTM</t>
+  </si>
+  <si>
+    <t>MCSMPK1ALSP</t>
+  </si>
+  <si>
+    <t>87100FSPBLXL</t>
+  </si>
+  <si>
+    <t>AHPS0306012</t>
+  </si>
+  <si>
+    <t>87100LXBLKXL</t>
+  </si>
+  <si>
+    <t>AHTS0201050</t>
+  </si>
+  <si>
+    <t>AHJK0101026</t>
+  </si>
+  <si>
+    <t>HIC60ML</t>
+  </si>
+  <si>
+    <t>MCSMPK1ALST</t>
+  </si>
+  <si>
+    <t>83750K2FP00SLV</t>
+  </si>
+  <si>
+    <t>61304K1AL00</t>
+  </si>
+  <si>
+    <t>53103K2FP00ORG</t>
+  </si>
+  <si>
+    <t>53103K2FP00SLV</t>
+  </si>
+  <si>
+    <t>3310AK2SA00</t>
+  </si>
+  <si>
+    <t>3310AK2VG00</t>
+  </si>
+  <si>
+    <t>08R80K2VG00</t>
+  </si>
+  <si>
+    <t>08F47K2FA00</t>
+  </si>
+  <si>
+    <t>08F22K3VA00</t>
+  </si>
+  <si>
+    <t>03512SKRCWH</t>
+  </si>
+  <si>
+    <t>AHJK0301033</t>
+  </si>
+  <si>
+    <t>AHTS0301050</t>
+  </si>
+  <si>
+    <t>AHTS0301053</t>
+  </si>
+  <si>
+    <t>87100PRLWHTXL</t>
+  </si>
+  <si>
+    <t>64300K0JA0BLK</t>
+  </si>
+  <si>
+    <t>64300K2FA00</t>
+  </si>
+  <si>
+    <t>61304K2FA00</t>
+  </si>
+  <si>
+    <t>08F44K2FP00LGR</t>
+  </si>
+  <si>
+    <t>08F88K3VA00</t>
+  </si>
+  <si>
+    <t>17200K1ZG00</t>
+  </si>
+  <si>
+    <t>AHTS0301048</t>
+  </si>
+  <si>
+    <t>AHK00201014</t>
+  </si>
+  <si>
+    <t>08F88K2FA00</t>
+  </si>
+  <si>
+    <t>87100HFBTRGRM</t>
+  </si>
+  <si>
+    <t>64301K2FP00LGR</t>
+  </si>
+  <si>
+    <t>AHTS0401048</t>
+  </si>
+  <si>
+    <t>AHTS0301052</t>
+  </si>
+  <si>
+    <t>87100CSMGREXL</t>
+  </si>
+  <si>
+    <t>08F47K2FP00LGR</t>
+  </si>
+  <si>
+    <t>43000K1AA00</t>
+  </si>
+  <si>
+    <t>61304K2FP00LGR</t>
+  </si>
+  <si>
+    <t>83750K2FP00LGR</t>
+  </si>
+  <si>
+    <t>64300K1ZG00</t>
+  </si>
+  <si>
+    <t>87100FSBLKXL</t>
+  </si>
+  <si>
+    <t>87100FSOWHL</t>
+  </si>
+  <si>
+    <t>87100FSOWHXL</t>
+  </si>
+  <si>
+    <t>MCSMPK3VA00</t>
+  </si>
+  <si>
+    <t>08F88K1ZG00</t>
+  </si>
+  <si>
+    <t>3311AK3VA00</t>
   </si>
 </sst>
 </file>
@@ -1550,6 +1884,18 @@
     <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="0" dataCellStyle="Comma"/>
     <tableColumn id="5" xr3:uid="{47EFE725-CDB5-45AD-BDA0-B6DCB63EE85D}" name="Cont % Akumulasi" dataCellStyle="Percent"/>
     <tableColumn id="6" xr3:uid="{37C8619E-0B0F-4647-86AB-979865F93ADA}" name="Rank"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E0B0D92-E7B1-4CCD-A8EF-202675C87341}" name="AVG6bulan" displayName="AVG6bulan" ref="A1:C587" totalsRowShown="0">
+  <autoFilter ref="A1:C587" xr:uid="{6E0B0D92-E7B1-4CCD-A8EF-202675C87341}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{DFADE281-9CFB-4143-A7AE-21AA7EF6CD6C}" name="kode part"/>
+    <tableColumn id="2" xr3:uid="{22EEB880-7A5B-4ADE-BA60-1CD27BE418FB}" name="Sum 6 Bulan"/>
+    <tableColumn id="3" xr3:uid="{B66B00FF-88CF-4D37-AA12-362EE52D1DB1}" name="AVG 6 Bulan"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11448,4 +11794,6474 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2FE4624-3088-4805-9B6C-76AA7D6B409E}">
+  <dimension ref="A1:C587"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B2">
+        <v>2639</v>
+      </c>
+      <c r="C2">
+        <v>439.83333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B3">
+        <v>1341</v>
+      </c>
+      <c r="C3">
+        <v>223.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B4">
+        <v>679</v>
+      </c>
+      <c r="C4">
+        <v>113.16666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B5">
+        <v>661</v>
+      </c>
+      <c r="C5">
+        <v>110.16666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>9410912000</v>
+      </c>
+      <c r="B6">
+        <v>605</v>
+      </c>
+      <c r="C6">
+        <v>100.83333333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>478</v>
+      </c>
+      <c r="B7">
+        <v>540</v>
+      </c>
+      <c r="C7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8">
+        <v>323</v>
+      </c>
+      <c r="C8">
+        <v>53.833333333333336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9">
+        <v>249</v>
+      </c>
+      <c r="C9">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>195</v>
+      </c>
+      <c r="C10">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11">
+        <v>173</v>
+      </c>
+      <c r="C11">
+        <v>28.833333333333332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>168</v>
+      </c>
+      <c r="C12">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>156</v>
+      </c>
+      <c r="C13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>481</v>
+      </c>
+      <c r="B14">
+        <v>136</v>
+      </c>
+      <c r="C14">
+        <v>22.666666666666668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>102</v>
+      </c>
+      <c r="C15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>487</v>
+      </c>
+      <c r="B16">
+        <v>101</v>
+      </c>
+      <c r="C16">
+        <v>16.833333333333332</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17">
+        <v>96</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>484</v>
+      </c>
+      <c r="B18">
+        <v>91</v>
+      </c>
+      <c r="C18">
+        <v>15.166666666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B19">
+        <v>82</v>
+      </c>
+      <c r="C19">
+        <v>13.666666666666666</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20">
+        <v>81</v>
+      </c>
+      <c r="C20">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>81</v>
+      </c>
+      <c r="C21">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>73</v>
+      </c>
+      <c r="C22">
+        <v>12.166666666666666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>482</v>
+      </c>
+      <c r="B23">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24">
+        <v>71</v>
+      </c>
+      <c r="C24">
+        <v>11.833333333333334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25">
+        <v>69</v>
+      </c>
+      <c r="C25">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26">
+        <v>68</v>
+      </c>
+      <c r="C26">
+        <v>11.333333333333334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27">
+        <v>67</v>
+      </c>
+      <c r="C27">
+        <v>11.166666666666666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>486</v>
+      </c>
+      <c r="B28">
+        <v>65</v>
+      </c>
+      <c r="C28">
+        <v>10.833333333333334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29">
+        <v>62</v>
+      </c>
+      <c r="C29">
+        <v>10.333333333333334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>489</v>
+      </c>
+      <c r="B30">
+        <v>61</v>
+      </c>
+      <c r="C30">
+        <v>10.166666666666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>57</v>
+      </c>
+      <c r="C31">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32">
+        <v>54</v>
+      </c>
+      <c r="C32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>483</v>
+      </c>
+      <c r="B33">
+        <v>54</v>
+      </c>
+      <c r="C33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>488</v>
+      </c>
+      <c r="B34">
+        <v>54</v>
+      </c>
+      <c r="C34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35">
+        <v>51</v>
+      </c>
+      <c r="C35">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36">
+        <v>49</v>
+      </c>
+      <c r="C36">
+        <v>8.1666666666666661</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37">
+        <v>47</v>
+      </c>
+      <c r="C37">
+        <v>7.833333333333333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38">
+        <v>45</v>
+      </c>
+      <c r="C38">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39">
+        <v>44</v>
+      </c>
+      <c r="C39">
+        <v>7.333333333333333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>485</v>
+      </c>
+      <c r="B40">
+        <v>43</v>
+      </c>
+      <c r="C40">
+        <v>7.166666666666667</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42">
+        <v>37</v>
+      </c>
+      <c r="C42">
+        <v>6.166666666666667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43">
+        <v>36</v>
+      </c>
+      <c r="C43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44">
+        <v>36</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45">
+        <v>35</v>
+      </c>
+      <c r="C45">
+        <v>5.833333333333333</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46">
+        <v>35</v>
+      </c>
+      <c r="C46">
+        <v>5.833333333333333</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47">
+        <v>34</v>
+      </c>
+      <c r="C47">
+        <v>5.666666666666667</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48">
+        <v>32</v>
+      </c>
+      <c r="C48">
+        <v>5.333333333333333</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>5.333333333333333</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50">
+        <v>30</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51">
+        <v>30</v>
+      </c>
+      <c r="C51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52">
+        <v>29</v>
+      </c>
+      <c r="C52">
+        <v>4.833333333333333</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53">
+        <v>29</v>
+      </c>
+      <c r="C53">
+        <v>4.833333333333333</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54">
+        <v>27</v>
+      </c>
+      <c r="C54">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>494</v>
+      </c>
+      <c r="B55">
+        <v>27</v>
+      </c>
+      <c r="C55">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
+        <v>27</v>
+      </c>
+      <c r="C56">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57">
+        <v>26</v>
+      </c>
+      <c r="C57">
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58">
+        <v>25</v>
+      </c>
+      <c r="C58">
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59">
+        <v>24</v>
+      </c>
+      <c r="C59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60">
+        <v>24</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61">
+        <v>23</v>
+      </c>
+      <c r="C61">
+        <v>3.8333333333333335</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62">
+        <v>23</v>
+      </c>
+      <c r="C62">
+        <v>3.8333333333333335</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63">
+        <v>23</v>
+      </c>
+      <c r="C63">
+        <v>3.8333333333333335</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>490</v>
+      </c>
+      <c r="B64">
+        <v>22</v>
+      </c>
+      <c r="C64">
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65">
+        <v>22</v>
+      </c>
+      <c r="C65">
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66">
+        <v>21</v>
+      </c>
+      <c r="C66">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67">
+        <v>21</v>
+      </c>
+      <c r="C67">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68">
+        <v>21</v>
+      </c>
+      <c r="C68">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69">
+        <v>20</v>
+      </c>
+      <c r="C69">
+        <v>3.3333333333333335</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <v>18</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>520</v>
+      </c>
+      <c r="B71">
+        <v>18</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72">
+        <v>17</v>
+      </c>
+      <c r="C72">
+        <v>2.8333333333333335</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73">
+        <v>16</v>
+      </c>
+      <c r="C73">
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74">
+        <v>16</v>
+      </c>
+      <c r="C74">
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>529</v>
+      </c>
+      <c r="B75">
+        <v>15</v>
+      </c>
+      <c r="C75">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>57</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77">
+        <v>14</v>
+      </c>
+      <c r="C77">
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>499</v>
+      </c>
+      <c r="B78">
+        <v>14</v>
+      </c>
+      <c r="C78">
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>151</v>
+      </c>
+      <c r="B79">
+        <v>13</v>
+      </c>
+      <c r="C79">
+        <v>2.1666666666666665</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80">
+        <v>13</v>
+      </c>
+      <c r="C80">
+        <v>2.1666666666666665</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>566</v>
+      </c>
+      <c r="B81">
+        <v>12</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>561</v>
+      </c>
+      <c r="B82">
+        <v>12</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83">
+        <v>12</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>524</v>
+      </c>
+      <c r="B84">
+        <v>12</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>152</v>
+      </c>
+      <c r="B85">
+        <v>12</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>542</v>
+      </c>
+      <c r="B87">
+        <v>10</v>
+      </c>
+      <c r="C87">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>492</v>
+      </c>
+      <c r="B88">
+        <v>10</v>
+      </c>
+      <c r="C88">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>155</v>
+      </c>
+      <c r="B89">
+        <v>10</v>
+      </c>
+      <c r="C89">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90">
+        <v>10</v>
+      </c>
+      <c r="C90">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91">
+        <v>10</v>
+      </c>
+      <c r="C91">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92">
+        <v>10</v>
+      </c>
+      <c r="C92">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>71</v>
+      </c>
+      <c r="B93">
+        <v>10</v>
+      </c>
+      <c r="C93">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>158</v>
+      </c>
+      <c r="B94">
+        <v>10</v>
+      </c>
+      <c r="C94">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>149</v>
+      </c>
+      <c r="B95">
+        <v>9</v>
+      </c>
+      <c r="C95">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97">
+        <v>9</v>
+      </c>
+      <c r="C97">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>507</v>
+      </c>
+      <c r="B98">
+        <v>9</v>
+      </c>
+      <c r="C98">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>154</v>
+      </c>
+      <c r="B99">
+        <v>9</v>
+      </c>
+      <c r="C99">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>163</v>
+      </c>
+      <c r="B100">
+        <v>9</v>
+      </c>
+      <c r="C100">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>80</v>
+      </c>
+      <c r="B101">
+        <v>9</v>
+      </c>
+      <c r="C101">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>36</v>
+      </c>
+      <c r="B102">
+        <v>9</v>
+      </c>
+      <c r="C102">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>74</v>
+      </c>
+      <c r="B103">
+        <v>9</v>
+      </c>
+      <c r="C103">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>567</v>
+      </c>
+      <c r="B104">
+        <v>8</v>
+      </c>
+      <c r="C104">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>102</v>
+      </c>
+      <c r="B105">
+        <v>8</v>
+      </c>
+      <c r="C105">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>545</v>
+      </c>
+      <c r="B106">
+        <v>8</v>
+      </c>
+      <c r="C106">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>150</v>
+      </c>
+      <c r="B107">
+        <v>8</v>
+      </c>
+      <c r="C107">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>59</v>
+      </c>
+      <c r="B108">
+        <v>8</v>
+      </c>
+      <c r="C108">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>157</v>
+      </c>
+      <c r="B109">
+        <v>8</v>
+      </c>
+      <c r="C109">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110">
+        <v>8</v>
+      </c>
+      <c r="C110">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>159</v>
+      </c>
+      <c r="B111">
+        <v>7</v>
+      </c>
+      <c r="C111">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>509</v>
+      </c>
+      <c r="B112">
+        <v>7</v>
+      </c>
+      <c r="C112">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>58</v>
+      </c>
+      <c r="B113">
+        <v>7</v>
+      </c>
+      <c r="C113">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>515</v>
+      </c>
+      <c r="B114">
+        <v>7</v>
+      </c>
+      <c r="C114">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>516</v>
+      </c>
+      <c r="B115">
+        <v>7</v>
+      </c>
+      <c r="C115">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>533</v>
+      </c>
+      <c r="B116">
+        <v>7</v>
+      </c>
+      <c r="C116">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>156</v>
+      </c>
+      <c r="B117">
+        <v>7</v>
+      </c>
+      <c r="C117">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>38</v>
+      </c>
+      <c r="B118">
+        <v>7</v>
+      </c>
+      <c r="C118">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>52</v>
+      </c>
+      <c r="B119">
+        <v>7</v>
+      </c>
+      <c r="C119">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120">
+        <v>7</v>
+      </c>
+      <c r="C120">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>512</v>
+      </c>
+      <c r="B121">
+        <v>6</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>547</v>
+      </c>
+      <c r="B122">
+        <v>6</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>540</v>
+      </c>
+      <c r="B123">
+        <v>6</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>166</v>
+      </c>
+      <c r="B124">
+        <v>6</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125">
+        <v>6</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>97</v>
+      </c>
+      <c r="B126">
+        <v>6</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>76</v>
+      </c>
+      <c r="B127">
+        <v>6</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>528</v>
+      </c>
+      <c r="B128">
+        <v>6</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>164</v>
+      </c>
+      <c r="B129">
+        <v>6</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>37</v>
+      </c>
+      <c r="B130">
+        <v>6</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>51</v>
+      </c>
+      <c r="B131">
+        <v>6</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>238</v>
+      </c>
+      <c r="B132">
+        <v>5</v>
+      </c>
+      <c r="C132">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>72</v>
+      </c>
+      <c r="B133">
+        <v>5</v>
+      </c>
+      <c r="C133">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>55</v>
+      </c>
+      <c r="B134">
+        <v>5</v>
+      </c>
+      <c r="C134">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>226</v>
+      </c>
+      <c r="B135">
+        <v>5</v>
+      </c>
+      <c r="C135">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>538</v>
+      </c>
+      <c r="B136">
+        <v>5</v>
+      </c>
+      <c r="C136">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>511</v>
+      </c>
+      <c r="B137">
+        <v>5</v>
+      </c>
+      <c r="C137">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>534</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+      <c r="C138">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>175</v>
+      </c>
+      <c r="B139">
+        <v>5</v>
+      </c>
+      <c r="C139">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>84</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+      <c r="C140">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>9820041000</v>
+      </c>
+      <c r="B141">
+        <v>5</v>
+      </c>
+      <c r="C141">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>26</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+      <c r="C142">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>168</v>
+      </c>
+      <c r="B143">
+        <v>5</v>
+      </c>
+      <c r="C143">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>568</v>
+      </c>
+      <c r="B144">
+        <v>5</v>
+      </c>
+      <c r="C144">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>20</v>
+      </c>
+      <c r="B145">
+        <v>5</v>
+      </c>
+      <c r="C145">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>161</v>
+      </c>
+      <c r="B146">
+        <v>5</v>
+      </c>
+      <c r="C146">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>123</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+      <c r="C147">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>557</v>
+      </c>
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="C148">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>70</v>
+      </c>
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>541</v>
+      </c>
+      <c r="B150">
+        <v>4</v>
+      </c>
+      <c r="C150">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>526</v>
+      </c>
+      <c r="B151">
+        <v>4</v>
+      </c>
+      <c r="C151">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>173</v>
+      </c>
+      <c r="B152">
+        <v>4</v>
+      </c>
+      <c r="C152">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>194</v>
+      </c>
+      <c r="B153">
+        <v>4</v>
+      </c>
+      <c r="C153">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>94</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>502</v>
+      </c>
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="C155">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>124</v>
+      </c>
+      <c r="B156">
+        <v>4</v>
+      </c>
+      <c r="C156">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>518</v>
+      </c>
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="C157">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>174</v>
+      </c>
+      <c r="B158">
+        <v>4</v>
+      </c>
+      <c r="C158">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>92</v>
+      </c>
+      <c r="B159">
+        <v>4</v>
+      </c>
+      <c r="C159">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>560</v>
+      </c>
+      <c r="B160">
+        <v>4</v>
+      </c>
+      <c r="C160">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>429</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>85</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>41</v>
+      </c>
+      <c r="B163">
+        <v>4</v>
+      </c>
+      <c r="C163">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164">
+        <v>4</v>
+      </c>
+      <c r="C164">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>176</v>
+      </c>
+      <c r="B166">
+        <v>4</v>
+      </c>
+      <c r="C166">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>177</v>
+      </c>
+      <c r="B167">
+        <v>4</v>
+      </c>
+      <c r="C167">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>196</v>
+      </c>
+      <c r="B168">
+        <v>4</v>
+      </c>
+      <c r="C168">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>550</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>9390334380</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
+      </c>
+      <c r="C170">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>42</v>
+      </c>
+      <c r="B171">
+        <v>4</v>
+      </c>
+      <c r="C171">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>60</v>
+      </c>
+      <c r="B172">
+        <v>4</v>
+      </c>
+      <c r="C172">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>160</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>130</v>
+      </c>
+      <c r="B174">
+        <v>4</v>
+      </c>
+      <c r="C174">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>169</v>
+      </c>
+      <c r="B175">
+        <v>4</v>
+      </c>
+      <c r="C175">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>521</v>
+      </c>
+      <c r="B176">
+        <v>4</v>
+      </c>
+      <c r="C176">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177">
+        <v>4</v>
+      </c>
+      <c r="C177">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>170</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>14</v>
+      </c>
+      <c r="B179">
+        <v>4</v>
+      </c>
+      <c r="C179">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>522</v>
+      </c>
+      <c r="B180">
+        <v>4</v>
+      </c>
+      <c r="C180">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>9805957927</v>
+      </c>
+      <c r="B181">
+        <v>4</v>
+      </c>
+      <c r="C181">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>9390324480</v>
+      </c>
+      <c r="B182">
+        <v>4</v>
+      </c>
+      <c r="C182">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>332</v>
+      </c>
+      <c r="B183">
+        <v>3</v>
+      </c>
+      <c r="C183">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>104</v>
+      </c>
+      <c r="B184">
+        <v>3</v>
+      </c>
+      <c r="C184">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>98</v>
+      </c>
+      <c r="B185">
+        <v>3</v>
+      </c>
+      <c r="C185">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>68</v>
+      </c>
+      <c r="B186">
+        <v>3</v>
+      </c>
+      <c r="C186">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>501</v>
+      </c>
+      <c r="B187">
+        <v>3</v>
+      </c>
+      <c r="C187">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>3</v>
+      </c>
+      <c r="C188">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>89</v>
+      </c>
+      <c r="B189">
+        <v>3</v>
+      </c>
+      <c r="C189">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>81</v>
+      </c>
+      <c r="B190">
+        <v>3</v>
+      </c>
+      <c r="C190">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>569</v>
+      </c>
+      <c r="B191">
+        <v>3</v>
+      </c>
+      <c r="C191">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>530</v>
+      </c>
+      <c r="B192">
+        <v>3</v>
+      </c>
+      <c r="C192">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>495</v>
+      </c>
+      <c r="B193">
+        <v>3</v>
+      </c>
+      <c r="C193">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>189</v>
+      </c>
+      <c r="B194">
+        <v>3</v>
+      </c>
+      <c r="C194">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195">
+        <v>3</v>
+      </c>
+      <c r="C195">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>187</v>
+      </c>
+      <c r="B196">
+        <v>3</v>
+      </c>
+      <c r="C196">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>167</v>
+      </c>
+      <c r="B197">
+        <v>3</v>
+      </c>
+      <c r="C197">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>188</v>
+      </c>
+      <c r="B198">
+        <v>3</v>
+      </c>
+      <c r="C198">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>215</v>
+      </c>
+      <c r="B199">
+        <v>3</v>
+      </c>
+      <c r="C199">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>505</v>
+      </c>
+      <c r="B200">
+        <v>3</v>
+      </c>
+      <c r="C200">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>172</v>
+      </c>
+      <c r="B201">
+        <v>3</v>
+      </c>
+      <c r="C201">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>105</v>
+      </c>
+      <c r="B202">
+        <v>3</v>
+      </c>
+      <c r="C202">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>109</v>
+      </c>
+      <c r="B203">
+        <v>3</v>
+      </c>
+      <c r="C203">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>103</v>
+      </c>
+      <c r="B204">
+        <v>3</v>
+      </c>
+      <c r="C204">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>178</v>
+      </c>
+      <c r="B205">
+        <v>3</v>
+      </c>
+      <c r="C205">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>100</v>
+      </c>
+      <c r="B206">
+        <v>3</v>
+      </c>
+      <c r="C206">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>180</v>
+      </c>
+      <c r="B207">
+        <v>3</v>
+      </c>
+      <c r="C207">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>83</v>
+      </c>
+      <c r="B208">
+        <v>3</v>
+      </c>
+      <c r="C208">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>210</v>
+      </c>
+      <c r="B209">
+        <v>3</v>
+      </c>
+      <c r="C209">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>9390325310</v>
+      </c>
+      <c r="B210">
+        <v>3</v>
+      </c>
+      <c r="C210">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>181</v>
+      </c>
+      <c r="B211">
+        <v>3</v>
+      </c>
+      <c r="C211">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>128</v>
+      </c>
+      <c r="B212">
+        <v>3</v>
+      </c>
+      <c r="C212">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>53</v>
+      </c>
+      <c r="B213">
+        <v>3</v>
+      </c>
+      <c r="C213">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>372</v>
+      </c>
+      <c r="B214">
+        <v>3</v>
+      </c>
+      <c r="C214">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>190</v>
+      </c>
+      <c r="B215">
+        <v>3</v>
+      </c>
+      <c r="C215">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>113</v>
+      </c>
+      <c r="B216">
+        <v>3</v>
+      </c>
+      <c r="C216">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>564</v>
+      </c>
+      <c r="B217">
+        <v>3</v>
+      </c>
+      <c r="C217">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>127</v>
+      </c>
+      <c r="B218">
+        <v>3</v>
+      </c>
+      <c r="C218">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>220</v>
+      </c>
+      <c r="B219">
+        <v>3</v>
+      </c>
+      <c r="C219">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>193</v>
+      </c>
+      <c r="B220">
+        <v>3</v>
+      </c>
+      <c r="C220">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>430</v>
+      </c>
+      <c r="B221">
+        <v>3</v>
+      </c>
+      <c r="C221">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>199</v>
+      </c>
+      <c r="B222">
+        <v>3</v>
+      </c>
+      <c r="C222">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>185</v>
+      </c>
+      <c r="B223">
+        <v>3</v>
+      </c>
+      <c r="C223">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>54</v>
+      </c>
+      <c r="B224">
+        <v>3</v>
+      </c>
+      <c r="C224">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>525</v>
+      </c>
+      <c r="B225">
+        <v>3</v>
+      </c>
+      <c r="C225">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>197</v>
+      </c>
+      <c r="B226">
+        <v>3</v>
+      </c>
+      <c r="C226">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>207</v>
+      </c>
+      <c r="B227">
+        <v>2</v>
+      </c>
+      <c r="C227">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>77</v>
+      </c>
+      <c r="B228">
+        <v>2</v>
+      </c>
+      <c r="C228">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>230</v>
+      </c>
+      <c r="B229">
+        <v>2</v>
+      </c>
+      <c r="C229">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>108</v>
+      </c>
+      <c r="B230">
+        <v>2</v>
+      </c>
+      <c r="C230">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>62</v>
+      </c>
+      <c r="B231">
+        <v>2</v>
+      </c>
+      <c r="C231">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>348</v>
+      </c>
+      <c r="B232">
+        <v>2</v>
+      </c>
+      <c r="C232">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>240</v>
+      </c>
+      <c r="B233">
+        <v>2</v>
+      </c>
+      <c r="C233">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>570</v>
+      </c>
+      <c r="B234">
+        <v>2</v>
+      </c>
+      <c r="C234">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>232</v>
+      </c>
+      <c r="B235">
+        <v>2</v>
+      </c>
+      <c r="C235">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>353</v>
+      </c>
+      <c r="B236">
+        <v>2</v>
+      </c>
+      <c r="C236">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>120</v>
+      </c>
+      <c r="B237">
+        <v>2</v>
+      </c>
+      <c r="C237">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>335</v>
+      </c>
+      <c r="B238">
+        <v>2</v>
+      </c>
+      <c r="C238">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>87</v>
+      </c>
+      <c r="B239">
+        <v>2</v>
+      </c>
+      <c r="C239">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>63</v>
+      </c>
+      <c r="B240">
+        <v>2</v>
+      </c>
+      <c r="C240">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>2</v>
+      </c>
+      <c r="C241">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>198</v>
+      </c>
+      <c r="B242">
+        <v>2</v>
+      </c>
+      <c r="C242">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>562</v>
+      </c>
+      <c r="B243">
+        <v>2</v>
+      </c>
+      <c r="C243">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>110</v>
+      </c>
+      <c r="B244">
+        <v>2</v>
+      </c>
+      <c r="C244">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>571</v>
+      </c>
+      <c r="B245">
+        <v>2</v>
+      </c>
+      <c r="C245">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>436</v>
+      </c>
+      <c r="B246">
+        <v>2</v>
+      </c>
+      <c r="C246">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>416</v>
+      </c>
+      <c r="B247">
+        <v>2</v>
+      </c>
+      <c r="C247">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>56</v>
+      </c>
+      <c r="B248">
+        <v>2</v>
+      </c>
+      <c r="C248">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>537</v>
+      </c>
+      <c r="B249">
+        <v>2</v>
+      </c>
+      <c r="C249">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>437</v>
+      </c>
+      <c r="B250">
+        <v>2</v>
+      </c>
+      <c r="C250">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>559</v>
+      </c>
+      <c r="B251">
+        <v>2</v>
+      </c>
+      <c r="C251">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>433</v>
+      </c>
+      <c r="B252">
+        <v>2</v>
+      </c>
+      <c r="C252">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>201</v>
+      </c>
+      <c r="B253">
+        <v>2</v>
+      </c>
+      <c r="C253">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>234</v>
+      </c>
+      <c r="B254">
+        <v>2</v>
+      </c>
+      <c r="C254">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>219</v>
+      </c>
+      <c r="B255">
+        <v>2</v>
+      </c>
+      <c r="C255">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>203</v>
+      </c>
+      <c r="B256">
+        <v>2</v>
+      </c>
+      <c r="C256">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>179</v>
+      </c>
+      <c r="B257">
+        <v>2</v>
+      </c>
+      <c r="C257">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>363</v>
+      </c>
+      <c r="B258">
+        <v>2</v>
+      </c>
+      <c r="C258">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>125</v>
+      </c>
+      <c r="B259">
+        <v>2</v>
+      </c>
+      <c r="C259">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>235</v>
+      </c>
+      <c r="B260">
+        <v>2</v>
+      </c>
+      <c r="C260">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>114</v>
+      </c>
+      <c r="B261">
+        <v>2</v>
+      </c>
+      <c r="C261">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>111</v>
+      </c>
+      <c r="B262">
+        <v>2</v>
+      </c>
+      <c r="C262">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>498</v>
+      </c>
+      <c r="B263">
+        <v>2</v>
+      </c>
+      <c r="C263">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>434</v>
+      </c>
+      <c r="B264">
+        <v>2</v>
+      </c>
+      <c r="C264">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>572</v>
+      </c>
+      <c r="B265">
+        <v>2</v>
+      </c>
+      <c r="C265">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>546</v>
+      </c>
+      <c r="B266">
+        <v>2</v>
+      </c>
+      <c r="C266">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>214</v>
+      </c>
+      <c r="B267">
+        <v>2</v>
+      </c>
+      <c r="C267">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>217</v>
+      </c>
+      <c r="B268">
+        <v>2</v>
+      </c>
+      <c r="C268">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>544</v>
+      </c>
+      <c r="B269">
+        <v>2</v>
+      </c>
+      <c r="C269">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>236</v>
+      </c>
+      <c r="B270">
+        <v>2</v>
+      </c>
+      <c r="C270">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>242</v>
+      </c>
+      <c r="B271">
+        <v>2</v>
+      </c>
+      <c r="C271">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>573</v>
+      </c>
+      <c r="B272">
+        <v>2</v>
+      </c>
+      <c r="C272">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>91</v>
+      </c>
+      <c r="B273">
+        <v>2</v>
+      </c>
+      <c r="C273">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>222</v>
+      </c>
+      <c r="B274">
+        <v>2</v>
+      </c>
+      <c r="C274">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>431</v>
+      </c>
+      <c r="B275">
+        <v>2</v>
+      </c>
+      <c r="C275">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>223</v>
+      </c>
+      <c r="B276">
+        <v>2</v>
+      </c>
+      <c r="C276">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>206</v>
+      </c>
+      <c r="B277">
+        <v>2</v>
+      </c>
+      <c r="C277">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>101</v>
+      </c>
+      <c r="B278">
+        <v>2</v>
+      </c>
+      <c r="C278">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>224</v>
+      </c>
+      <c r="B279">
+        <v>2</v>
+      </c>
+      <c r="C279">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>213</v>
+      </c>
+      <c r="B280">
+        <v>2</v>
+      </c>
+      <c r="C280">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>225</v>
+      </c>
+      <c r="B281">
+        <v>2</v>
+      </c>
+      <c r="C281">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>227</v>
+      </c>
+      <c r="B282">
+        <v>2</v>
+      </c>
+      <c r="C282">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>237</v>
+      </c>
+      <c r="B283">
+        <v>2</v>
+      </c>
+      <c r="C283">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>202</v>
+      </c>
+      <c r="B284">
+        <v>2</v>
+      </c>
+      <c r="C284">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>119</v>
+      </c>
+      <c r="B285">
+        <v>2</v>
+      </c>
+      <c r="C285">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>209</v>
+      </c>
+      <c r="B286">
+        <v>2</v>
+      </c>
+      <c r="C286">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>75</v>
+      </c>
+      <c r="B287">
+        <v>2</v>
+      </c>
+      <c r="C287">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>9390334320</v>
+      </c>
+      <c r="B288">
+        <v>2</v>
+      </c>
+      <c r="C288">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>325</v>
+      </c>
+      <c r="B289">
+        <v>2</v>
+      </c>
+      <c r="C289">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>182</v>
+      </c>
+      <c r="B290">
+        <v>2</v>
+      </c>
+      <c r="C290">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>183</v>
+      </c>
+      <c r="B291">
+        <v>2</v>
+      </c>
+      <c r="C291">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>531</v>
+      </c>
+      <c r="B292">
+        <v>2</v>
+      </c>
+      <c r="C292">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>523</v>
+      </c>
+      <c r="B293">
+        <v>2</v>
+      </c>
+      <c r="C293">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>264</v>
+      </c>
+      <c r="B294">
+        <v>2</v>
+      </c>
+      <c r="C294">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>233</v>
+      </c>
+      <c r="B295">
+        <v>2</v>
+      </c>
+      <c r="C295">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>574</v>
+      </c>
+      <c r="B296">
+        <v>2</v>
+      </c>
+      <c r="C296">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>241</v>
+      </c>
+      <c r="B297">
+        <v>2</v>
+      </c>
+      <c r="C297">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>208</v>
+      </c>
+      <c r="B298">
+        <v>2</v>
+      </c>
+      <c r="C298">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>387</v>
+      </c>
+      <c r="B299">
+        <v>2</v>
+      </c>
+      <c r="C299">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>211</v>
+      </c>
+      <c r="B300">
+        <v>2</v>
+      </c>
+      <c r="C300">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>563</v>
+      </c>
+      <c r="B301">
+        <v>2</v>
+      </c>
+      <c r="C301">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>66</v>
+      </c>
+      <c r="B302">
+        <v>2</v>
+      </c>
+      <c r="C302">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>118</v>
+      </c>
+      <c r="B303">
+        <v>2</v>
+      </c>
+      <c r="C303">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>221</v>
+      </c>
+      <c r="B304">
+        <v>2</v>
+      </c>
+      <c r="C304">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>218</v>
+      </c>
+      <c r="B305">
+        <v>2</v>
+      </c>
+      <c r="C305">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>506</v>
+      </c>
+      <c r="B306">
+        <v>2</v>
+      </c>
+      <c r="C306">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>555</v>
+      </c>
+      <c r="B307">
+        <v>2</v>
+      </c>
+      <c r="C307">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>192</v>
+      </c>
+      <c r="B308">
+        <v>2</v>
+      </c>
+      <c r="C308">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>432</v>
+      </c>
+      <c r="B309">
+        <v>2</v>
+      </c>
+      <c r="C309">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>212</v>
+      </c>
+      <c r="B310">
+        <v>2</v>
+      </c>
+      <c r="C310">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>229</v>
+      </c>
+      <c r="B311">
+        <v>2</v>
+      </c>
+      <c r="C311">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>200</v>
+      </c>
+      <c r="B312">
+        <v>2</v>
+      </c>
+      <c r="C312">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>204</v>
+      </c>
+      <c r="B313">
+        <v>2</v>
+      </c>
+      <c r="C313">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>435</v>
+      </c>
+      <c r="B314">
+        <v>2</v>
+      </c>
+      <c r="C314">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>231</v>
+      </c>
+      <c r="B315">
+        <v>2</v>
+      </c>
+      <c r="C315">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>553</v>
+      </c>
+      <c r="B316">
+        <v>2</v>
+      </c>
+      <c r="C316">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>331</v>
+      </c>
+      <c r="B317">
+        <v>2</v>
+      </c>
+      <c r="C317">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>115</v>
+      </c>
+      <c r="B318">
+        <v>1</v>
+      </c>
+      <c r="C318">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>412</v>
+      </c>
+      <c r="B319">
+        <v>1</v>
+      </c>
+      <c r="C319">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>549</v>
+      </c>
+      <c r="B320">
+        <v>1</v>
+      </c>
+      <c r="C320">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>285</v>
+      </c>
+      <c r="B321">
+        <v>1</v>
+      </c>
+      <c r="C321">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>496</v>
+      </c>
+      <c r="B322">
+        <v>1</v>
+      </c>
+      <c r="C322">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>263</v>
+      </c>
+      <c r="B323">
+        <v>1</v>
+      </c>
+      <c r="C323">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>468</v>
+      </c>
+      <c r="B324">
+        <v>1</v>
+      </c>
+      <c r="C324">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>359</v>
+      </c>
+      <c r="B325">
+        <v>1</v>
+      </c>
+      <c r="C325">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>422</v>
+      </c>
+      <c r="B326">
+        <v>1</v>
+      </c>
+      <c r="C326">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>299</v>
+      </c>
+      <c r="B327">
+        <v>1</v>
+      </c>
+      <c r="C327">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>397</v>
+      </c>
+      <c r="B328">
+        <v>1</v>
+      </c>
+      <c r="C328">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>425</v>
+      </c>
+      <c r="B329">
+        <v>1</v>
+      </c>
+      <c r="C329">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>351</v>
+      </c>
+      <c r="B330">
+        <v>1</v>
+      </c>
+      <c r="C330">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>361</v>
+      </c>
+      <c r="B331">
+        <v>1</v>
+      </c>
+      <c r="C331">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>311</v>
+      </c>
+      <c r="B332">
+        <v>1</v>
+      </c>
+      <c r="C332">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>244</v>
+      </c>
+      <c r="B333">
+        <v>1</v>
+      </c>
+      <c r="C333">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>396</v>
+      </c>
+      <c r="B334">
+        <v>1</v>
+      </c>
+      <c r="C334">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>575</v>
+      </c>
+      <c r="B335">
+        <v>1</v>
+      </c>
+      <c r="C335">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>322</v>
+      </c>
+      <c r="B336">
+        <v>1</v>
+      </c>
+      <c r="C336">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>454</v>
+      </c>
+      <c r="B337">
+        <v>1</v>
+      </c>
+      <c r="C337">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>457</v>
+      </c>
+      <c r="B338">
+        <v>1</v>
+      </c>
+      <c r="C338">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>301</v>
+      </c>
+      <c r="B339">
+        <v>1</v>
+      </c>
+      <c r="C339">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>394</v>
+      </c>
+      <c r="B340">
+        <v>1</v>
+      </c>
+      <c r="C340">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>447</v>
+      </c>
+      <c r="B341">
+        <v>1</v>
+      </c>
+      <c r="C341">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>469</v>
+      </c>
+      <c r="B342">
+        <v>1</v>
+      </c>
+      <c r="C342">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>265</v>
+      </c>
+      <c r="B343">
+        <v>1</v>
+      </c>
+      <c r="C343">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>517</v>
+      </c>
+      <c r="B344">
+        <v>1</v>
+      </c>
+      <c r="C344">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>367</v>
+      </c>
+      <c r="B345">
+        <v>1</v>
+      </c>
+      <c r="C345">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>576</v>
+      </c>
+      <c r="B346">
+        <v>1</v>
+      </c>
+      <c r="C346">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>303</v>
+      </c>
+      <c r="B347">
+        <v>1</v>
+      </c>
+      <c r="C347">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>261</v>
+      </c>
+      <c r="B348">
+        <v>1</v>
+      </c>
+      <c r="C348">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>283</v>
+      </c>
+      <c r="B349">
+        <v>1</v>
+      </c>
+      <c r="C349">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>441</v>
+      </c>
+      <c r="B350">
+        <v>1</v>
+      </c>
+      <c r="C350">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>228</v>
+      </c>
+      <c r="B351">
+        <v>1</v>
+      </c>
+      <c r="C351">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>338</v>
+      </c>
+      <c r="B352">
+        <v>1</v>
+      </c>
+      <c r="C352">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>456</v>
+      </c>
+      <c r="B353">
+        <v>1</v>
+      </c>
+      <c r="C353">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>384</v>
+      </c>
+      <c r="B354">
+        <v>1</v>
+      </c>
+      <c r="C354">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>96</v>
+      </c>
+      <c r="B355">
+        <v>1</v>
+      </c>
+      <c r="C355">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>388</v>
+      </c>
+      <c r="B356">
+        <v>1</v>
+      </c>
+      <c r="C356">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>112</v>
+      </c>
+      <c r="B357">
+        <v>1</v>
+      </c>
+      <c r="C357">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>403</v>
+      </c>
+      <c r="B358">
+        <v>1</v>
+      </c>
+      <c r="C358">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>305</v>
+      </c>
+      <c r="B359">
+        <v>1</v>
+      </c>
+      <c r="C359">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>407</v>
+      </c>
+      <c r="B360">
+        <v>1</v>
+      </c>
+      <c r="C360">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>371</v>
+      </c>
+      <c r="B361">
+        <v>1</v>
+      </c>
+      <c r="C361">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>411</v>
+      </c>
+      <c r="B362">
+        <v>1</v>
+      </c>
+      <c r="C362">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>267</v>
+      </c>
+      <c r="B363">
+        <v>1</v>
+      </c>
+      <c r="C363">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>458</v>
+      </c>
+      <c r="B364">
+        <v>1</v>
+      </c>
+      <c r="C364">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>373</v>
+      </c>
+      <c r="B365">
+        <v>1</v>
+      </c>
+      <c r="C365">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>417</v>
+      </c>
+      <c r="B366">
+        <v>1</v>
+      </c>
+      <c r="C366">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>307</v>
+      </c>
+      <c r="B367">
+        <v>1</v>
+      </c>
+      <c r="C367">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>255</v>
+      </c>
+      <c r="B368">
+        <v>1</v>
+      </c>
+      <c r="C368">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>375</v>
+      </c>
+      <c r="B369">
+        <v>1</v>
+      </c>
+      <c r="C369">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>292</v>
+      </c>
+      <c r="B370">
+        <v>1</v>
+      </c>
+      <c r="C370">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>450</v>
+      </c>
+      <c r="B371">
+        <v>1</v>
+      </c>
+      <c r="C371">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>406</v>
+      </c>
+      <c r="B372">
+        <v>1</v>
+      </c>
+      <c r="C372">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>309</v>
+      </c>
+      <c r="B373">
+        <v>1</v>
+      </c>
+      <c r="C373">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>556</v>
+      </c>
+      <c r="B374">
+        <v>1</v>
+      </c>
+      <c r="C374">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>577</v>
+      </c>
+      <c r="B375">
+        <v>1</v>
+      </c>
+      <c r="C375">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>527</v>
+      </c>
+      <c r="B376">
+        <v>1</v>
+      </c>
+      <c r="C376">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>578</v>
+      </c>
+      <c r="B377">
+        <v>1</v>
+      </c>
+      <c r="C377">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>294</v>
+      </c>
+      <c r="B378">
+        <v>1</v>
+      </c>
+      <c r="C378">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>350</v>
+      </c>
+      <c r="B379">
+        <v>1</v>
+      </c>
+      <c r="C379">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>424</v>
+      </c>
+      <c r="B380">
+        <v>1</v>
+      </c>
+      <c r="C380">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>269</v>
+      </c>
+      <c r="B381">
+        <v>1</v>
+      </c>
+      <c r="C381">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>440</v>
+      </c>
+      <c r="B382">
+        <v>1</v>
+      </c>
+      <c r="C382">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>451</v>
+      </c>
+      <c r="B383">
+        <v>1</v>
+      </c>
+      <c r="C383">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>354</v>
+      </c>
+      <c r="B384">
+        <v>1</v>
+      </c>
+      <c r="C384">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>310</v>
+      </c>
+      <c r="B385">
+        <v>1</v>
+      </c>
+      <c r="C385">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>497</v>
+      </c>
+      <c r="B386">
+        <v>1</v>
+      </c>
+      <c r="C386">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>439</v>
+      </c>
+      <c r="B387">
+        <v>1</v>
+      </c>
+      <c r="C387">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>426</v>
+      </c>
+      <c r="B388">
+        <v>1</v>
+      </c>
+      <c r="C388">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>459</v>
+      </c>
+      <c r="B389">
+        <v>1</v>
+      </c>
+      <c r="C389">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>465</v>
+      </c>
+      <c r="B390">
+        <v>1</v>
+      </c>
+      <c r="C390">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>382</v>
+      </c>
+      <c r="B391">
+        <v>1</v>
+      </c>
+      <c r="C391">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>381</v>
+      </c>
+      <c r="B392">
+        <v>1</v>
+      </c>
+      <c r="C392">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>252</v>
+      </c>
+      <c r="B393">
+        <v>1</v>
+      </c>
+      <c r="C393">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>386</v>
+      </c>
+      <c r="B394">
+        <v>1</v>
+      </c>
+      <c r="C394">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>383</v>
+      </c>
+      <c r="B395">
+        <v>1</v>
+      </c>
+      <c r="C395">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>191</v>
+      </c>
+      <c r="B396">
+        <v>1</v>
+      </c>
+      <c r="C396">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>312</v>
+      </c>
+      <c r="B397">
+        <v>1</v>
+      </c>
+      <c r="C397">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>390</v>
+      </c>
+      <c r="B398">
+        <v>1</v>
+      </c>
+      <c r="C398">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>385</v>
+      </c>
+      <c r="B399">
+        <v>1</v>
+      </c>
+      <c r="C399">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>466</v>
+      </c>
+      <c r="B400">
+        <v>1</v>
+      </c>
+      <c r="C400">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>355</v>
+      </c>
+      <c r="B401">
+        <v>1</v>
+      </c>
+      <c r="C401">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>276</v>
+      </c>
+      <c r="B402">
+        <v>1</v>
+      </c>
+      <c r="C402">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>579</v>
+      </c>
+      <c r="B403">
+        <v>1</v>
+      </c>
+      <c r="C403">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>324</v>
+      </c>
+      <c r="B404">
+        <v>1</v>
+      </c>
+      <c r="C404">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>580</v>
+      </c>
+      <c r="B405">
+        <v>1</v>
+      </c>
+      <c r="C405">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>254</v>
+      </c>
+      <c r="B406">
+        <v>1</v>
+      </c>
+      <c r="C406">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>581</v>
+      </c>
+      <c r="B407">
+        <v>1</v>
+      </c>
+      <c r="C407">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>326</v>
+      </c>
+      <c r="B408">
+        <v>1</v>
+      </c>
+      <c r="C408">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>539</v>
+      </c>
+      <c r="B409">
+        <v>1</v>
+      </c>
+      <c r="C409">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>278</v>
+      </c>
+      <c r="B410">
+        <v>1</v>
+      </c>
+      <c r="C410">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>366</v>
+      </c>
+      <c r="B411">
+        <v>1</v>
+      </c>
+      <c r="C411">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>328</v>
+      </c>
+      <c r="B412">
+        <v>1</v>
+      </c>
+      <c r="C412">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>472</v>
+      </c>
+      <c r="B413">
+        <v>1</v>
+      </c>
+      <c r="C413">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>392</v>
+      </c>
+      <c r="B414">
+        <v>1</v>
+      </c>
+      <c r="C414">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>510</v>
+      </c>
+      <c r="B415">
+        <v>1</v>
+      </c>
+      <c r="C415">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>329</v>
+      </c>
+      <c r="B416">
+        <v>1</v>
+      </c>
+      <c r="C416">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>368</v>
+      </c>
+      <c r="B417">
+        <v>1</v>
+      </c>
+      <c r="C417">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>395</v>
+      </c>
+      <c r="B418">
+        <v>1</v>
+      </c>
+      <c r="C418">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>369</v>
+      </c>
+      <c r="B419">
+        <v>1</v>
+      </c>
+      <c r="C419">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>399</v>
+      </c>
+      <c r="B420">
+        <v>1</v>
+      </c>
+      <c r="C420">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>370</v>
+      </c>
+      <c r="B421">
+        <v>1</v>
+      </c>
+      <c r="C421">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>400</v>
+      </c>
+      <c r="B422">
+        <v>1</v>
+      </c>
+      <c r="C422">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>519</v>
+      </c>
+      <c r="B423">
+        <v>1</v>
+      </c>
+      <c r="C423">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>421</v>
+      </c>
+      <c r="B424">
+        <v>1</v>
+      </c>
+      <c r="C424">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>419</v>
+      </c>
+      <c r="B425">
+        <v>1</v>
+      </c>
+      <c r="C425">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>402</v>
+      </c>
+      <c r="B426">
+        <v>1</v>
+      </c>
+      <c r="C426">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>286</v>
+      </c>
+      <c r="B427">
+        <v>1</v>
+      </c>
+      <c r="C427">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>404</v>
+      </c>
+      <c r="B428">
+        <v>1</v>
+      </c>
+      <c r="C428">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>340</v>
+      </c>
+      <c r="B429">
+        <v>1</v>
+      </c>
+      <c r="C429">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>408</v>
+      </c>
+      <c r="B430">
+        <v>1</v>
+      </c>
+      <c r="C430">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>504</v>
+      </c>
+      <c r="B431">
+        <v>1</v>
+      </c>
+      <c r="C431">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>543</v>
+      </c>
+      <c r="B432">
+        <v>1</v>
+      </c>
+      <c r="C432">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>420</v>
+      </c>
+      <c r="B433">
+        <v>1</v>
+      </c>
+      <c r="C433">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>461</v>
+      </c>
+      <c r="B434">
+        <v>1</v>
+      </c>
+      <c r="C434">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>270</v>
+      </c>
+      <c r="B435">
+        <v>1</v>
+      </c>
+      <c r="C435">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>247</v>
+      </c>
+      <c r="B436">
+        <v>1</v>
+      </c>
+      <c r="C436">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>452</v>
+      </c>
+      <c r="B437">
+        <v>1</v>
+      </c>
+      <c r="C437">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>535</v>
+      </c>
+      <c r="B438">
+        <v>1</v>
+      </c>
+      <c r="C438">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>453</v>
+      </c>
+      <c r="B439">
+        <v>1</v>
+      </c>
+      <c r="C439">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>352</v>
+      </c>
+      <c r="B440">
+        <v>1</v>
+      </c>
+      <c r="C440">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>548</v>
+      </c>
+      <c r="B441">
+        <v>1</v>
+      </c>
+      <c r="C441">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>463</v>
+      </c>
+      <c r="B442">
+        <v>1</v>
+      </c>
+      <c r="C442">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>243</v>
+      </c>
+      <c r="B443">
+        <v>1</v>
+      </c>
+      <c r="C443">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>464</v>
+      </c>
+      <c r="B444">
+        <v>1</v>
+      </c>
+      <c r="C444">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>391</v>
+      </c>
+      <c r="B445">
+        <v>1</v>
+      </c>
+      <c r="C445">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>558</v>
+      </c>
+      <c r="B446">
+        <v>1</v>
+      </c>
+      <c r="C446">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>460</v>
+      </c>
+      <c r="B447">
+        <v>1</v>
+      </c>
+      <c r="C447">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>358</v>
+      </c>
+      <c r="B448">
+        <v>1</v>
+      </c>
+      <c r="C448">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>316</v>
+      </c>
+      <c r="B449">
+        <v>1</v>
+      </c>
+      <c r="C449">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>360</v>
+      </c>
+      <c r="B450">
+        <v>1</v>
+      </c>
+      <c r="C450">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>288</v>
+      </c>
+      <c r="B451">
+        <v>1</v>
+      </c>
+      <c r="C451">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>296</v>
+      </c>
+      <c r="B452">
+        <v>1</v>
+      </c>
+      <c r="C452">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>344</v>
+      </c>
+      <c r="B453">
+        <v>1</v>
+      </c>
+      <c r="C453">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>251</v>
+      </c>
+      <c r="B454">
+        <v>1</v>
+      </c>
+      <c r="C454">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>462</v>
+      </c>
+      <c r="B455">
+        <v>1</v>
+      </c>
+      <c r="C455">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>582</v>
+      </c>
+      <c r="B456">
+        <v>1</v>
+      </c>
+      <c r="C456">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>290</v>
+      </c>
+      <c r="B457">
+        <v>1</v>
+      </c>
+      <c r="C457">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>467</v>
+      </c>
+      <c r="B458">
+        <v>1</v>
+      </c>
+      <c r="C458">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>313</v>
+      </c>
+      <c r="B459">
+        <v>1</v>
+      </c>
+      <c r="C459">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>473</v>
+      </c>
+      <c r="B460">
+        <v>1</v>
+      </c>
+      <c r="C460">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>347</v>
+      </c>
+      <c r="B461">
+        <v>1</v>
+      </c>
+      <c r="C461">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>536</v>
+      </c>
+      <c r="B462">
+        <v>1</v>
+      </c>
+      <c r="C462">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>442</v>
+      </c>
+      <c r="B463">
+        <v>1</v>
+      </c>
+      <c r="C463">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>297</v>
+      </c>
+      <c r="B464">
+        <v>1</v>
+      </c>
+      <c r="C464">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>205</v>
+      </c>
+      <c r="B465">
+        <v>1</v>
+      </c>
+      <c r="C465">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>9805957916</v>
+      </c>
+      <c r="B466">
+        <v>1</v>
+      </c>
+      <c r="C466">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>248</v>
+      </c>
+      <c r="B467">
+        <v>1</v>
+      </c>
+      <c r="C467">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>260</v>
+      </c>
+      <c r="B468">
+        <v>1</v>
+      </c>
+      <c r="C468">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>315</v>
+      </c>
+      <c r="B469">
+        <v>1</v>
+      </c>
+      <c r="C469">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>268</v>
+      </c>
+      <c r="B470">
+        <v>1</v>
+      </c>
+      <c r="C470">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>446</v>
+      </c>
+      <c r="B471">
+        <v>1</v>
+      </c>
+      <c r="C471">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>455</v>
+      </c>
+      <c r="B472">
+        <v>1</v>
+      </c>
+      <c r="C472">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>427</v>
+      </c>
+      <c r="B473">
+        <v>1</v>
+      </c>
+      <c r="C473">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>551</v>
+      </c>
+      <c r="B474">
+        <v>1</v>
+      </c>
+      <c r="C474">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>554</v>
+      </c>
+      <c r="B475">
+        <v>1</v>
+      </c>
+      <c r="C475">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>293</v>
+      </c>
+      <c r="B476">
+        <v>1</v>
+      </c>
+      <c r="C476">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>339</v>
+      </c>
+      <c r="B477">
+        <v>1</v>
+      </c>
+      <c r="C477">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>321</v>
+      </c>
+      <c r="B478">
+        <v>1</v>
+      </c>
+      <c r="C478">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>362</v>
+      </c>
+      <c r="B479">
+        <v>1</v>
+      </c>
+      <c r="C479">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>443</v>
+      </c>
+      <c r="B480">
+        <v>1</v>
+      </c>
+      <c r="C480">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>257</v>
+      </c>
+      <c r="B481">
+        <v>1</v>
+      </c>
+      <c r="C481">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>9820042500</v>
+      </c>
+      <c r="B482">
+        <v>1</v>
+      </c>
+      <c r="C482">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>448</v>
+      </c>
+      <c r="B483">
+        <v>1</v>
+      </c>
+      <c r="C483">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>380</v>
+      </c>
+      <c r="B484">
+        <v>1</v>
+      </c>
+      <c r="C484">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>314</v>
+      </c>
+      <c r="B485">
+        <v>1</v>
+      </c>
+      <c r="C485">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>398</v>
+      </c>
+      <c r="B486">
+        <v>1</v>
+      </c>
+      <c r="C486">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>249</v>
+      </c>
+      <c r="B487">
+        <v>1</v>
+      </c>
+      <c r="C487">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>552</v>
+      </c>
+      <c r="B488">
+        <v>1</v>
+      </c>
+      <c r="C488">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>318</v>
+      </c>
+      <c r="B489">
+        <v>1</v>
+      </c>
+      <c r="C489">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>410</v>
+      </c>
+      <c r="B490">
+        <v>1</v>
+      </c>
+      <c r="C490">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>333</v>
+      </c>
+      <c r="B491">
+        <v>1</v>
+      </c>
+      <c r="C491">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>95</v>
+      </c>
+      <c r="B492">
+        <v>1</v>
+      </c>
+      <c r="C492">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>449</v>
+      </c>
+      <c r="B493">
+        <v>1</v>
+      </c>
+      <c r="C493">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>470</v>
+      </c>
+      <c r="B494">
+        <v>1</v>
+      </c>
+      <c r="C494">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>320</v>
+      </c>
+      <c r="B495">
+        <v>1</v>
+      </c>
+      <c r="C495">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>583</v>
+      </c>
+      <c r="B496">
+        <v>1</v>
+      </c>
+      <c r="C496">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>117</v>
+      </c>
+      <c r="B497">
+        <v>1</v>
+      </c>
+      <c r="C497">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>323</v>
+      </c>
+      <c r="B498">
+        <v>1</v>
+      </c>
+      <c r="C498">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>414</v>
+      </c>
+      <c r="B499">
+        <v>1</v>
+      </c>
+      <c r="C499">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>423</v>
+      </c>
+      <c r="B500">
+        <v>1</v>
+      </c>
+      <c r="C500">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>444</v>
+      </c>
+      <c r="B501">
+        <v>1</v>
+      </c>
+      <c r="C501">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <v>13111087001</v>
+      </c>
+      <c r="B502">
+        <v>1</v>
+      </c>
+      <c r="C502">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>532</v>
+      </c>
+      <c r="B503">
+        <v>1</v>
+      </c>
+      <c r="C503">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>349</v>
+      </c>
+      <c r="B504">
+        <v>1</v>
+      </c>
+      <c r="C504">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>428</v>
+      </c>
+      <c r="B505">
+        <v>1</v>
+      </c>
+      <c r="C505">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>389</v>
+      </c>
+      <c r="B506">
+        <v>1</v>
+      </c>
+      <c r="C506">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>413</v>
+      </c>
+      <c r="B507">
+        <v>1</v>
+      </c>
+      <c r="C507">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>584</v>
+      </c>
+      <c r="B508">
+        <v>1</v>
+      </c>
+      <c r="C508">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>280</v>
+      </c>
+      <c r="B509">
+        <v>1</v>
+      </c>
+      <c r="C509">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>245</v>
+      </c>
+      <c r="B510">
+        <v>1</v>
+      </c>
+      <c r="C510">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>259</v>
+      </c>
+      <c r="B511">
+        <v>1</v>
+      </c>
+      <c r="C511">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>409</v>
+      </c>
+      <c r="B512">
+        <v>1</v>
+      </c>
+      <c r="C512">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>295</v>
+      </c>
+      <c r="B513">
+        <v>1</v>
+      </c>
+      <c r="C513">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>401</v>
+      </c>
+      <c r="B514">
+        <v>1</v>
+      </c>
+      <c r="C514">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>337</v>
+      </c>
+      <c r="B515">
+        <v>1</v>
+      </c>
+      <c r="C515">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>356</v>
+      </c>
+      <c r="B516">
+        <v>1</v>
+      </c>
+      <c r="C516">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>342</v>
+      </c>
+      <c r="B517">
+        <v>1</v>
+      </c>
+      <c r="C517">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>341</v>
+      </c>
+      <c r="B518">
+        <v>1</v>
+      </c>
+      <c r="C518">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>298</v>
+      </c>
+      <c r="B519">
+        <v>1</v>
+      </c>
+      <c r="C519">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>271</v>
+      </c>
+      <c r="B520">
+        <v>1</v>
+      </c>
+      <c r="C520">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>262</v>
+      </c>
+      <c r="B521">
+        <v>1</v>
+      </c>
+      <c r="C521">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>319</v>
+      </c>
+      <c r="B522">
+        <v>1</v>
+      </c>
+      <c r="C522">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>67</v>
+      </c>
+      <c r="B523">
+        <v>1</v>
+      </c>
+      <c r="C523">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>327</v>
+      </c>
+      <c r="B524">
+        <v>1</v>
+      </c>
+      <c r="C524">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A525">
+        <v>9452028000</v>
+      </c>
+      <c r="B525">
+        <v>1</v>
+      </c>
+      <c r="C525">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>246</v>
+      </c>
+      <c r="B526">
+        <v>1</v>
+      </c>
+      <c r="C526">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>308</v>
+      </c>
+      <c r="B527">
+        <v>1</v>
+      </c>
+      <c r="C527">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>415</v>
+      </c>
+      <c r="B528">
+        <v>1</v>
+      </c>
+      <c r="C528">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>106</v>
+      </c>
+      <c r="B529">
+        <v>1</v>
+      </c>
+      <c r="C529">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>565</v>
+      </c>
+      <c r="B530">
+        <v>1</v>
+      </c>
+      <c r="C530">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>287</v>
+      </c>
+      <c r="B531">
+        <v>1</v>
+      </c>
+      <c r="C531">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>418</v>
+      </c>
+      <c r="B532">
+        <v>1</v>
+      </c>
+      <c r="C532">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A533">
+        <v>91201434003</v>
+      </c>
+      <c r="B533">
+        <v>1</v>
+      </c>
+      <c r="C533">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>374</v>
+      </c>
+      <c r="B534">
+        <v>1</v>
+      </c>
+      <c r="C534">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A535">
+        <v>9454003010</v>
+      </c>
+      <c r="B535">
+        <v>1</v>
+      </c>
+      <c r="C535">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>122</v>
+      </c>
+      <c r="B536">
+        <v>1</v>
+      </c>
+      <c r="C536">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>273</v>
+      </c>
+      <c r="B537">
+        <v>1</v>
+      </c>
+      <c r="C537">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>514</v>
+      </c>
+      <c r="B538">
+        <v>1</v>
+      </c>
+      <c r="C538">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>275</v>
+      </c>
+      <c r="B539">
+        <v>1</v>
+      </c>
+      <c r="C539">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>291</v>
+      </c>
+      <c r="B540">
+        <v>1</v>
+      </c>
+      <c r="C540">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>279</v>
+      </c>
+      <c r="B541">
+        <v>1</v>
+      </c>
+      <c r="C541">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>376</v>
+      </c>
+      <c r="B542">
+        <v>1</v>
+      </c>
+      <c r="C542">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>69</v>
+      </c>
+      <c r="B543">
+        <v>1</v>
+      </c>
+      <c r="C543">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>508</v>
+      </c>
+      <c r="B544">
+        <v>1</v>
+      </c>
+      <c r="C544">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>284</v>
+      </c>
+      <c r="B545">
+        <v>1</v>
+      </c>
+      <c r="C545">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>378</v>
+      </c>
+      <c r="B546">
+        <v>1</v>
+      </c>
+      <c r="C546">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>500</v>
+      </c>
+      <c r="B547">
+        <v>1</v>
+      </c>
+      <c r="C547">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>393</v>
+      </c>
+      <c r="B548">
+        <v>1</v>
+      </c>
+      <c r="C548">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>345</v>
+      </c>
+      <c r="B549">
+        <v>1</v>
+      </c>
+      <c r="C549">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>274</v>
+      </c>
+      <c r="B550">
+        <v>1</v>
+      </c>
+      <c r="C550">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>346</v>
+      </c>
+      <c r="B551">
+        <v>1</v>
+      </c>
+      <c r="C551">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>513</v>
+      </c>
+      <c r="B552">
+        <v>1</v>
+      </c>
+      <c r="C552">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>379</v>
+      </c>
+      <c r="B553">
+        <v>1</v>
+      </c>
+      <c r="C553">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>405</v>
+      </c>
+      <c r="B554">
+        <v>1</v>
+      </c>
+      <c r="C554">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A555">
+        <v>960010606500</v>
+      </c>
+      <c r="B555">
+        <v>1</v>
+      </c>
+      <c r="C555">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>126</v>
+      </c>
+      <c r="B556">
+        <v>1</v>
+      </c>
+      <c r="C556">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>216</v>
+      </c>
+      <c r="B557">
+        <v>1</v>
+      </c>
+      <c r="C557">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>471</v>
+      </c>
+      <c r="B558">
+        <v>1</v>
+      </c>
+      <c r="C558">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>357</v>
+      </c>
+      <c r="B559">
+        <v>1</v>
+      </c>
+      <c r="C559">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>250</v>
+      </c>
+      <c r="B560">
+        <v>1</v>
+      </c>
+      <c r="C560">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>365</v>
+      </c>
+      <c r="B561">
+        <v>1</v>
+      </c>
+      <c r="C561">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>46</v>
+      </c>
+      <c r="B562">
+        <v>1</v>
+      </c>
+      <c r="C562">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>272</v>
+      </c>
+      <c r="B563">
+        <v>1</v>
+      </c>
+      <c r="C563">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>377</v>
+      </c>
+      <c r="B564">
+        <v>1</v>
+      </c>
+      <c r="C564">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>364</v>
+      </c>
+      <c r="B565">
+        <v>1</v>
+      </c>
+      <c r="C565">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>121</v>
+      </c>
+      <c r="B566">
+        <v>1</v>
+      </c>
+      <c r="C566">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>253</v>
+      </c>
+      <c r="B567">
+        <v>1</v>
+      </c>
+      <c r="C567">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>258</v>
+      </c>
+      <c r="B568">
+        <v>1</v>
+      </c>
+      <c r="C568">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>256</v>
+      </c>
+      <c r="B569">
+        <v>1</v>
+      </c>
+      <c r="C569">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>86</v>
+      </c>
+      <c r="B570">
+        <v>1</v>
+      </c>
+      <c r="C570">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>281</v>
+      </c>
+      <c r="B571">
+        <v>1</v>
+      </c>
+      <c r="C571">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>334</v>
+      </c>
+      <c r="B572">
+        <v>1</v>
+      </c>
+      <c r="C572">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>304</v>
+      </c>
+      <c r="B573">
+        <v>1</v>
+      </c>
+      <c r="C573">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>266</v>
+      </c>
+      <c r="B574">
+        <v>1</v>
+      </c>
+      <c r="C574">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>300</v>
+      </c>
+      <c r="B575">
+        <v>1</v>
+      </c>
+      <c r="C575">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>99</v>
+      </c>
+      <c r="B576">
+        <v>1</v>
+      </c>
+      <c r="C576">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>302</v>
+      </c>
+      <c r="B577">
+        <v>1</v>
+      </c>
+      <c r="C577">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>445</v>
+      </c>
+      <c r="B578">
+        <v>1</v>
+      </c>
+      <c r="C578">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>306</v>
+      </c>
+      <c r="B579">
+        <v>1</v>
+      </c>
+      <c r="C579">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>277</v>
+      </c>
+      <c r="B580">
+        <v>1</v>
+      </c>
+      <c r="C580">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>317</v>
+      </c>
+      <c r="B581">
+        <v>1</v>
+      </c>
+      <c r="C581">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>438</v>
+      </c>
+      <c r="B582">
+        <v>1</v>
+      </c>
+      <c r="C582">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>330</v>
+      </c>
+      <c r="B583">
+        <v>1</v>
+      </c>
+      <c r="C583">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>282</v>
+      </c>
+      <c r="B584">
+        <v>1</v>
+      </c>
+      <c r="C584">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>336</v>
+      </c>
+      <c r="B585">
+        <v>1</v>
+      </c>
+      <c r="C585">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>289</v>
+      </c>
+      <c r="B586">
+        <v>1</v>
+      </c>
+      <c r="C586">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>343</v>
+      </c>
+      <c r="B587">
+        <v>1</v>
+      </c>
+      <c r="C587">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/STOK RANK/Rank Dealer/RANK LSP.xlsx
+++ b/STOK RANK/Rank Dealer/RANK LSP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926D01B4-D66C-4D4E-95F8-7E1A8F8C2647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0DD98B-4D33-4249-AC08-DE139962CB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="649">
   <si>
     <t>Sum of Qty</t>
   </si>
@@ -1933,6 +1933,57 @@
   </si>
   <si>
     <t>08P71MCMBLK</t>
+  </si>
+  <si>
+    <t>9410912000</t>
+  </si>
+  <si>
+    <t>9390334380</t>
+  </si>
+  <si>
+    <t>9390334320</t>
+  </si>
+  <si>
+    <t>9390324480</t>
+  </si>
+  <si>
+    <t>9820041000</t>
+  </si>
+  <si>
+    <t>9390325310</t>
+  </si>
+  <si>
+    <t>960010606500</t>
+  </si>
+  <si>
+    <t>957010802507</t>
+  </si>
+  <si>
+    <t>960010602800</t>
+  </si>
+  <si>
+    <t>13111087001</t>
+  </si>
+  <si>
+    <t>90439443740</t>
+  </si>
+  <si>
+    <t>9805957916</t>
+  </si>
+  <si>
+    <t>9454003010</t>
+  </si>
+  <si>
+    <t>91201434003</t>
+  </si>
+  <si>
+    <t>9451116000</t>
+  </si>
+  <si>
+    <t>9820042500</t>
+  </si>
+  <si>
+    <t>9452028000</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +2043,20 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
@@ -2019,10 +2083,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}" name="rankparts" displayName="rankparts" ref="A1:F515" totalsRowShown="0">
   <autoFilter ref="A1:F515" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EC489C37-CEDC-4675-8D70-1D331AA94B51}" name="kode part" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{EC489C37-CEDC-4675-8D70-1D331AA94B51}" name="kode part" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{36D6B850-0C62-4808-8CA4-A3ADDE283157}" name="Sum of Qty"/>
-    <tableColumn id="3" xr3:uid="{6AF7942C-7A8B-42A4-8893-BB3A0B0BA8DB}" name="AVG 12 Bulan" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{6AF7942C-7A8B-42A4-8893-BB3A0B0BA8DB}" name="AVG 12 Bulan" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="2" dataCellStyle="Comma"/>
     <tableColumn id="5" xr3:uid="{47EFE725-CDB5-45AD-BDA0-B6DCB63EE85D}" name="Cont % Akumulasi" dataCellStyle="Percent"/>
     <tableColumn id="6" xr3:uid="{37C8619E-0B0F-4647-86AB-979865F93ADA}" name="Rank"/>
   </tableColumns>
@@ -2034,7 +2098,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E0B0D92-E7B1-4CCD-A8EF-202675C87341}" name="AVG6bulan" displayName="AVG6bulan" ref="A1:C637" totalsRowShown="0">
   <autoFilter ref="A1:C637" xr:uid="{6E0B0D92-E7B1-4CCD-A8EF-202675C87341}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DFADE281-9CFB-4143-A7AE-21AA7EF6CD6C}" name="kode part"/>
+    <tableColumn id="1" xr3:uid="{DFADE281-9CFB-4143-A7AE-21AA7EF6CD6C}" name="kode part" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{22EEB880-7A5B-4ADE-BA60-1CD27BE418FB}" name="Sum 6 Bulan"/>
     <tableColumn id="3" xr3:uid="{B66B00FF-88CF-4D37-AA12-362EE52D1DB1}" name="AVG 6 Bulan"/>
   </tableColumns>
@@ -12682,13 +12746,13 @@
   <dimension ref="A1:C637"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B1" t="s">
@@ -12699,7 +12763,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>448</v>
       </c>
       <c r="B2">
@@ -12710,7 +12774,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>449</v>
       </c>
       <c r="B3">
@@ -12721,7 +12785,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>451</v>
       </c>
       <c r="B4">
@@ -12732,7 +12796,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>450</v>
       </c>
       <c r="B5">
@@ -12743,8 +12807,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>9410912000</v>
+      <c r="A6" s="3" t="s">
+        <v>632</v>
       </c>
       <c r="B6">
         <v>625</v>
@@ -12754,7 +12818,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>474</v>
       </c>
       <c r="B7">
@@ -12765,7 +12829,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>452</v>
       </c>
       <c r="B8">
@@ -12776,7 +12840,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>465</v>
       </c>
       <c r="B9">
@@ -12787,7 +12851,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10">
@@ -12798,7 +12862,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B11">
@@ -12809,7 +12873,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B12">
@@ -12820,7 +12884,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B13">
@@ -12831,7 +12895,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B14">
@@ -12842,7 +12906,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>459</v>
       </c>
       <c r="B15">
@@ -12853,7 +12917,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B16">
@@ -12864,7 +12928,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>456</v>
       </c>
       <c r="B17">
@@ -12875,7 +12939,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>453</v>
       </c>
       <c r="B18">
@@ -12886,7 +12950,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B19">
@@ -12897,7 +12961,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>454</v>
       </c>
       <c r="B20">
@@ -12908,7 +12972,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B21">
@@ -12919,7 +12983,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>458</v>
       </c>
       <c r="B22">
@@ -12930,7 +12994,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B23">
@@ -12941,7 +13005,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B24">
@@ -12952,7 +13016,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>461</v>
       </c>
       <c r="B25">
@@ -12963,7 +13027,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>127</v>
       </c>
       <c r="B26">
@@ -12974,7 +13038,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B27">
@@ -12985,7 +13049,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B28">
@@ -12996,7 +13060,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B29">
@@ -13007,7 +13071,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B30">
@@ -13018,7 +13082,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B31">
@@ -13029,7 +13093,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>455</v>
       </c>
       <c r="B32">
@@ -13040,7 +13104,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>460</v>
       </c>
       <c r="B33">
@@ -13051,7 +13115,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B34">
@@ -13062,7 +13126,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B35">
@@ -13073,7 +13137,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>457</v>
       </c>
       <c r="B36">
@@ -13084,7 +13148,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B37">
@@ -13095,7 +13159,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
         <v>134</v>
       </c>
       <c r="B38">
@@ -13106,7 +13170,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="3" t="s">
         <v>128</v>
       </c>
       <c r="B39">
@@ -13117,7 +13181,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B40">
@@ -13128,7 +13192,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B41">
@@ -13139,7 +13203,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B42">
@@ -13150,7 +13214,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B43">
@@ -13161,7 +13225,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B44">
@@ -13172,7 +13236,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B45">
@@ -13183,7 +13247,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B46">
@@ -13194,7 +13258,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B47">
@@ -13205,7 +13269,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B48">
@@ -13216,7 +13280,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B49">
@@ -13227,7 +13291,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="3" t="s">
         <v>136</v>
       </c>
       <c r="B50">
@@ -13238,7 +13302,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B51">
@@ -13249,7 +13313,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="3" t="s">
         <v>129</v>
       </c>
       <c r="B52">
@@ -13260,7 +13324,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="3" t="s">
         <v>463</v>
       </c>
       <c r="B53">
@@ -13271,7 +13335,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B54">
@@ -13282,7 +13346,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B55">
@@ -13293,7 +13357,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="3" t="s">
         <v>137</v>
       </c>
       <c r="B56">
@@ -13304,7 +13368,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="3" t="s">
         <v>140</v>
       </c>
       <c r="B57">
@@ -13315,7 +13379,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B58">
@@ -13326,7 +13390,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B59">
@@ -13337,7 +13401,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B60">
@@ -13348,7 +13412,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B61">
@@ -13359,7 +13423,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="3" t="s">
         <v>462</v>
       </c>
       <c r="B62">
@@ -13370,7 +13434,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B63">
@@ -13381,7 +13445,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B64">
@@ -13392,7 +13456,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B65">
@@ -13403,7 +13467,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B66">
@@ -13414,7 +13478,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="3" t="s">
         <v>471</v>
       </c>
       <c r="B67">
@@ -13425,7 +13489,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="3" t="s">
         <v>133</v>
       </c>
       <c r="B68">
@@ -13436,7 +13500,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B69">
@@ -13447,7 +13511,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B70">
@@ -13458,7 +13522,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="3" t="s">
         <v>466</v>
       </c>
       <c r="B71">
@@ -13469,7 +13533,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="3" t="s">
         <v>135</v>
       </c>
       <c r="B72">
@@ -13480,7 +13544,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B73">
@@ -13491,7 +13555,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="3" t="s">
         <v>490</v>
       </c>
       <c r="B74">
@@ -13502,7 +13566,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="3" t="s">
         <v>533</v>
       </c>
       <c r="B75">
@@ -13513,7 +13577,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B76">
@@ -13524,7 +13588,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B77">
@@ -13535,7 +13599,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B78">
@@ -13546,7 +13610,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="3" t="s">
         <v>464</v>
       </c>
       <c r="B79">
@@ -13557,7 +13621,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B80">
@@ -13568,7 +13632,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B81">
@@ -13579,7 +13643,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="3" t="s">
         <v>499</v>
       </c>
       <c r="B82">
@@ -13590,7 +13654,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B83">
@@ -13601,7 +13665,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B84">
@@ -13612,7 +13676,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B85">
@@ -13623,7 +13687,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B86">
@@ -13634,7 +13698,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="3" t="s">
         <v>147</v>
       </c>
       <c r="B87">
@@ -13645,7 +13709,7 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="3" t="s">
         <v>156</v>
       </c>
       <c r="B88">
@@ -13656,7 +13720,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="3" t="s">
         <v>157</v>
       </c>
       <c r="B89">
@@ -13667,7 +13731,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" s="3" t="s">
         <v>141</v>
       </c>
       <c r="B90">
@@ -13678,7 +13742,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B91">
@@ -13689,7 +13753,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="A92" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B92">
@@ -13700,7 +13764,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B93">
@@ -13711,7 +13775,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="A94" s="3" t="s">
         <v>503</v>
       </c>
       <c r="B94">
@@ -13722,7 +13786,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="A95" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B95">
@@ -13733,7 +13797,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="A96" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B96">
@@ -13744,7 +13808,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B97">
@@ -13755,7 +13819,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B98">
@@ -13766,7 +13830,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" s="3" t="s">
         <v>144</v>
       </c>
       <c r="B99">
@@ -13777,7 +13841,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B100">
@@ -13788,7 +13852,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" s="3" t="s">
         <v>485</v>
       </c>
       <c r="B101">
@@ -13799,7 +13863,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="A102" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B102">
@@ -13810,7 +13874,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B103">
@@ -13821,7 +13885,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="A104" s="3" t="s">
         <v>514</v>
       </c>
       <c r="B104">
@@ -13832,7 +13896,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="A105" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B105">
@@ -13843,7 +13907,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="A106" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B106">
@@ -13854,7 +13918,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" s="3" t="s">
         <v>152</v>
       </c>
       <c r="B107">
@@ -13865,7 +13929,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="A108" s="3" t="s">
         <v>148</v>
       </c>
       <c r="B108">
@@ -13876,7 +13940,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="A109" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B109">
@@ -13887,7 +13951,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="A110" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B110">
@@ -13898,7 +13962,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="A111" s="3" t="s">
         <v>150</v>
       </c>
       <c r="B111">
@@ -13909,7 +13973,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="A112" s="3" t="s">
         <v>478</v>
       </c>
       <c r="B112">
@@ -13920,7 +13984,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="A113" s="3" t="s">
         <v>494</v>
       </c>
       <c r="B113">
@@ -13931,7 +13995,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="A114" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B114">
@@ -13942,7 +14006,7 @@
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="A115" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B115">
@@ -13953,7 +14017,7 @@
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="A116" s="3" t="s">
         <v>509</v>
       </c>
       <c r="B116">
@@ -13964,7 +14028,7 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="A117" s="3" t="s">
         <v>504</v>
       </c>
       <c r="B117">
@@ -13975,7 +14039,7 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" s="3" t="s">
         <v>437</v>
       </c>
       <c r="B118">
@@ -13986,7 +14050,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="A119" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B119">
@@ -13997,7 +14061,7 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="A120" s="3" t="s">
         <v>181</v>
       </c>
       <c r="B120">
@@ -14008,7 +14072,7 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="3" t="s">
         <v>160</v>
       </c>
       <c r="B121">
@@ -14019,7 +14083,7 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="A122" s="3" t="s">
         <v>401</v>
       </c>
       <c r="B122">
@@ -14030,7 +14094,7 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" s="3" t="s">
         <v>498</v>
       </c>
       <c r="B123">
@@ -14041,7 +14105,7 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B124">
@@ -14052,7 +14116,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" s="3" t="s">
         <v>511</v>
       </c>
       <c r="B125">
@@ -14063,7 +14127,7 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B126">
@@ -14074,7 +14138,7 @@
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" s="3" t="s">
         <v>158</v>
       </c>
       <c r="B127">
@@ -14085,8 +14149,8 @@
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>9390334380</v>
+      <c r="A128" s="3" t="s">
+        <v>633</v>
       </c>
       <c r="B128">
         <v>6</v>
@@ -14096,8 +14160,8 @@
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>9390334320</v>
+      <c r="A129" s="3" t="s">
+        <v>634</v>
       </c>
       <c r="B129">
         <v>6</v>
@@ -14107,7 +14171,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B130">
@@ -14118,7 +14182,7 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="A131" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B131">
@@ -14129,7 +14193,7 @@
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="A132" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B132">
@@ -14140,7 +14204,7 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="A133" s="3" t="s">
         <v>492</v>
       </c>
       <c r="B133">
@@ -14151,7 +14215,7 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="A134" s="3" t="s">
         <v>491</v>
       </c>
       <c r="B134">
@@ -14162,7 +14226,7 @@
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="A135" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B135">
@@ -14173,7 +14237,7 @@
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="A136" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B136">
@@ -14184,8 +14248,8 @@
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>9390324480</v>
+      <c r="A137" s="3" t="s">
+        <v>635</v>
       </c>
       <c r="B137">
         <v>6</v>
@@ -14195,7 +14259,7 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="A138" s="3" t="s">
         <v>217</v>
       </c>
       <c r="B138">
@@ -14206,7 +14270,7 @@
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="A139" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B139">
@@ -14217,7 +14281,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" s="3" t="s">
         <v>483</v>
       </c>
       <c r="B140">
@@ -14228,7 +14292,7 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="A141" s="3" t="s">
         <v>482</v>
       </c>
       <c r="B141">
@@ -14239,7 +14303,7 @@
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A142" s="3" t="s">
         <v>525</v>
       </c>
       <c r="B142">
@@ -14250,7 +14314,7 @@
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="A143" s="3" t="s">
         <v>476</v>
       </c>
       <c r="B143">
@@ -14261,7 +14325,7 @@
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" s="3" t="s">
         <v>229</v>
       </c>
       <c r="B144">
@@ -14272,7 +14336,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" s="3" t="s">
         <v>496</v>
       </c>
       <c r="B145">
@@ -14283,7 +14347,7 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" s="3" t="s">
         <v>161</v>
       </c>
       <c r="B146">
@@ -14294,8 +14358,8 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>9820041000</v>
+      <c r="A147" s="3" t="s">
+        <v>636</v>
       </c>
       <c r="B147">
         <v>5</v>
@@ -14305,7 +14369,7 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" s="3" t="s">
         <v>99</v>
       </c>
       <c r="B148">
@@ -14316,7 +14380,7 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" s="3" t="s">
         <v>535</v>
       </c>
       <c r="B149">
@@ -14327,7 +14391,7 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" s="3" t="s">
         <v>402</v>
       </c>
       <c r="B150">
@@ -14338,7 +14402,7 @@
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" s="3" t="s">
         <v>168</v>
       </c>
       <c r="B151">
@@ -14349,7 +14413,7 @@
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="3" t="s">
         <v>164</v>
       </c>
       <c r="B152">
@@ -14360,7 +14424,7 @@
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B153">
@@ -14371,7 +14435,7 @@
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="A154" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B154">
@@ -14382,7 +14446,7 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="A155" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B155">
@@ -14393,7 +14457,7 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="A156" s="3" t="s">
         <v>470</v>
       </c>
       <c r="B156">
@@ -14404,7 +14468,7 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="A157" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B157">
@@ -14415,7 +14479,7 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="A158" s="3" t="s">
         <v>534</v>
       </c>
       <c r="B158">
@@ -14426,7 +14490,7 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="A159" s="3" t="s">
         <v>488</v>
       </c>
       <c r="B159">
@@ -14437,7 +14501,7 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="A160" s="3" t="s">
         <v>500</v>
       </c>
       <c r="B160">
@@ -14448,7 +14512,7 @@
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="A161" s="3" t="s">
         <v>550</v>
       </c>
       <c r="B161">
@@ -14459,7 +14523,7 @@
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="A162" s="3" t="s">
         <v>507</v>
       </c>
       <c r="B162">
@@ -14470,7 +14534,7 @@
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="A163" s="3" t="s">
         <v>167</v>
       </c>
       <c r="B163">
@@ -14481,7 +14545,7 @@
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="A164" s="3" t="s">
         <v>497</v>
       </c>
       <c r="B164">
@@ -14492,7 +14556,7 @@
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" s="3" t="s">
         <v>119</v>
       </c>
       <c r="B165">
@@ -14503,7 +14567,7 @@
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" s="3" t="s">
         <v>480</v>
       </c>
       <c r="B166">
@@ -14514,7 +14578,7 @@
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B167">
@@ -14525,7 +14589,7 @@
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B168">
@@ -14536,7 +14600,7 @@
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" s="3" t="s">
         <v>495</v>
       </c>
       <c r="B169">
@@ -14547,7 +14611,7 @@
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B170">
@@ -14558,7 +14622,7 @@
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="A171" s="3" t="s">
         <v>122</v>
       </c>
       <c r="B171">
@@ -14569,7 +14633,7 @@
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" s="3" t="s">
         <v>346</v>
       </c>
       <c r="B172">
@@ -14580,7 +14644,7 @@
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B173">
@@ -14591,7 +14655,7 @@
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="A174" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B174">
@@ -14602,7 +14666,7 @@
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="A175" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B175">
@@ -14613,7 +14677,7 @@
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="A176" s="3" t="s">
         <v>501</v>
       </c>
       <c r="B176">
@@ -14624,7 +14688,7 @@
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" s="3" t="s">
         <v>177</v>
       </c>
       <c r="B177">
@@ -14635,7 +14699,7 @@
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="A178" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B178">
@@ -14646,7 +14710,7 @@
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="A179" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B179">
@@ -14657,7 +14721,7 @@
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A180" s="3" t="s">
         <v>486</v>
       </c>
       <c r="B180">
@@ -14668,7 +14732,7 @@
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="A181" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B181">
@@ -14679,7 +14743,7 @@
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="A182" s="3" t="s">
         <v>265</v>
       </c>
       <c r="B182">
@@ -14690,7 +14754,7 @@
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="A183" s="3" t="s">
         <v>163</v>
       </c>
       <c r="B183">
@@ -14701,7 +14765,7 @@
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="A184" s="3" t="s">
         <v>176</v>
       </c>
       <c r="B184">
@@ -14712,7 +14776,7 @@
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="A185" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B185">
@@ -14723,7 +14787,7 @@
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" s="3" t="s">
         <v>516</v>
       </c>
       <c r="B186">
@@ -14734,7 +14798,7 @@
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="A187" s="3" t="s">
         <v>515</v>
       </c>
       <c r="B187">
@@ -14745,7 +14809,7 @@
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="A188" s="3" t="s">
         <v>180</v>
       </c>
       <c r="B188">
@@ -14756,7 +14820,7 @@
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="A189" s="3" t="s">
         <v>179</v>
       </c>
       <c r="B189">
@@ -14767,7 +14831,7 @@
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="A190" s="3" t="s">
         <v>473</v>
       </c>
       <c r="B190">
@@ -14778,7 +14842,7 @@
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="A191" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B191">
@@ -14789,7 +14853,7 @@
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="A192" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B192">
@@ -14800,7 +14864,7 @@
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="A193" s="3" t="s">
         <v>467</v>
       </c>
       <c r="B193">
@@ -14811,7 +14875,7 @@
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="A194" s="3" t="s">
         <v>329</v>
       </c>
       <c r="B194">
@@ -14822,7 +14886,7 @@
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="A195" s="3" t="s">
         <v>313</v>
       </c>
       <c r="B195">
@@ -14833,7 +14897,7 @@
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="A196" s="3" t="s">
         <v>178</v>
       </c>
       <c r="B196">
@@ -14844,7 +14908,7 @@
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="A197" s="3" t="s">
         <v>612</v>
       </c>
       <c r="B197">
@@ -14855,7 +14919,7 @@
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="A198" s="3" t="s">
         <v>165</v>
       </c>
       <c r="B198">
@@ -14866,7 +14930,7 @@
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="A199" s="3" t="s">
         <v>310</v>
       </c>
       <c r="B199">
@@ -14877,7 +14941,7 @@
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="A200" s="3" t="s">
         <v>339</v>
       </c>
       <c r="B200">
@@ -14888,7 +14952,7 @@
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="A201" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B201">
@@ -14899,7 +14963,7 @@
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+      <c r="A202" s="3" t="s">
         <v>107</v>
       </c>
       <c r="B202">
@@ -14910,7 +14974,7 @@
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="A203" s="3" t="s">
         <v>472</v>
       </c>
       <c r="B203">
@@ -14921,7 +14985,7 @@
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="3" t="s">
         <v>551</v>
       </c>
       <c r="B204">
@@ -14932,7 +14996,7 @@
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+      <c r="A205" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B205">
@@ -14943,7 +15007,7 @@
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="A206" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B206">
@@ -14954,7 +15018,7 @@
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+      <c r="A207" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B207">
@@ -14965,8 +15029,8 @@
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208">
-        <v>9390325310</v>
+      <c r="A208" s="3" t="s">
+        <v>637</v>
       </c>
       <c r="B208">
         <v>3</v>
@@ -14976,7 +15040,7 @@
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="A209" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B209">
@@ -14987,7 +15051,7 @@
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+      <c r="A210" s="3" t="s">
         <v>216</v>
       </c>
       <c r="B210">
@@ -14998,7 +15062,7 @@
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+      <c r="A211" s="3" t="s">
         <v>172</v>
       </c>
       <c r="B211">
@@ -15009,7 +15073,7 @@
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+      <c r="A212" s="3" t="s">
         <v>170</v>
       </c>
       <c r="B212">
@@ -15020,7 +15084,7 @@
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="3" t="s">
         <v>251</v>
       </c>
       <c r="B213">
@@ -15031,7 +15095,7 @@
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+      <c r="A214" s="3" t="s">
         <v>539</v>
       </c>
       <c r="B214">
@@ -15042,7 +15106,7 @@
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+      <c r="A215" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B215">
@@ -15053,7 +15117,7 @@
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="A216" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B216">
@@ -15064,7 +15128,7 @@
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+      <c r="A217" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B217">
@@ -15075,7 +15139,7 @@
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="A218" s="3" t="s">
         <v>188</v>
       </c>
       <c r="B218">
@@ -15086,7 +15150,7 @@
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="A219" s="3" t="s">
         <v>125</v>
       </c>
       <c r="B219">
@@ -15097,7 +15161,7 @@
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+      <c r="A220" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B220">
@@ -15108,7 +15172,7 @@
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+      <c r="A221" s="3" t="s">
         <v>519</v>
       </c>
       <c r="B221">
@@ -15119,7 +15183,7 @@
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
+      <c r="A222" s="3" t="s">
         <v>175</v>
       </c>
       <c r="B222">
@@ -15130,7 +15194,7 @@
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+      <c r="A223" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B223">
@@ -15141,7 +15205,7 @@
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+      <c r="A224" s="3" t="s">
         <v>173</v>
       </c>
       <c r="B224">
@@ -15152,7 +15216,7 @@
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="A225" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B225">
@@ -15163,7 +15227,7 @@
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="A226" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B226">
@@ -15174,7 +15238,7 @@
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+      <c r="A227" s="3" t="s">
         <v>190</v>
       </c>
       <c r="B227">
@@ -15185,7 +15249,7 @@
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
+      <c r="A228" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B228">
@@ -15196,7 +15260,7 @@
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+      <c r="A229" s="3" t="s">
         <v>361</v>
       </c>
       <c r="B229">
@@ -15207,7 +15271,7 @@
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
+      <c r="A230" s="3" t="s">
         <v>171</v>
       </c>
       <c r="B230">
@@ -15218,7 +15282,7 @@
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+      <c r="A231" s="3" t="s">
         <v>529</v>
       </c>
       <c r="B231">
@@ -15229,7 +15293,7 @@
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
+      <c r="A232" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B232">
@@ -15240,7 +15304,7 @@
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
+      <c r="A233" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B233">
@@ -15251,7 +15315,7 @@
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
+      <c r="A234" s="3" t="s">
         <v>221</v>
       </c>
       <c r="B234">
@@ -15262,7 +15326,7 @@
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
+      <c r="A235" s="3" t="s">
         <v>487</v>
       </c>
       <c r="B235">
@@ -15273,7 +15337,7 @@
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+      <c r="A236" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B236">
@@ -15284,7 +15348,7 @@
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
+      <c r="A237" s="3" t="s">
         <v>527</v>
       </c>
       <c r="B237">
@@ -15295,7 +15359,7 @@
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
+      <c r="A238" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B238">
@@ -15306,7 +15370,7 @@
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
+      <c r="A239" s="3" t="s">
         <v>233</v>
       </c>
       <c r="B239">
@@ -15317,7 +15381,7 @@
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
+      <c r="A240" s="3" t="s">
         <v>536</v>
       </c>
       <c r="B240">
@@ -15328,7 +15392,7 @@
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
+      <c r="A241" s="3" t="s">
         <v>194</v>
       </c>
       <c r="B241">
@@ -15339,7 +15403,7 @@
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
+      <c r="A242" s="3" t="s">
         <v>403</v>
       </c>
       <c r="B242">
@@ -15350,7 +15414,7 @@
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
+      <c r="A243" s="3" t="s">
         <v>325</v>
       </c>
       <c r="B243">
@@ -15361,7 +15425,7 @@
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
+      <c r="A244" s="3" t="s">
         <v>281</v>
       </c>
       <c r="B244">
@@ -15372,7 +15436,7 @@
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
+      <c r="A245" s="3" t="s">
         <v>506</v>
       </c>
       <c r="B245">
@@ -15383,7 +15447,7 @@
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+      <c r="A246" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B246">
@@ -15394,7 +15458,7 @@
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
+      <c r="A247" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B247">
@@ -15405,7 +15469,7 @@
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+      <c r="A248" s="3" t="s">
         <v>375</v>
       </c>
       <c r="B248">
@@ -15416,7 +15480,7 @@
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
+      <c r="A249" s="3" t="s">
         <v>513</v>
       </c>
       <c r="B249">
@@ -15427,7 +15491,7 @@
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
+      <c r="A250" s="3" t="s">
         <v>230</v>
       </c>
       <c r="B250">
@@ -15438,7 +15502,7 @@
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
+      <c r="A251" s="3" t="s">
         <v>555</v>
       </c>
       <c r="B251">
@@ -15449,7 +15513,7 @@
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
+      <c r="A252" s="3" t="s">
         <v>554</v>
       </c>
       <c r="B252">
@@ -15460,7 +15524,7 @@
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
+      <c r="A253" s="3" t="s">
         <v>469</v>
       </c>
       <c r="B253">
@@ -15471,7 +15535,7 @@
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
+      <c r="A254" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B254">
@@ -15482,7 +15546,7 @@
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
+      <c r="A255" s="3" t="s">
         <v>545</v>
       </c>
       <c r="B255">
@@ -15493,7 +15557,7 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
+      <c r="A256" s="3" t="s">
         <v>226</v>
       </c>
       <c r="B256">
@@ -15504,7 +15568,7 @@
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
+      <c r="A257" s="3" t="s">
         <v>546</v>
       </c>
       <c r="B257">
@@ -15515,7 +15579,7 @@
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
+      <c r="A258" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B258">
@@ -15526,7 +15590,7 @@
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
+      <c r="A259" s="3" t="s">
         <v>408</v>
       </c>
       <c r="B259">
@@ -15537,7 +15601,7 @@
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
+      <c r="A260" s="3" t="s">
         <v>406</v>
       </c>
       <c r="B260">
@@ -15548,7 +15612,7 @@
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
+      <c r="A261" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B261">
@@ -15559,7 +15623,7 @@
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
+      <c r="A262" s="3" t="s">
         <v>552</v>
       </c>
       <c r="B262">
@@ -15570,7 +15634,7 @@
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
+      <c r="A263" s="3" t="s">
         <v>530</v>
       </c>
       <c r="B263">
@@ -15581,7 +15645,7 @@
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
+      <c r="A264" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B264">
@@ -15592,7 +15656,7 @@
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
+      <c r="A265" s="3" t="s">
         <v>409</v>
       </c>
       <c r="B265">
@@ -15603,7 +15667,7 @@
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
+      <c r="A266" s="3" t="s">
         <v>557</v>
       </c>
       <c r="B266">
@@ -15614,7 +15678,7 @@
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
+      <c r="A267" s="3" t="s">
         <v>537</v>
       </c>
       <c r="B267">
@@ -15625,7 +15689,7 @@
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
+      <c r="A268" s="3" t="s">
         <v>553</v>
       </c>
       <c r="B268">
@@ -15636,7 +15700,7 @@
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
+      <c r="A269" s="3" t="s">
         <v>210</v>
       </c>
       <c r="B269">
@@ -15647,7 +15711,7 @@
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
+      <c r="A270" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B270">
@@ -15658,7 +15722,7 @@
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
+      <c r="A271" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B271">
@@ -15669,7 +15733,7 @@
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
+      <c r="A272" s="3" t="s">
         <v>556</v>
       </c>
       <c r="B272">
@@ -15680,7 +15744,7 @@
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
+      <c r="A273" s="3" t="s">
         <v>198</v>
       </c>
       <c r="B273">
@@ -15691,7 +15755,7 @@
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
+      <c r="A274" s="3" t="s">
         <v>227</v>
       </c>
       <c r="B274">
@@ -15702,7 +15766,7 @@
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
+      <c r="A275" s="3" t="s">
         <v>225</v>
       </c>
       <c r="B275">
@@ -15713,7 +15777,7 @@
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
+      <c r="A276" s="3" t="s">
         <v>231</v>
       </c>
       <c r="B276">
@@ -15724,7 +15788,7 @@
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
+      <c r="A277" s="3" t="s">
         <v>538</v>
       </c>
       <c r="B277">
@@ -15735,7 +15799,7 @@
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
+      <c r="A278" s="3" t="s">
         <v>208</v>
       </c>
       <c r="B278">
@@ -15746,7 +15810,7 @@
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
+      <c r="A279" s="3" t="s">
         <v>558</v>
       </c>
       <c r="B279">
@@ -15757,7 +15821,7 @@
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
+      <c r="A280" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B280">
@@ -15768,7 +15832,7 @@
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
+      <c r="A281" s="3" t="s">
         <v>493</v>
       </c>
       <c r="B281">
@@ -15779,7 +15843,7 @@
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
+      <c r="A282" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B282">
@@ -15790,7 +15854,7 @@
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+      <c r="A283" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B283">
@@ -15801,7 +15865,7 @@
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
+      <c r="A284" s="3" t="s">
         <v>442</v>
       </c>
       <c r="B284">
@@ -15812,7 +15876,7 @@
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
+      <c r="A285" s="3" t="s">
         <v>531</v>
       </c>
       <c r="B285">
@@ -15823,7 +15887,7 @@
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
+      <c r="A286" s="3" t="s">
         <v>191</v>
       </c>
       <c r="B286">
@@ -15834,7 +15898,7 @@
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
+      <c r="A287" s="3" t="s">
         <v>522</v>
       </c>
       <c r="B287">
@@ -15845,7 +15909,7 @@
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
+      <c r="A288" s="3" t="s">
         <v>407</v>
       </c>
       <c r="B288">
@@ -15856,7 +15920,7 @@
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
+      <c r="A289" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B289">
@@ -15867,7 +15931,7 @@
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
+      <c r="A290" s="3" t="s">
         <v>200</v>
       </c>
       <c r="B290">
@@ -15878,7 +15942,7 @@
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
+      <c r="A291" s="3" t="s">
         <v>613</v>
       </c>
       <c r="B291">
@@ -15889,7 +15953,7 @@
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
+      <c r="A292" s="3" t="s">
         <v>174</v>
       </c>
       <c r="B292">
@@ -15900,7 +15964,7 @@
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
+      <c r="A293" s="3" t="s">
         <v>532</v>
       </c>
       <c r="B293">
@@ -15911,7 +15975,7 @@
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
+      <c r="A294" s="3" t="s">
         <v>159</v>
       </c>
       <c r="B294">
@@ -15922,7 +15986,7 @@
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
+      <c r="A295" s="3" t="s">
         <v>304</v>
       </c>
       <c r="B295">
@@ -15933,7 +15997,7 @@
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
+      <c r="A296" s="3" t="s">
         <v>236</v>
       </c>
       <c r="B296">
@@ -15944,7 +16008,7 @@
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
+      <c r="A297" s="3" t="s">
         <v>559</v>
       </c>
       <c r="B297">
@@ -15955,7 +16019,7 @@
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
+      <c r="A298" s="3" t="s">
         <v>182</v>
       </c>
       <c r="B298">
@@ -15966,7 +16030,7 @@
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
+      <c r="A299" s="3" t="s">
         <v>427</v>
       </c>
       <c r="B299">
@@ -15977,7 +16041,7 @@
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
+      <c r="A300" s="3" t="s">
         <v>309</v>
       </c>
       <c r="B300">
@@ -15988,7 +16052,7 @@
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
+      <c r="A301" s="3" t="s">
         <v>370</v>
       </c>
       <c r="B301">
@@ -15999,7 +16063,7 @@
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
+      <c r="A302" s="3" t="s">
         <v>166</v>
       </c>
       <c r="B302">
@@ -16010,7 +16074,7 @@
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
+      <c r="A303" s="3" t="s">
         <v>479</v>
       </c>
       <c r="B303">
@@ -16021,7 +16085,7 @@
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
+      <c r="A304" s="3" t="s">
         <v>204</v>
       </c>
       <c r="B304">
@@ -16032,7 +16096,7 @@
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
+      <c r="A305" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B305">
@@ -16043,7 +16107,7 @@
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
+      <c r="A306" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B306">
@@ -16054,7 +16118,7 @@
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
+      <c r="A307" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B307">
@@ -16065,7 +16129,7 @@
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
+      <c r="A308" s="3" t="s">
         <v>224</v>
       </c>
       <c r="B308">
@@ -16076,7 +16140,7 @@
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
+      <c r="A309" s="3" t="s">
         <v>154</v>
       </c>
       <c r="B309">
@@ -16087,7 +16151,7 @@
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
+      <c r="A310" s="3" t="s">
         <v>232</v>
       </c>
       <c r="B310">
@@ -16098,7 +16162,7 @@
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
+      <c r="A311" s="3" t="s">
         <v>443</v>
       </c>
       <c r="B311">
@@ -16109,8 +16173,8 @@
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312">
-        <v>960010606500</v>
+      <c r="A312" s="3" t="s">
+        <v>638</v>
       </c>
       <c r="B312">
         <v>2</v>
@@ -16120,7 +16184,7 @@
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
+      <c r="A313" s="3" t="s">
         <v>228</v>
       </c>
       <c r="B313">
@@ -16131,7 +16195,7 @@
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
+      <c r="A314" s="3" t="s">
         <v>520</v>
       </c>
       <c r="B314">
@@ -16142,7 +16206,7 @@
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
+      <c r="A315" s="3" t="s">
         <v>114</v>
       </c>
       <c r="B315">
@@ -16153,7 +16217,7 @@
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
+      <c r="A316" s="3" t="s">
         <v>238</v>
       </c>
       <c r="B316">
@@ -16164,7 +16228,7 @@
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
+      <c r="A317" s="3" t="s">
         <v>404</v>
       </c>
       <c r="B317">
@@ -16175,7 +16239,7 @@
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
+      <c r="A318" s="3" t="s">
         <v>222</v>
       </c>
       <c r="B318">
@@ -16186,7 +16250,7 @@
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
+      <c r="A319" s="3" t="s">
         <v>183</v>
       </c>
       <c r="B319">
@@ -16197,7 +16261,7 @@
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
+      <c r="A320" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B320">
@@ -16208,7 +16272,7 @@
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
+      <c r="A321" s="3" t="s">
         <v>195</v>
       </c>
       <c r="B321">
@@ -16219,7 +16283,7 @@
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
+      <c r="A322" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B322">
@@ -16230,7 +16294,7 @@
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
+      <c r="A323" s="3" t="s">
         <v>184</v>
       </c>
       <c r="B323">
@@ -16241,7 +16305,7 @@
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
+      <c r="A324" s="3" t="s">
         <v>405</v>
       </c>
       <c r="B324">
@@ -16252,7 +16316,7 @@
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
+      <c r="A325" s="3" t="s">
         <v>524</v>
       </c>
       <c r="B325">
@@ -16263,7 +16327,7 @@
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
+      <c r="A326" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B326">
@@ -16274,7 +16338,7 @@
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
+      <c r="A327" s="3" t="s">
         <v>193</v>
       </c>
       <c r="B327">
@@ -16285,7 +16349,7 @@
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
+      <c r="A328" s="3" t="s">
         <v>502</v>
       </c>
       <c r="B328">
@@ -16296,7 +16360,7 @@
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
+      <c r="A329" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B329">
@@ -16307,7 +16371,7 @@
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
+      <c r="A330" s="3" t="s">
         <v>202</v>
       </c>
       <c r="B330">
@@ -16318,7 +16382,7 @@
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
+      <c r="A331" s="3" t="s">
         <v>614</v>
       </c>
       <c r="B331">
@@ -16329,7 +16393,7 @@
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
+      <c r="A332" s="3" t="s">
         <v>355</v>
       </c>
       <c r="B332">
@@ -16340,7 +16404,7 @@
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
+      <c r="A333" s="3" t="s">
         <v>615</v>
       </c>
       <c r="B333">
@@ -16351,7 +16415,7 @@
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
+      <c r="A334" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B334">
@@ -16362,7 +16426,7 @@
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
+      <c r="A335" s="3" t="s">
         <v>468</v>
       </c>
       <c r="B335">
@@ -16373,7 +16437,7 @@
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
+      <c r="A336" s="3" t="s">
         <v>378</v>
       </c>
       <c r="B336">
@@ -16384,7 +16448,7 @@
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
+      <c r="A337" s="3" t="s">
         <v>376</v>
       </c>
       <c r="B337">
@@ -16395,7 +16459,7 @@
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
+      <c r="A338" s="3" t="s">
         <v>426</v>
       </c>
       <c r="B338">
@@ -16406,7 +16470,7 @@
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
+      <c r="A339" s="3" t="s">
         <v>305</v>
       </c>
       <c r="B339">
@@ -16417,7 +16481,7 @@
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
+      <c r="A340" s="3" t="s">
         <v>380</v>
       </c>
       <c r="B340">
@@ -16428,7 +16492,7 @@
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
+      <c r="A341" s="3" t="s">
         <v>270</v>
       </c>
       <c r="B341">
@@ -16439,7 +16503,7 @@
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
+      <c r="A342" s="3" t="s">
         <v>252</v>
       </c>
       <c r="B342">
@@ -16450,7 +16514,7 @@
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
+      <c r="A343" s="3" t="s">
         <v>328</v>
       </c>
       <c r="B343">
@@ -16461,7 +16525,7 @@
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
+      <c r="A344" s="3" t="s">
         <v>577</v>
       </c>
       <c r="B344">
@@ -16472,7 +16536,7 @@
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
+      <c r="A345" s="3" t="s">
         <v>372</v>
       </c>
       <c r="B345">
@@ -16483,7 +16547,7 @@
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
+      <c r="A346" s="3" t="s">
         <v>433</v>
       </c>
       <c r="B346">
@@ -16494,7 +16558,7 @@
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
+      <c r="A347" s="3" t="s">
         <v>585</v>
       </c>
       <c r="B347">
@@ -16505,7 +16569,7 @@
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
+      <c r="A348" s="3" t="s">
         <v>517</v>
       </c>
       <c r="B348">
@@ -16516,8 +16580,8 @@
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349">
-        <v>957010802507</v>
+      <c r="A349" s="3" t="s">
+        <v>639</v>
       </c>
       <c r="B349">
         <v>1</v>
@@ -16527,7 +16591,7 @@
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
+      <c r="A350" s="3" t="s">
         <v>579</v>
       </c>
       <c r="B350">
@@ -16538,7 +16602,7 @@
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
+      <c r="A351" s="3" t="s">
         <v>306</v>
       </c>
       <c r="B351">
@@ -16549,7 +16613,7 @@
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
+      <c r="A352" s="3" t="s">
         <v>428</v>
       </c>
       <c r="B352">
@@ -16560,7 +16624,7 @@
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
+      <c r="A353" s="3" t="s">
         <v>358</v>
       </c>
       <c r="B353">
@@ -16571,7 +16635,7 @@
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
+      <c r="A354" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B354">
@@ -16582,7 +16646,7 @@
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
+      <c r="A355" s="3" t="s">
         <v>393</v>
       </c>
       <c r="B355">
@@ -16593,7 +16657,7 @@
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
+      <c r="A356" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B356">
@@ -16604,7 +16668,7 @@
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
+      <c r="A357" s="3" t="s">
         <v>365</v>
       </c>
       <c r="B357">
@@ -16615,7 +16679,7 @@
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
+      <c r="A358" s="3" t="s">
         <v>287</v>
       </c>
       <c r="B358">
@@ -16626,7 +16690,7 @@
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
+      <c r="A359" s="3" t="s">
         <v>505</v>
       </c>
       <c r="B359">
@@ -16637,7 +16701,7 @@
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A360" t="s">
+      <c r="A360" s="3" t="s">
         <v>347</v>
       </c>
       <c r="B360">
@@ -16648,7 +16712,7 @@
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
+      <c r="A361" s="3" t="s">
         <v>616</v>
       </c>
       <c r="B361">
@@ -16659,7 +16723,7 @@
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
+      <c r="A362" s="3" t="s">
         <v>581</v>
       </c>
       <c r="B362">
@@ -16670,7 +16734,7 @@
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A363" t="s">
+      <c r="A363" s="3" t="s">
         <v>412</v>
       </c>
       <c r="B363">
@@ -16681,7 +16745,7 @@
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
+      <c r="A364" s="3" t="s">
         <v>583</v>
       </c>
       <c r="B364">
@@ -16692,7 +16756,7 @@
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
+      <c r="A365" s="3" t="s">
         <v>335</v>
       </c>
       <c r="B365">
@@ -16703,7 +16767,7 @@
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
+      <c r="A366" s="3" t="s">
         <v>288</v>
       </c>
       <c r="B366">
@@ -16714,7 +16778,7 @@
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
+      <c r="A367" s="3" t="s">
         <v>586</v>
       </c>
       <c r="B367">
@@ -16725,7 +16789,7 @@
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
+      <c r="A368" s="3" t="s">
         <v>617</v>
       </c>
       <c r="B368">
@@ -16736,7 +16800,7 @@
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
+      <c r="A369" s="3" t="s">
         <v>561</v>
       </c>
       <c r="B369">
@@ -16747,7 +16811,7 @@
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
+      <c r="A370" s="3" t="s">
         <v>565</v>
       </c>
       <c r="B370">
@@ -16758,7 +16822,7 @@
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
+      <c r="A371" s="3" t="s">
         <v>590</v>
       </c>
       <c r="B371">
@@ -16769,7 +16833,7 @@
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A372" t="s">
+      <c r="A372" s="3" t="s">
         <v>566</v>
       </c>
       <c r="B372">
@@ -16780,7 +16844,7 @@
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
+      <c r="A373" s="3" t="s">
         <v>263</v>
       </c>
       <c r="B373">
@@ -16791,7 +16855,7 @@
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
+      <c r="A374" s="3" t="s">
         <v>567</v>
       </c>
       <c r="B374">
@@ -16802,7 +16866,7 @@
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
+      <c r="A375" s="3" t="s">
         <v>618</v>
       </c>
       <c r="B375">
@@ -16813,7 +16877,7 @@
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A376" t="s">
+      <c r="A376" s="3" t="s">
         <v>518</v>
       </c>
       <c r="B376">
@@ -16824,7 +16888,7 @@
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
+      <c r="A377" s="3" t="s">
         <v>389</v>
       </c>
       <c r="B377">
@@ -16835,7 +16899,7 @@
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A378" t="s">
+      <c r="A378" s="3" t="s">
         <v>541</v>
       </c>
       <c r="B378">
@@ -16846,7 +16910,7 @@
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
+      <c r="A379" s="3" t="s">
         <v>243</v>
       </c>
       <c r="B379">
@@ -16857,7 +16921,7 @@
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A380" t="s">
+      <c r="A380" s="3" t="s">
         <v>327</v>
       </c>
       <c r="B380">
@@ -16868,7 +16932,7 @@
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A381" t="s">
+      <c r="A381" s="3" t="s">
         <v>364</v>
       </c>
       <c r="B381">
@@ -16879,7 +16943,7 @@
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
+      <c r="A382" s="3" t="s">
         <v>334</v>
       </c>
       <c r="B382">
@@ -16890,7 +16954,7 @@
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
+      <c r="A383" s="3" t="s">
         <v>321</v>
       </c>
       <c r="B383">
@@ -16901,7 +16965,7 @@
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
+      <c r="A384" s="3" t="s">
         <v>255</v>
       </c>
       <c r="B384">
@@ -16912,7 +16976,7 @@
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
+      <c r="A385" s="3" t="s">
         <v>429</v>
       </c>
       <c r="B385">
@@ -16923,7 +16987,7 @@
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
+      <c r="A386" s="3" t="s">
         <v>435</v>
       </c>
       <c r="B386">
@@ -16934,7 +16998,7 @@
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
+      <c r="A387" s="3" t="s">
         <v>512</v>
       </c>
       <c r="B387">
@@ -16945,7 +17009,7 @@
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
+      <c r="A388" s="3" t="s">
         <v>291</v>
       </c>
       <c r="B388">
@@ -16956,7 +17020,7 @@
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
+      <c r="A389" s="3" t="s">
         <v>619</v>
       </c>
       <c r="B389">
@@ -16967,7 +17031,7 @@
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
+      <c r="A390" s="3" t="s">
         <v>411</v>
       </c>
       <c r="B390">
@@ -16978,7 +17042,7 @@
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A391" t="s">
+      <c r="A391" s="3" t="s">
         <v>367</v>
       </c>
       <c r="B391">
@@ -16989,7 +17053,7 @@
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
+      <c r="A392" s="3" t="s">
         <v>431</v>
       </c>
       <c r="B392">
@@ -17000,7 +17064,7 @@
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
+      <c r="A393" s="3" t="s">
         <v>620</v>
       </c>
       <c r="B393">
@@ -17011,7 +17075,7 @@
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
+      <c r="A394" s="3" t="s">
         <v>356</v>
       </c>
       <c r="B394">
@@ -17022,7 +17086,7 @@
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A395" t="s">
+      <c r="A395" s="3" t="s">
         <v>369</v>
       </c>
       <c r="B395">
@@ -17033,7 +17097,7 @@
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
+      <c r="A396" s="3" t="s">
         <v>240</v>
       </c>
       <c r="B396">
@@ -17044,7 +17108,7 @@
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A397" t="s">
+      <c r="A397" s="3" t="s">
         <v>621</v>
       </c>
       <c r="B397">
@@ -17055,7 +17119,7 @@
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
+      <c r="A398" s="3" t="s">
         <v>357</v>
       </c>
       <c r="B398">
@@ -17066,7 +17130,7 @@
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A399" t="s">
+      <c r="A399" s="3" t="s">
         <v>239</v>
       </c>
       <c r="B399">
@@ -17077,7 +17141,7 @@
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
+      <c r="A400" s="3" t="s">
         <v>293</v>
       </c>
       <c r="B400">
@@ -17088,7 +17152,7 @@
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401" t="s">
+      <c r="A401" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B401">
@@ -17099,7 +17163,7 @@
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
+      <c r="A402" s="3" t="s">
         <v>359</v>
       </c>
       <c r="B402">
@@ -17110,7 +17174,7 @@
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
+      <c r="A403" s="3" t="s">
         <v>578</v>
       </c>
       <c r="B403">
@@ -17121,7 +17185,7 @@
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
+      <c r="A404" s="3" t="s">
         <v>562</v>
       </c>
       <c r="B404">
@@ -17132,7 +17196,7 @@
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A405" t="s">
+      <c r="A405" s="3" t="s">
         <v>445</v>
       </c>
       <c r="B405">
@@ -17143,7 +17207,7 @@
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
+      <c r="A406" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B406">
@@ -17154,7 +17218,7 @@
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
+      <c r="A407" s="3" t="s">
         <v>587</v>
       </c>
       <c r="B407">
@@ -17165,7 +17229,7 @@
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408" t="s">
+      <c r="A408" s="3" t="s">
         <v>544</v>
       </c>
       <c r="B408">
@@ -17176,7 +17240,7 @@
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A409" t="s">
+      <c r="A409" s="3" t="s">
         <v>622</v>
       </c>
       <c r="B409">
@@ -17187,7 +17251,7 @@
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
+      <c r="A410" s="3" t="s">
         <v>436</v>
       </c>
       <c r="B410">
@@ -17198,7 +17262,7 @@
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" t="s">
+      <c r="A411" s="3" t="s">
         <v>573</v>
       </c>
       <c r="B411">
@@ -17209,7 +17273,7 @@
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
+      <c r="A412" s="3" t="s">
         <v>336</v>
       </c>
       <c r="B412">
@@ -17220,8 +17284,8 @@
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413">
-        <v>960010602800</v>
+      <c r="A413" s="3" t="s">
+        <v>640</v>
       </c>
       <c r="B413">
         <v>1</v>
@@ -17231,7 +17295,7 @@
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
+      <c r="A414" s="3" t="s">
         <v>508</v>
       </c>
       <c r="B414">
@@ -17242,7 +17306,7 @@
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
+      <c r="A415" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B415">
@@ -17253,7 +17317,7 @@
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
+      <c r="A416" s="3" t="s">
         <v>481</v>
       </c>
       <c r="B416">
@@ -17264,7 +17328,7 @@
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
+      <c r="A417" s="3" t="s">
         <v>383</v>
       </c>
       <c r="B417">
@@ -17275,7 +17339,7 @@
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
+      <c r="A418" s="3" t="s">
         <v>223</v>
       </c>
       <c r="B418">
@@ -17286,7 +17350,7 @@
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
+      <c r="A419" s="3" t="s">
         <v>384</v>
       </c>
       <c r="B419">
@@ -17297,7 +17361,7 @@
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
+      <c r="A420" s="3" t="s">
         <v>510</v>
       </c>
       <c r="B420">
@@ -17308,7 +17372,7 @@
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
+      <c r="A421" s="3" t="s">
         <v>398</v>
       </c>
       <c r="B421">
@@ -17319,7 +17383,7 @@
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
+      <c r="A422" s="3" t="s">
         <v>582</v>
       </c>
       <c r="B422">
@@ -17330,7 +17394,7 @@
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
+      <c r="A423" s="3" t="s">
         <v>569</v>
       </c>
       <c r="B423">
@@ -17341,7 +17405,7 @@
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A424" t="s">
+      <c r="A424" s="3" t="s">
         <v>489</v>
       </c>
       <c r="B424">
@@ -17352,7 +17416,7 @@
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A425" t="s">
+      <c r="A425" s="3" t="s">
         <v>307</v>
       </c>
       <c r="B425">
@@ -17363,7 +17427,7 @@
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
+      <c r="A426" s="3" t="s">
         <v>388</v>
       </c>
       <c r="B426">
@@ -17374,7 +17438,7 @@
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A427" t="s">
+      <c r="A427" s="3" t="s">
         <v>574</v>
       </c>
       <c r="B427">
@@ -17385,7 +17449,7 @@
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A428" t="s">
+      <c r="A428" s="3" t="s">
         <v>423</v>
       </c>
       <c r="B428">
@@ -17396,7 +17460,7 @@
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
+      <c r="A429" s="3" t="s">
         <v>360</v>
       </c>
       <c r="B429">
@@ -17407,7 +17471,7 @@
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
+      <c r="A430" s="3" t="s">
         <v>568</v>
       </c>
       <c r="B430">
@@ -17418,7 +17482,7 @@
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
+      <c r="A431" s="3" t="s">
         <v>570</v>
       </c>
       <c r="B431">
@@ -17429,7 +17493,7 @@
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A432" t="s">
+      <c r="A432" s="3" t="s">
         <v>439</v>
       </c>
       <c r="B432">
@@ -17440,7 +17504,7 @@
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
+      <c r="A433" s="3" t="s">
         <v>362</v>
       </c>
       <c r="B433">
@@ -17451,7 +17515,7 @@
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
+      <c r="A434" s="3" t="s">
         <v>475</v>
       </c>
       <c r="B434">
@@ -17462,7 +17526,7 @@
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
+      <c r="A435" s="3" t="s">
         <v>571</v>
       </c>
       <c r="B435">
@@ -17473,7 +17537,7 @@
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
+      <c r="A436" s="3" t="s">
         <v>440</v>
       </c>
       <c r="B436">
@@ -17484,7 +17548,7 @@
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A437" t="s">
+      <c r="A437" s="3" t="s">
         <v>272</v>
       </c>
       <c r="B437">
@@ -17495,7 +17559,7 @@
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
+      <c r="A438" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B438">
@@ -17506,7 +17570,7 @@
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
+      <c r="A439" s="3" t="s">
         <v>274</v>
       </c>
       <c r="B439">
@@ -17517,7 +17581,7 @@
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
+      <c r="A440" s="3" t="s">
         <v>528</v>
       </c>
       <c r="B440">
@@ -17528,7 +17592,7 @@
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A441" t="s">
+      <c r="A441" s="3" t="s">
         <v>324</v>
       </c>
       <c r="B441">
@@ -17539,7 +17603,7 @@
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A442" t="s">
+      <c r="A442" s="3" t="s">
         <v>342</v>
       </c>
       <c r="B442">
@@ -17550,7 +17614,7 @@
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
+      <c r="A443" s="3" t="s">
         <v>430</v>
       </c>
       <c r="B443">
@@ -17561,7 +17625,7 @@
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A444" t="s">
+      <c r="A444" s="3" t="s">
         <v>234</v>
       </c>
       <c r="B444">
@@ -17572,7 +17636,7 @@
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
+      <c r="A445" s="3" t="s">
         <v>623</v>
       </c>
       <c r="B445">
@@ -17583,7 +17647,7 @@
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A446" t="s">
+      <c r="A446" s="3" t="s">
         <v>432</v>
       </c>
       <c r="B446">
@@ -17594,7 +17658,7 @@
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
+      <c r="A447" s="3" t="s">
         <v>276</v>
       </c>
       <c r="B447">
@@ -17605,7 +17669,7 @@
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
+      <c r="A448" s="3" t="s">
         <v>296</v>
       </c>
       <c r="B448">
@@ -17616,7 +17680,7 @@
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A449" t="s">
+      <c r="A449" s="3" t="s">
         <v>563</v>
       </c>
       <c r="B449">
@@ -17627,7 +17691,7 @@
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A450" t="s">
+      <c r="A450" s="3" t="s">
         <v>543</v>
       </c>
       <c r="B450">
@@ -17638,7 +17702,7 @@
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A451" t="s">
+      <c r="A451" s="3" t="s">
         <v>564</v>
       </c>
       <c r="B451">
@@ -17649,7 +17713,7 @@
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
+      <c r="A452" s="3" t="s">
         <v>434</v>
       </c>
       <c r="B452">
@@ -17660,7 +17724,7 @@
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A453" t="s">
+      <c r="A453" s="3" t="s">
         <v>278</v>
       </c>
       <c r="B453">
@@ -17671,7 +17735,7 @@
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
+      <c r="A454" s="3" t="s">
         <v>576</v>
       </c>
       <c r="B454">
@@ -17682,7 +17746,7 @@
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
+      <c r="A455" s="3" t="s">
         <v>624</v>
       </c>
       <c r="B455">
@@ -17693,7 +17757,7 @@
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
+      <c r="A456" s="3" t="s">
         <v>343</v>
       </c>
       <c r="B456">
@@ -17704,7 +17768,7 @@
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A457" t="s">
+      <c r="A457" s="3" t="s">
         <v>625</v>
       </c>
       <c r="B457">
@@ -17715,7 +17779,7 @@
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
+      <c r="A458" s="3" t="s">
         <v>344</v>
       </c>
       <c r="B458">
@@ -17726,7 +17790,7 @@
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A459" t="s">
+      <c r="A459" s="3" t="s">
         <v>591</v>
       </c>
       <c r="B459">
@@ -17737,7 +17801,7 @@
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
+      <c r="A460" s="3" t="s">
         <v>345</v>
       </c>
       <c r="B460">
@@ -17748,7 +17812,7 @@
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
+      <c r="A461" s="3" t="s">
         <v>248</v>
       </c>
       <c r="B461">
@@ -17759,7 +17823,7 @@
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
+      <c r="A462" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B462">
@@ -17770,7 +17834,7 @@
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A463" t="s">
+      <c r="A463" s="3" t="s">
         <v>371</v>
       </c>
       <c r="B463">
@@ -17781,7 +17845,7 @@
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A464" t="s">
+      <c r="A464" s="3" t="s">
         <v>316</v>
       </c>
       <c r="B464">
@@ -17792,7 +17856,7 @@
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A465" t="s">
+      <c r="A465" s="3" t="s">
         <v>526</v>
       </c>
       <c r="B465">
@@ -17803,7 +17867,7 @@
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466" t="s">
+      <c r="A466" s="3" t="s">
         <v>424</v>
       </c>
       <c r="B466">
@@ -17814,7 +17878,7 @@
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
+      <c r="A467" s="3" t="s">
         <v>280</v>
       </c>
       <c r="B467">
@@ -17825,7 +17889,7 @@
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" t="s">
+      <c r="A468" s="3" t="s">
         <v>391</v>
       </c>
       <c r="B468">
@@ -17836,7 +17900,7 @@
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A469" t="s">
+      <c r="A469" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B469">
@@ -17847,7 +17911,7 @@
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
+      <c r="A470" s="3" t="s">
         <v>368</v>
       </c>
       <c r="B470">
@@ -17858,7 +17922,7 @@
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A471" t="s">
+      <c r="A471" s="3" t="s">
         <v>374</v>
       </c>
       <c r="B471">
@@ -17869,7 +17933,7 @@
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A472" t="s">
+      <c r="A472" s="3" t="s">
         <v>392</v>
       </c>
       <c r="B472">
@@ -17880,7 +17944,7 @@
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A473" t="s">
+      <c r="A473" s="3" t="s">
         <v>196</v>
       </c>
       <c r="B473">
@@ -17891,7 +17955,7 @@
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A474" t="s">
+      <c r="A474" s="3" t="s">
         <v>394</v>
       </c>
       <c r="B474">
@@ -17902,7 +17966,7 @@
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A475" t="s">
+      <c r="A475" s="3" t="s">
         <v>547</v>
       </c>
       <c r="B475">
@@ -17913,7 +17977,7 @@
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A476" t="s">
+      <c r="A476" s="3" t="s">
         <v>441</v>
       </c>
       <c r="B476">
@@ -17924,7 +17988,7 @@
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A477" t="s">
+      <c r="A477" s="3" t="s">
         <v>283</v>
       </c>
       <c r="B477">
@@ -17935,7 +17999,7 @@
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A478" t="s">
+      <c r="A478" s="3" t="s">
         <v>580</v>
       </c>
       <c r="B478">
@@ -17946,7 +18010,7 @@
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A479" t="s">
+      <c r="A479" s="3" t="s">
         <v>444</v>
       </c>
       <c r="B479">
@@ -17957,7 +18021,7 @@
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A480" t="s">
+      <c r="A480" s="3" t="s">
         <v>584</v>
       </c>
       <c r="B480">
@@ -17968,7 +18032,7 @@
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A481" t="s">
+      <c r="A481" s="3" t="s">
         <v>413</v>
       </c>
       <c r="B481">
@@ -17979,7 +18043,7 @@
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A482" t="s">
+      <c r="A482" s="3" t="s">
         <v>396</v>
       </c>
       <c r="B482">
@@ -17990,7 +18054,7 @@
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A483" t="s">
+      <c r="A483" s="3" t="s">
         <v>414</v>
       </c>
       <c r="B483">
@@ -18001,7 +18065,7 @@
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
+      <c r="A484" s="3" t="s">
         <v>301</v>
       </c>
       <c r="B484">
@@ -18012,7 +18076,7 @@
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A485" t="s">
+      <c r="A485" s="3" t="s">
         <v>572</v>
       </c>
       <c r="B485">
@@ -18023,7 +18087,7 @@
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
+      <c r="A486" s="3" t="s">
         <v>438</v>
       </c>
       <c r="B486">
@@ -18034,7 +18098,7 @@
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A487" t="s">
+      <c r="A487" s="3" t="s">
         <v>626</v>
       </c>
       <c r="B487">
@@ -18045,7 +18109,7 @@
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
+      <c r="A488" s="3" t="s">
         <v>397</v>
       </c>
       <c r="B488">
@@ -18056,7 +18120,7 @@
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
+      <c r="A489" s="3" t="s">
         <v>627</v>
       </c>
       <c r="B489">
@@ -18067,7 +18131,7 @@
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
+      <c r="A490" s="3" t="s">
         <v>261</v>
       </c>
       <c r="B490">
@@ -18078,7 +18142,7 @@
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
+      <c r="A491" s="3" t="s">
         <v>628</v>
       </c>
       <c r="B491">
@@ -18089,7 +18153,7 @@
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
+      <c r="A492" s="3" t="s">
         <v>425</v>
       </c>
       <c r="B492">
@@ -18100,7 +18164,7 @@
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
+      <c r="A493" s="3" t="s">
         <v>588</v>
       </c>
       <c r="B493">
@@ -18111,7 +18175,7 @@
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
+      <c r="A494" s="3" t="s">
         <v>331</v>
       </c>
       <c r="B494">
@@ -18122,7 +18186,7 @@
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
+      <c r="A495" s="3" t="s">
         <v>589</v>
       </c>
       <c r="B495">
@@ -18133,7 +18197,7 @@
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
+      <c r="A496" s="3" t="s">
         <v>303</v>
       </c>
       <c r="B496">
@@ -18144,7 +18208,7 @@
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
+      <c r="A497" s="3" t="s">
         <v>629</v>
       </c>
       <c r="B497">
@@ -18155,7 +18219,7 @@
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
+      <c r="A498" s="3" t="s">
         <v>379</v>
       </c>
       <c r="B498">
@@ -18166,7 +18230,7 @@
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
+      <c r="A499" s="3" t="s">
         <v>575</v>
       </c>
       <c r="B499">
@@ -18177,7 +18241,7 @@
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
+      <c r="A500" s="3" t="s">
         <v>560</v>
       </c>
       <c r="B500">
@@ -18188,7 +18252,7 @@
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
+      <c r="A501" s="3" t="s">
         <v>337</v>
       </c>
       <c r="B501">
@@ -18199,7 +18263,7 @@
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
+      <c r="A502" s="3" t="s">
         <v>242</v>
       </c>
       <c r="B502">
@@ -18210,7 +18274,7 @@
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
+      <c r="A503" s="3" t="s">
         <v>349</v>
       </c>
       <c r="B503">
@@ -18221,7 +18285,7 @@
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
+      <c r="A504" s="3" t="s">
         <v>592</v>
       </c>
       <c r="B504">
@@ -18232,7 +18296,7 @@
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
+      <c r="A505" s="3" t="s">
         <v>422</v>
       </c>
       <c r="B505">
@@ -18243,7 +18307,7 @@
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A506" t="s">
+      <c r="A506" s="3" t="s">
         <v>593</v>
       </c>
       <c r="B506">
@@ -18254,7 +18318,7 @@
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A507" t="s">
+      <c r="A507" s="3" t="s">
         <v>594</v>
       </c>
       <c r="B507">
@@ -18265,7 +18329,7 @@
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A508" t="s">
+      <c r="A508" s="3" t="s">
         <v>419</v>
       </c>
       <c r="B508">
@@ -18276,7 +18340,7 @@
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A509" t="s">
+      <c r="A509" s="3" t="s">
         <v>542</v>
       </c>
       <c r="B509">
@@ -18287,7 +18351,7 @@
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A510" t="s">
+      <c r="A510" s="3" t="s">
         <v>290</v>
       </c>
       <c r="B510">
@@ -18298,7 +18362,7 @@
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A511" t="s">
+      <c r="A511" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B511">
@@ -18309,7 +18373,7 @@
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A512" t="s">
+      <c r="A512" s="3" t="s">
         <v>601</v>
       </c>
       <c r="B512">
@@ -18320,7 +18384,7 @@
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A513" t="s">
+      <c r="A513" s="3" t="s">
         <v>209</v>
       </c>
       <c r="B513">
@@ -18331,7 +18395,7 @@
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A514" t="s">
+      <c r="A514" s="3" t="s">
         <v>416</v>
       </c>
       <c r="B514">
@@ -18342,7 +18406,7 @@
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A515" t="s">
+      <c r="A515" s="3" t="s">
         <v>523</v>
       </c>
       <c r="B515">
@@ -18353,7 +18417,7 @@
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A516" t="s">
+      <c r="A516" s="3" t="s">
         <v>279</v>
       </c>
       <c r="B516">
@@ -18364,7 +18428,7 @@
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A517" t="s">
+      <c r="A517" s="3" t="s">
         <v>417</v>
       </c>
       <c r="B517">
@@ -18375,7 +18439,7 @@
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A518" t="s">
+      <c r="A518" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B518">
@@ -18386,7 +18450,7 @@
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A519" t="s">
+      <c r="A519" s="3" t="s">
         <v>399</v>
       </c>
       <c r="B519">
@@ -18397,7 +18461,7 @@
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A520" t="s">
+      <c r="A520" s="3" t="s">
         <v>385</v>
       </c>
       <c r="B520">
@@ -18408,7 +18472,7 @@
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A521" t="s">
+      <c r="A521" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B521">
@@ -18419,8 +18483,8 @@
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A522">
-        <v>13111087001</v>
+      <c r="A522" s="3" t="s">
+        <v>641</v>
       </c>
       <c r="B522">
         <v>1</v>
@@ -18430,7 +18494,7 @@
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A523" t="s">
+      <c r="A523" s="3" t="s">
         <v>348</v>
       </c>
       <c r="B523">
@@ -18441,7 +18505,7 @@
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A524" t="s">
+      <c r="A524" s="3" t="s">
         <v>548</v>
       </c>
       <c r="B524">
@@ -18452,7 +18516,7 @@
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A525" t="s">
+      <c r="A525" s="3" t="s">
         <v>311</v>
       </c>
       <c r="B525">
@@ -18463,7 +18527,7 @@
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A526" t="s">
+      <c r="A526" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B526">
@@ -18474,7 +18538,7 @@
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A527" t="s">
+      <c r="A527" s="3" t="s">
         <v>377</v>
       </c>
       <c r="B527">
@@ -18485,7 +18549,7 @@
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
+      <c r="A528" s="3" t="s">
         <v>381</v>
       </c>
       <c r="B528">
@@ -18496,7 +18560,7 @@
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A529" t="s">
+      <c r="A529" s="3" t="s">
         <v>315</v>
       </c>
       <c r="B529">
@@ -18507,7 +18571,7 @@
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A530" t="s">
+      <c r="A530" s="3" t="s">
         <v>289</v>
       </c>
       <c r="B530">
@@ -18518,7 +18582,7 @@
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A531" t="s">
+      <c r="A531" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B531">
@@ -18529,7 +18593,7 @@
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A532" t="s">
+      <c r="A532" s="3" t="s">
         <v>421</v>
       </c>
       <c r="B532">
@@ -18540,7 +18604,7 @@
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A533" t="s">
+      <c r="A533" s="3" t="s">
         <v>257</v>
       </c>
       <c r="B533">
@@ -18551,7 +18615,7 @@
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A534" t="s">
+      <c r="A534" s="3" t="s">
         <v>286</v>
       </c>
       <c r="B534">
@@ -18562,7 +18626,7 @@
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A535" t="s">
+      <c r="A535" s="3" t="s">
         <v>268</v>
       </c>
       <c r="B535">
@@ -18573,8 +18637,8 @@
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A536">
-        <v>90439443740</v>
+      <c r="A536" s="3" t="s">
+        <v>642</v>
       </c>
       <c r="B536">
         <v>1</v>
@@ -18584,7 +18648,7 @@
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A537" t="s">
+      <c r="A537" s="3" t="s">
         <v>484</v>
       </c>
       <c r="B537">
@@ -18595,7 +18659,7 @@
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A538" t="s">
+      <c r="A538" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B538">
@@ -18606,7 +18670,7 @@
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A539" t="s">
+      <c r="A539" s="3" t="s">
         <v>292</v>
       </c>
       <c r="B539">
@@ -18617,7 +18681,7 @@
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A540" t="s">
+      <c r="A540" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B540">
@@ -18628,7 +18692,7 @@
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A541" t="s">
+      <c r="A541" s="3" t="s">
         <v>338</v>
       </c>
       <c r="B541">
@@ -18639,7 +18703,7 @@
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A542" t="s">
+      <c r="A542" s="3" t="s">
         <v>386</v>
       </c>
       <c r="B542">
@@ -18650,7 +18714,7 @@
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A543" t="s">
+      <c r="A543" s="3" t="s">
         <v>354</v>
       </c>
       <c r="B543">
@@ -18661,7 +18725,7 @@
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A544" t="s">
+      <c r="A544" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B544">
@@ -18672,8 +18736,8 @@
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A545">
-        <v>9805957916</v>
+      <c r="A545" s="3" t="s">
+        <v>643</v>
       </c>
       <c r="B545">
         <v>1</v>
@@ -18683,7 +18747,7 @@
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A546" t="s">
+      <c r="A546" s="3" t="s">
         <v>351</v>
       </c>
       <c r="B546">
@@ -18694,7 +18758,7 @@
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A547" t="s">
+      <c r="A547" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B547">
@@ -18705,7 +18769,7 @@
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A548" t="s">
+      <c r="A548" s="3" t="s">
         <v>387</v>
       </c>
       <c r="B548">
@@ -18716,7 +18780,7 @@
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A549" t="s">
+      <c r="A549" s="3" t="s">
         <v>600</v>
       </c>
       <c r="B549">
@@ -18727,7 +18791,7 @@
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A550" t="s">
+      <c r="A550" s="3" t="s">
         <v>607</v>
       </c>
       <c r="B550">
@@ -18738,7 +18802,7 @@
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A551" t="s">
+      <c r="A551" s="3" t="s">
         <v>319</v>
       </c>
       <c r="B551">
@@ -18749,7 +18813,7 @@
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A552" t="s">
+      <c r="A552" s="3" t="s">
         <v>604</v>
       </c>
       <c r="B552">
@@ -18760,7 +18824,7 @@
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A553" t="s">
+      <c r="A553" s="3" t="s">
         <v>521</v>
       </c>
       <c r="B553">
@@ -18771,7 +18835,7 @@
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A554" t="s">
+      <c r="A554" s="3" t="s">
         <v>297</v>
       </c>
       <c r="B554">
@@ -18782,7 +18846,7 @@
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A555" t="s">
+      <c r="A555" s="3" t="s">
         <v>273</v>
       </c>
       <c r="B555">
@@ -18793,7 +18857,7 @@
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A556" t="s">
+      <c r="A556" s="3" t="s">
         <v>308</v>
       </c>
       <c r="B556">
@@ -18804,7 +18868,7 @@
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A557" t="s">
+      <c r="A557" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B557">
@@ -18815,7 +18879,7 @@
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A558" t="s">
+      <c r="A558" s="3" t="s">
         <v>314</v>
       </c>
       <c r="B558">
@@ -18826,7 +18890,7 @@
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A559" t="s">
+      <c r="A559" s="3" t="s">
         <v>260</v>
       </c>
       <c r="B559">
@@ -18837,8 +18901,8 @@
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A560">
-        <v>9454003010</v>
+      <c r="A560" s="3" t="s">
+        <v>644</v>
       </c>
       <c r="B560">
         <v>1</v>
@@ -18848,7 +18912,7 @@
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A561" t="s">
+      <c r="A561" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B561">
@@ -18859,7 +18923,7 @@
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A562" t="s">
+      <c r="A562" s="3" t="s">
         <v>116</v>
       </c>
       <c r="B562">
@@ -18870,7 +18934,7 @@
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A563" t="s">
+      <c r="A563" s="3" t="s">
         <v>373</v>
       </c>
       <c r="B563">
@@ -18881,7 +18945,7 @@
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A564" t="s">
+      <c r="A564" s="3" t="s">
         <v>322</v>
       </c>
       <c r="B564">
@@ -18892,7 +18956,7 @@
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A565" t="s">
+      <c r="A565" s="3" t="s">
         <v>606</v>
       </c>
       <c r="B565">
@@ -18903,7 +18967,7 @@
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A566" t="s">
+      <c r="A566" s="3" t="s">
         <v>323</v>
       </c>
       <c r="B566">
@@ -18914,7 +18978,7 @@
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A567" t="s">
+      <c r="A567" s="3" t="s">
         <v>340</v>
       </c>
       <c r="B567">
@@ -18925,7 +18989,7 @@
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A568" t="s">
+      <c r="A568" s="3" t="s">
         <v>353</v>
       </c>
       <c r="B568">
@@ -18936,7 +19000,7 @@
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A569" t="s">
+      <c r="A569" s="3" t="s">
         <v>249</v>
       </c>
       <c r="B569">
@@ -18947,7 +19011,7 @@
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A570" t="s">
+      <c r="A570" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B570">
@@ -18958,7 +19022,7 @@
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A571" t="s">
+      <c r="A571" s="3" t="s">
         <v>400</v>
       </c>
       <c r="B571">
@@ -18969,7 +19033,7 @@
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A572" t="s">
+      <c r="A572" s="3" t="s">
         <v>595</v>
       </c>
       <c r="B572">
@@ -18980,7 +19044,7 @@
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A573" t="s">
+      <c r="A573" s="3" t="s">
         <v>259</v>
       </c>
       <c r="B573">
@@ -18991,7 +19055,7 @@
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A574" t="s">
+      <c r="A574" s="3" t="s">
         <v>608</v>
       </c>
       <c r="B574">
@@ -19002,7 +19066,7 @@
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A575" t="s">
+      <c r="A575" s="3" t="s">
         <v>596</v>
       </c>
       <c r="B575">
@@ -19013,7 +19077,7 @@
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A576" t="s">
+      <c r="A576" s="3" t="s">
         <v>333</v>
       </c>
       <c r="B576">
@@ -19024,7 +19088,7 @@
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A577" t="s">
+      <c r="A577" s="3" t="s">
         <v>352</v>
       </c>
       <c r="B577">
@@ -19035,7 +19099,7 @@
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A578" t="s">
+      <c r="A578" s="3" t="s">
         <v>341</v>
       </c>
       <c r="B578">
@@ -19046,7 +19110,7 @@
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A579" t="s">
+      <c r="A579" s="3" t="s">
         <v>366</v>
       </c>
       <c r="B579">
@@ -19057,7 +19121,7 @@
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A580" t="s">
+      <c r="A580" s="3" t="s">
         <v>302</v>
       </c>
       <c r="B580">
@@ -19068,7 +19132,7 @@
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A581" t="s">
+      <c r="A581" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B581">
@@ -19079,7 +19143,7 @@
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A582" t="s">
+      <c r="A582" s="3" t="s">
         <v>241</v>
       </c>
       <c r="B582">
@@ -19090,7 +19154,7 @@
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A583" t="s">
+      <c r="A583" s="3" t="s">
         <v>549</v>
       </c>
       <c r="B583">
@@ -19101,7 +19165,7 @@
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A584" t="s">
+      <c r="A584" s="3" t="s">
         <v>244</v>
       </c>
       <c r="B584">
@@ -19112,7 +19176,7 @@
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A585" t="s">
+      <c r="A585" s="3" t="s">
         <v>382</v>
       </c>
       <c r="B585">
@@ -19123,7 +19187,7 @@
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A586" t="s">
+      <c r="A586" s="3" t="s">
         <v>215</v>
       </c>
       <c r="B586">
@@ -19134,7 +19198,7 @@
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A587" t="s">
+      <c r="A587" s="3" t="s">
         <v>418</v>
       </c>
       <c r="B587">
@@ -19145,7 +19209,7 @@
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A588" t="s">
+      <c r="A588" s="3" t="s">
         <v>284</v>
       </c>
       <c r="B588">
@@ -19156,7 +19220,7 @@
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A589" t="s">
+      <c r="A589" s="3" t="s">
         <v>237</v>
       </c>
       <c r="B589">
@@ -19167,7 +19231,7 @@
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A590" t="s">
+      <c r="A590" s="3" t="s">
         <v>285</v>
       </c>
       <c r="B590">
@@ -19178,7 +19242,7 @@
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A591" t="s">
+      <c r="A591" s="3" t="s">
         <v>350</v>
       </c>
       <c r="B591">
@@ -19189,7 +19253,7 @@
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A592" t="s">
+      <c r="A592" s="3" t="s">
         <v>605</v>
       </c>
       <c r="B592">
@@ -19200,7 +19264,7 @@
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A593" t="s">
+      <c r="A593" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B593">
@@ -19211,7 +19275,7 @@
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A594" t="s">
+      <c r="A594" s="3" t="s">
         <v>298</v>
       </c>
       <c r="B594">
@@ -19222,8 +19286,8 @@
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A595">
-        <v>91201434003</v>
+      <c r="A595" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -19233,7 +19297,7 @@
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A596" t="s">
+      <c r="A596" s="3" t="s">
         <v>300</v>
       </c>
       <c r="B596">
@@ -19244,8 +19308,8 @@
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A597">
-        <v>9451116000</v>
+      <c r="A597" s="3" t="s">
+        <v>646</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -19255,7 +19319,7 @@
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A598" t="s">
+      <c r="A598" s="3" t="s">
         <v>610</v>
       </c>
       <c r="B598">
@@ -19266,7 +19330,7 @@
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A599" t="s">
+      <c r="A599" s="3" t="s">
         <v>245</v>
       </c>
       <c r="B599">
@@ -19277,7 +19341,7 @@
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A600" t="s">
+      <c r="A600" s="3" t="s">
         <v>599</v>
       </c>
       <c r="B600">
@@ -19288,7 +19352,7 @@
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A601" t="s">
+      <c r="A601" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B601">
@@ -19299,7 +19363,7 @@
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A602" t="s">
+      <c r="A602" s="3" t="s">
         <v>611</v>
       </c>
       <c r="B602">
@@ -19310,7 +19374,7 @@
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A603" t="s">
+      <c r="A603" s="3" t="s">
         <v>609</v>
       </c>
       <c r="B603">
@@ -19321,7 +19385,7 @@
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A604" t="s">
+      <c r="A604" s="3" t="s">
         <v>598</v>
       </c>
       <c r="B604">
@@ -19332,8 +19396,8 @@
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A605">
-        <v>9820042500</v>
+      <c r="A605" s="3" t="s">
+        <v>647</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -19343,7 +19407,7 @@
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A606" t="s">
+      <c r="A606" s="3" t="s">
         <v>603</v>
       </c>
       <c r="B606">
@@ -19354,7 +19418,7 @@
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A607" t="s">
+      <c r="A607" s="3" t="s">
         <v>254</v>
       </c>
       <c r="B607">
@@ -19365,7 +19429,7 @@
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A608" t="s">
+      <c r="A608" s="3" t="s">
         <v>597</v>
       </c>
       <c r="B608">
@@ -19376,7 +19440,7 @@
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A609" t="s">
+      <c r="A609" s="3" t="s">
         <v>258</v>
       </c>
       <c r="B609">
@@ -19387,7 +19451,7 @@
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A610" t="s">
+      <c r="A610" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B610">
@@ -19398,7 +19462,7 @@
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A611" t="s">
+      <c r="A611" s="3" t="s">
         <v>262</v>
       </c>
       <c r="B611">
@@ -19409,7 +19473,7 @@
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A612" t="s">
+      <c r="A612" s="3" t="s">
         <v>390</v>
       </c>
       <c r="B612">
@@ -19420,7 +19484,7 @@
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A613" t="s">
+      <c r="A613" s="3" t="s">
         <v>410</v>
       </c>
       <c r="B613">
@@ -19431,7 +19495,7 @@
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A614" t="s">
+      <c r="A614" s="3" t="s">
         <v>395</v>
       </c>
       <c r="B614">
@@ -19442,7 +19506,7 @@
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A615" t="s">
+      <c r="A615" s="3" t="s">
         <v>266</v>
       </c>
       <c r="B615">
@@ -19453,7 +19517,7 @@
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A616" t="s">
+      <c r="A616" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B616">
@@ -19464,7 +19528,7 @@
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A617" t="s">
+      <c r="A617" s="3" t="s">
         <v>269</v>
       </c>
       <c r="B617">
@@ -19475,7 +19539,7 @@
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A618" t="s">
+      <c r="A618" s="3" t="s">
         <v>277</v>
       </c>
       <c r="B618">
@@ -19486,7 +19550,7 @@
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A619" t="s">
+      <c r="A619" s="3" t="s">
         <v>312</v>
       </c>
       <c r="B619">
@@ -19497,7 +19561,7 @@
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A620" t="s">
+      <c r="A620" s="3" t="s">
         <v>415</v>
       </c>
       <c r="B620">
@@ -19508,8 +19572,8 @@
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A621">
-        <v>9452028000</v>
+      <c r="A621" s="3" t="s">
+        <v>648</v>
       </c>
       <c r="B621">
         <v>1</v>
@@ -19519,7 +19583,7 @@
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A622" t="s">
+      <c r="A622" s="3" t="s">
         <v>246</v>
       </c>
       <c r="B622">
@@ -19530,7 +19594,7 @@
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A623" t="s">
+      <c r="A623" s="3" t="s">
         <v>320</v>
       </c>
       <c r="B623">
@@ -19541,7 +19605,7 @@
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A624" t="s">
+      <c r="A624" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B624">
@@ -19552,7 +19616,7 @@
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A625" t="s">
+      <c r="A625" s="3" t="s">
         <v>294</v>
       </c>
       <c r="B625">
@@ -19563,7 +19627,7 @@
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A626" t="s">
+      <c r="A626" s="3" t="s">
         <v>332</v>
       </c>
       <c r="B626">
@@ -19574,7 +19638,7 @@
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A627" t="s">
+      <c r="A627" s="3" t="s">
         <v>420</v>
       </c>
       <c r="B627">
@@ -19585,7 +19649,7 @@
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A628" t="s">
+      <c r="A628" s="3" t="s">
         <v>630</v>
       </c>
       <c r="B628">
@@ -19596,7 +19660,7 @@
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A629" t="s">
+      <c r="A629" s="3" t="s">
         <v>540</v>
       </c>
       <c r="B629">
@@ -19607,7 +19671,7 @@
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A630" t="s">
+      <c r="A630" s="3" t="s">
         <v>318</v>
       </c>
       <c r="B630">
@@ -19618,7 +19682,7 @@
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A631" t="s">
+      <c r="A631" s="3" t="s">
         <v>477</v>
       </c>
       <c r="B631">
@@ -19629,7 +19693,7 @@
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A632" t="s">
+      <c r="A632" s="3" t="s">
         <v>631</v>
       </c>
       <c r="B632">
@@ -19640,7 +19704,7 @@
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A633" t="s">
+      <c r="A633" s="3" t="s">
         <v>602</v>
       </c>
       <c r="B633">
@@ -19651,7 +19715,7 @@
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A634" t="s">
+      <c r="A634" s="3" t="s">
         <v>326</v>
       </c>
       <c r="B634">
@@ -19662,7 +19726,7 @@
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A635" t="s">
+      <c r="A635" s="3" t="s">
         <v>299</v>
       </c>
       <c r="B635">
@@ -19673,7 +19737,7 @@
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A636" t="s">
+      <c r="A636" s="3" t="s">
         <v>295</v>
       </c>
       <c r="B636">
@@ -19684,7 +19748,7 @@
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A637" t="s">
+      <c r="A637" s="3" t="s">
         <v>363</v>
       </c>
       <c r="B637">
@@ -19695,9 +19759,13 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/STOK RANK/Rank Dealer/RANK LSP.xlsx
+++ b/STOK RANK/Rank Dealer/RANK LSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0DD98B-4D33-4249-AC08-DE139962CB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCABDF02-7D77-4A46-ABDE-EAA12A0512B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
@@ -2461,7 +2461,7 @@
         <v>625</v>
       </c>
       <c r="C2" s="1">
-        <v>104.16666666666667</v>
+        <v>105</v>
       </c>
       <c r="D2" s="1">
         <v>104.16666666666667</v>
@@ -2501,7 +2501,7 @@
         <v>190</v>
       </c>
       <c r="C4" s="1">
-        <v>31.666666666666668</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1">
         <v>168.83333333333334</v>
@@ -2521,7 +2521,7 @@
         <v>185</v>
       </c>
       <c r="C5" s="1">
-        <v>30.833333333333332</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1">
         <v>199.66666666666669</v>
@@ -2541,7 +2541,7 @@
         <v>135</v>
       </c>
       <c r="C6" s="1">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>222.16666666666669</v>
@@ -2561,7 +2561,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="1">
-        <v>18.833333333333332</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1">
         <v>241.00000000000003</v>
@@ -2581,7 +2581,7 @@
         <v>103</v>
       </c>
       <c r="C8" s="1">
-        <v>17.166666666666668</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1">
         <v>258.16666666666669</v>
@@ -2601,7 +2601,7 @@
         <v>83</v>
       </c>
       <c r="C9" s="1">
-        <v>13.833333333333334</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1">
         <v>272</v>
@@ -2621,7 +2621,7 @@
         <v>79</v>
       </c>
       <c r="C10" s="1">
-        <v>13.166666666666666</v>
+        <v>14</v>
       </c>
       <c r="D10" s="1">
         <v>285.16666666666669</v>
@@ -2641,7 +2641,7 @@
         <v>69</v>
       </c>
       <c r="C11" s="1">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1">
         <v>296.66666666666669</v>
@@ -2661,7 +2661,7 @@
         <v>67</v>
       </c>
       <c r="C12" s="1">
-        <v>11.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1">
         <v>307.83333333333337</v>
@@ -2681,7 +2681,7 @@
         <v>65</v>
       </c>
       <c r="C13" s="1">
-        <v>10.833333333333334</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1">
         <v>318.66666666666669</v>
@@ -2701,7 +2701,7 @@
         <v>61</v>
       </c>
       <c r="C14" s="1">
-        <v>10.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1">
         <v>328.83333333333337</v>
@@ -2721,7 +2721,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="1">
-        <v>10.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1">
         <v>339.00000000000006</v>
@@ -2741,7 +2741,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="1">
-        <v>9.8333333333333339</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1">
         <v>348.83333333333337</v>
@@ -2761,7 +2761,7 @@
         <v>56</v>
       </c>
       <c r="C17" s="1">
-        <v>9.3333333333333339</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1">
         <v>358.16666666666669</v>
@@ -2781,7 +2781,7 @@
         <v>55</v>
       </c>
       <c r="C18" s="1">
-        <v>9.1666666666666661</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1">
         <v>367.33333333333337</v>
@@ -2801,7 +2801,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="1">
-        <v>8.1666666666666661</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1">
         <v>375.50000000000006</v>
@@ -2821,7 +2821,7 @@
         <v>43</v>
       </c>
       <c r="C20" s="1">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
         <v>382.66666666666674</v>
@@ -2841,7 +2841,7 @@
         <v>43</v>
       </c>
       <c r="C21" s="1">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1">
         <v>389.83333333333343</v>
@@ -2901,7 +2901,7 @@
         <v>41</v>
       </c>
       <c r="C24" s="1">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1">
         <v>410.66666666666674</v>
@@ -2921,7 +2921,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="1">
-        <v>6.666666666666667</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1">
         <v>417.33333333333343</v>
@@ -2941,7 +2941,7 @@
         <v>39</v>
       </c>
       <c r="C26" s="1">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1">
         <v>423.83333333333343</v>
@@ -2961,7 +2961,7 @@
         <v>38</v>
       </c>
       <c r="C27" s="1">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1">
         <v>430.16666666666674</v>
@@ -2981,7 +2981,7 @@
         <v>38</v>
       </c>
       <c r="C28" s="1">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="D28" s="1">
         <v>436.50000000000006</v>
@@ -3001,7 +3001,7 @@
         <v>37</v>
       </c>
       <c r="C29" s="1">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1">
         <v>442.66666666666674</v>
@@ -3041,7 +3041,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="1">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="D31" s="1">
         <v>454.50000000000006</v>
@@ -3061,7 +3061,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="1">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="D32" s="1">
         <v>459.66666666666674</v>
@@ -3081,7 +3081,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="1">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="D33" s="1">
         <v>464.83333333333343</v>
@@ -3161,7 +3161,7 @@
         <v>29</v>
       </c>
       <c r="C37" s="1">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="D37" s="1">
         <v>484.66666666666674</v>
@@ -3181,7 +3181,7 @@
         <v>28</v>
       </c>
       <c r="C38" s="1">
-        <v>4.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="D38" s="1">
         <v>489.33333333333343</v>
@@ -3201,7 +3201,7 @@
         <v>27</v>
       </c>
       <c r="C39" s="1">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D39" s="1">
         <v>493.83333333333343</v>
@@ -3221,7 +3221,7 @@
         <v>26</v>
       </c>
       <c r="C40" s="1">
-        <v>4.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="D40" s="1">
         <v>498.16666666666674</v>
@@ -3241,7 +3241,7 @@
         <v>25</v>
       </c>
       <c r="C41" s="1">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="D41" s="1">
         <v>502.33333333333343</v>
@@ -3261,7 +3261,7 @@
         <v>25</v>
       </c>
       <c r="C42" s="1">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="D42" s="1">
         <v>506.50000000000011</v>
@@ -3321,7 +3321,7 @@
         <v>23</v>
       </c>
       <c r="C45" s="1">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
       <c r="D45" s="1">
         <v>518.33333333333348</v>
@@ -3341,7 +3341,7 @@
         <v>22</v>
       </c>
       <c r="C46" s="1">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
       <c r="D46" s="1">
         <v>522.00000000000011</v>
@@ -3361,7 +3361,7 @@
         <v>22</v>
       </c>
       <c r="C47" s="1">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
       <c r="D47" s="1">
         <v>525.66666666666674</v>
@@ -3381,7 +3381,7 @@
         <v>22</v>
       </c>
       <c r="C48" s="1">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
       <c r="D48" s="1">
         <v>529.33333333333337</v>
@@ -3401,7 +3401,7 @@
         <v>22</v>
       </c>
       <c r="C49" s="1">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
       <c r="D49" s="1">
         <v>533</v>
@@ -3421,7 +3421,7 @@
         <v>21</v>
       </c>
       <c r="C50" s="1">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D50" s="1">
         <v>536.5</v>
@@ -3441,7 +3441,7 @@
         <v>20</v>
       </c>
       <c r="C51" s="1">
-        <v>3.3333333333333335</v>
+        <v>4</v>
       </c>
       <c r="D51" s="1">
         <v>539.83333333333337</v>
@@ -3461,7 +3461,7 @@
         <v>16</v>
       </c>
       <c r="C52" s="1">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D52" s="1">
         <v>542.5</v>
@@ -3481,7 +3481,7 @@
         <v>16</v>
       </c>
       <c r="C53" s="1">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D53" s="1">
         <v>545.16666666666663</v>
@@ -3501,7 +3501,7 @@
         <v>13</v>
       </c>
       <c r="C54" s="1">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D54" s="1">
         <v>547.33333333333326</v>
@@ -3521,7 +3521,7 @@
         <v>13</v>
       </c>
       <c r="C55" s="1">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D55" s="1">
         <v>549.49999999999989</v>
@@ -3541,7 +3541,7 @@
         <v>13</v>
       </c>
       <c r="C56" s="1">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D56" s="1">
         <v>551.66666666666652</v>
@@ -3601,7 +3601,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D59" s="1">
         <v>557.49999999999989</v>
@@ -3621,7 +3621,7 @@
         <v>11</v>
       </c>
       <c r="C60" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D60" s="1">
         <v>559.33333333333326</v>
@@ -3641,7 +3641,7 @@
         <v>11</v>
       </c>
       <c r="C61" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D61" s="1">
         <v>561.16666666666663</v>
@@ -3661,7 +3661,7 @@
         <v>11</v>
       </c>
       <c r="C62" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D62" s="1">
         <v>563</v>
@@ -3681,7 +3681,7 @@
         <v>11</v>
       </c>
       <c r="C63" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1">
         <v>564.83333333333337</v>
@@ -3701,7 +3701,7 @@
         <v>10</v>
       </c>
       <c r="C64" s="1">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D64" s="1">
         <v>566.5</v>
@@ -3721,7 +3721,7 @@
         <v>10</v>
       </c>
       <c r="C65" s="1">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D65" s="1">
         <v>568.16666666666663</v>
@@ -3741,7 +3741,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="1">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D66" s="1">
         <v>569.83333333333326</v>
@@ -3761,7 +3761,7 @@
         <v>9</v>
       </c>
       <c r="C67" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D67" s="1">
         <v>571.33333333333326</v>
@@ -3781,7 +3781,7 @@
         <v>9</v>
       </c>
       <c r="C68" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D68" s="1">
         <v>572.83333333333326</v>
@@ -3801,7 +3801,7 @@
         <v>9</v>
       </c>
       <c r="C69" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D69" s="1">
         <v>574.33333333333326</v>
@@ -3821,7 +3821,7 @@
         <v>9</v>
       </c>
       <c r="C70" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D70" s="1">
         <v>575.83333333333326</v>
@@ -3841,7 +3841,7 @@
         <v>9</v>
       </c>
       <c r="C71" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D71" s="1">
         <v>577.33333333333326</v>
@@ -3861,7 +3861,7 @@
         <v>9</v>
       </c>
       <c r="C72" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D72" s="1">
         <v>578.83333333333326</v>
@@ -3881,7 +3881,7 @@
         <v>9</v>
       </c>
       <c r="C73" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D73" s="1">
         <v>580.33333333333326</v>
@@ -3901,7 +3901,7 @@
         <v>9</v>
       </c>
       <c r="C74" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D74" s="1">
         <v>581.83333333333326</v>
@@ -3921,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="1">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D75" s="1">
         <v>583.16666666666663</v>
@@ -3941,7 +3941,7 @@
         <v>8</v>
       </c>
       <c r="C76" s="1">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D76" s="1">
         <v>584.5</v>
@@ -3961,7 +3961,7 @@
         <v>8</v>
       </c>
       <c r="C77" s="1">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D77" s="1">
         <v>585.83333333333337</v>
@@ -3981,7 +3981,7 @@
         <v>7</v>
       </c>
       <c r="C78" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D78" s="1">
         <v>587</v>
@@ -4001,7 +4001,7 @@
         <v>7</v>
       </c>
       <c r="C79" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D79" s="1">
         <v>588.16666666666663</v>
@@ -4021,7 +4021,7 @@
         <v>7</v>
       </c>
       <c r="C80" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D80" s="1">
         <v>589.33333333333326</v>
@@ -4041,7 +4041,7 @@
         <v>7</v>
       </c>
       <c r="C81" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D81" s="1">
         <v>590.49999999999989</v>
@@ -4061,7 +4061,7 @@
         <v>7</v>
       </c>
       <c r="C82" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D82" s="1">
         <v>591.66666666666652</v>
@@ -4081,7 +4081,7 @@
         <v>7</v>
       </c>
       <c r="C83" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D83" s="1">
         <v>592.83333333333314</v>
@@ -4101,7 +4101,7 @@
         <v>7</v>
       </c>
       <c r="C84" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D84" s="1">
         <v>593.99999999999977</v>
@@ -4121,7 +4121,7 @@
         <v>7</v>
       </c>
       <c r="C85" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D85" s="1">
         <v>595.1666666666664</v>
@@ -4481,7 +4481,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D103" s="1">
         <v>612.99999999999977</v>
@@ -4501,7 +4501,7 @@
         <v>5</v>
       </c>
       <c r="C104" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D104" s="1">
         <v>613.83333333333314</v>
@@ -4521,7 +4521,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D105" s="1">
         <v>614.66666666666652</v>
@@ -4541,7 +4541,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D106" s="1">
         <v>615.49999999999989</v>
@@ -4561,7 +4561,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D107" s="1">
         <v>616.33333333333326</v>
@@ -4581,7 +4581,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D108" s="1">
         <v>617.16666666666663</v>
@@ -4601,7 +4601,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D109" s="1">
         <v>618</v>
@@ -4621,7 +4621,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D110" s="1">
         <v>618.83333333333337</v>
@@ -4641,7 +4641,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D111" s="1">
         <v>619.66666666666674</v>
@@ -4661,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="C112" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D112" s="1">
         <v>620.33333333333337</v>
@@ -4681,7 +4681,7 @@
         <v>4</v>
       </c>
       <c r="C113" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D113" s="1">
         <v>621</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="C114" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D114" s="1">
         <v>621.66666666666663</v>
@@ -4721,7 +4721,7 @@
         <v>4</v>
       </c>
       <c r="C115" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D115" s="1">
         <v>622.33333333333326</v>
@@ -4741,7 +4741,7 @@
         <v>4</v>
       </c>
       <c r="C116" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D116" s="1">
         <v>622.99999999999989</v>
@@ -4761,7 +4761,7 @@
         <v>4</v>
       </c>
       <c r="C117" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D117" s="1">
         <v>623.66666666666652</v>
@@ -4781,7 +4781,7 @@
         <v>4</v>
       </c>
       <c r="C118" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D118" s="1">
         <v>624.33333333333314</v>
@@ -4801,7 +4801,7 @@
         <v>4</v>
       </c>
       <c r="C119" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D119" s="1">
         <v>624.99999999999977</v>
@@ -4821,7 +4821,7 @@
         <v>4</v>
       </c>
       <c r="C120" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D120" s="1">
         <v>625.6666666666664</v>
@@ -4841,7 +4841,7 @@
         <v>4</v>
       </c>
       <c r="C121" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D121" s="1">
         <v>626.33333333333303</v>
@@ -4861,7 +4861,7 @@
         <v>4</v>
       </c>
       <c r="C122" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D122" s="1">
         <v>626.99999999999966</v>
@@ -4881,7 +4881,7 @@
         <v>4</v>
       </c>
       <c r="C123" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D123" s="1">
         <v>627.66666666666629</v>
@@ -4901,7 +4901,7 @@
         <v>4</v>
       </c>
       <c r="C124" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D124" s="1">
         <v>628.33333333333292</v>
@@ -4921,7 +4921,7 @@
         <v>4</v>
       </c>
       <c r="C125" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D125" s="1">
         <v>628.99999999999955</v>
@@ -4941,7 +4941,7 @@
         <v>4</v>
       </c>
       <c r="C126" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D126" s="1">
         <v>629.66666666666617</v>
@@ -4961,7 +4961,7 @@
         <v>4</v>
       </c>
       <c r="C127" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D127" s="1">
         <v>630.3333333333328</v>
@@ -4981,7 +4981,7 @@
         <v>4</v>
       </c>
       <c r="C128" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D128" s="1">
         <v>630.99999999999943</v>
@@ -5001,7 +5001,7 @@
         <v>4</v>
       </c>
       <c r="C129" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D129" s="1">
         <v>631.66666666666606</v>
@@ -5021,7 +5021,7 @@
         <v>4</v>
       </c>
       <c r="C130" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D130" s="1">
         <v>632.33333333333269</v>
@@ -5041,7 +5041,7 @@
         <v>4</v>
       </c>
       <c r="C131" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D131" s="1">
         <v>632.99999999999932</v>
@@ -5061,7 +5061,7 @@
         <v>4</v>
       </c>
       <c r="C132" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D132" s="1">
         <v>633.66666666666595</v>
@@ -5081,7 +5081,7 @@
         <v>4</v>
       </c>
       <c r="C133" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D133" s="1">
         <v>634.33333333333258</v>
@@ -5101,7 +5101,7 @@
         <v>3</v>
       </c>
       <c r="C134" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D134" s="1">
         <v>634.83333333333258</v>
@@ -5121,7 +5121,7 @@
         <v>3</v>
       </c>
       <c r="C135" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D135" s="1">
         <v>635.33333333333258</v>
@@ -5141,7 +5141,7 @@
         <v>3</v>
       </c>
       <c r="C136" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D136" s="1">
         <v>635.83333333333258</v>
@@ -5161,7 +5161,7 @@
         <v>3</v>
       </c>
       <c r="C137" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D137" s="1">
         <v>636.33333333333258</v>
@@ -5181,7 +5181,7 @@
         <v>3</v>
       </c>
       <c r="C138" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D138" s="1">
         <v>636.83333333333258</v>
@@ -5201,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="C139" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D139" s="1">
         <v>637.33333333333258</v>
@@ -5221,7 +5221,7 @@
         <v>3</v>
       </c>
       <c r="C140" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D140" s="1">
         <v>637.83333333333258</v>
@@ -5241,7 +5241,7 @@
         <v>3</v>
       </c>
       <c r="C141" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D141" s="1">
         <v>638.33333333333258</v>
@@ -5261,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="C142" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D142" s="1">
         <v>638.83333333333258</v>
@@ -5281,7 +5281,7 @@
         <v>3</v>
       </c>
       <c r="C143" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D143" s="1">
         <v>639.33333333333258</v>
@@ -5301,7 +5301,7 @@
         <v>3</v>
       </c>
       <c r="C144" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D144" s="1">
         <v>639.83333333333258</v>
@@ -5321,7 +5321,7 @@
         <v>3</v>
       </c>
       <c r="C145" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D145" s="1">
         <v>640.33333333333258</v>
@@ -5341,7 +5341,7 @@
         <v>3</v>
       </c>
       <c r="C146" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D146" s="1">
         <v>640.83333333333258</v>
@@ -5361,7 +5361,7 @@
         <v>3</v>
       </c>
       <c r="C147" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D147" s="1">
         <v>641.33333333333258</v>
@@ -5381,7 +5381,7 @@
         <v>3</v>
       </c>
       <c r="C148" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D148" s="1">
         <v>641.83333333333258</v>
@@ -5401,7 +5401,7 @@
         <v>3</v>
       </c>
       <c r="C149" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D149" s="1">
         <v>642.33333333333258</v>
@@ -5421,7 +5421,7 @@
         <v>3</v>
       </c>
       <c r="C150" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D150" s="1">
         <v>642.83333333333258</v>
@@ -5441,7 +5441,7 @@
         <v>3</v>
       </c>
       <c r="C151" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D151" s="1">
         <v>643.33333333333258</v>
@@ -5461,7 +5461,7 @@
         <v>3</v>
       </c>
       <c r="C152" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D152" s="1">
         <v>643.83333333333258</v>
@@ -5481,7 +5481,7 @@
         <v>3</v>
       </c>
       <c r="C153" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D153" s="1">
         <v>644.33333333333258</v>
@@ -5501,7 +5501,7 @@
         <v>3</v>
       </c>
       <c r="C154" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D154" s="1">
         <v>644.83333333333258</v>
@@ -5521,7 +5521,7 @@
         <v>3</v>
       </c>
       <c r="C155" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D155" s="1">
         <v>645.33333333333258</v>
@@ -5541,7 +5541,7 @@
         <v>3</v>
       </c>
       <c r="C156" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D156" s="1">
         <v>645.83333333333258</v>
@@ -5561,7 +5561,7 @@
         <v>3</v>
       </c>
       <c r="C157" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D157" s="1">
         <v>646.33333333333258</v>
@@ -5581,7 +5581,7 @@
         <v>3</v>
       </c>
       <c r="C158" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D158" s="1">
         <v>646.83333333333258</v>
@@ -5601,7 +5601,7 @@
         <v>3</v>
       </c>
       <c r="C159" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D159" s="1">
         <v>647.33333333333258</v>
@@ -5621,7 +5621,7 @@
         <v>3</v>
       </c>
       <c r="C160" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D160" s="1">
         <v>647.83333333333258</v>
@@ -5641,7 +5641,7 @@
         <v>3</v>
       </c>
       <c r="C161" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D161" s="1">
         <v>648.33333333333258</v>
@@ -5661,7 +5661,7 @@
         <v>3</v>
       </c>
       <c r="C162" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D162" s="1">
         <v>648.83333333333258</v>
@@ -5681,7 +5681,7 @@
         <v>3</v>
       </c>
       <c r="C163" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D163" s="1">
         <v>649.33333333333258</v>
@@ -5701,7 +5701,7 @@
         <v>3</v>
       </c>
       <c r="C164" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D164" s="1">
         <v>649.83333333333258</v>
@@ -5721,7 +5721,7 @@
         <v>3</v>
       </c>
       <c r="C165" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D165" s="1">
         <v>650.33333333333258</v>
@@ -5741,7 +5741,7 @@
         <v>3</v>
       </c>
       <c r="C166" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D166" s="1">
         <v>650.83333333333258</v>
@@ -5761,7 +5761,7 @@
         <v>3</v>
       </c>
       <c r="C167" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D167" s="1">
         <v>651.33333333333258</v>
@@ -5781,7 +5781,7 @@
         <v>3</v>
       </c>
       <c r="C168" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D168" s="1">
         <v>651.83333333333258</v>
@@ -5801,7 +5801,7 @@
         <v>3</v>
       </c>
       <c r="C169" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D169" s="1">
         <v>652.33333333333258</v>
@@ -5821,7 +5821,7 @@
         <v>3</v>
       </c>
       <c r="C170" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D170" s="1">
         <v>652.83333333333258</v>
@@ -5841,7 +5841,7 @@
         <v>3</v>
       </c>
       <c r="C171" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D171" s="1">
         <v>653.33333333333258</v>
@@ -5861,7 +5861,7 @@
         <v>2</v>
       </c>
       <c r="C172" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D172" s="1">
         <v>653.66666666666595</v>
@@ -5881,7 +5881,7 @@
         <v>2</v>
       </c>
       <c r="C173" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D173" s="1">
         <v>653.99999999999932</v>
@@ -5901,7 +5901,7 @@
         <v>2</v>
       </c>
       <c r="C174" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D174" s="1">
         <v>654.33333333333269</v>
@@ -5921,7 +5921,7 @@
         <v>2</v>
       </c>
       <c r="C175" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D175" s="1">
         <v>654.66666666666606</v>
@@ -5941,7 +5941,7 @@
         <v>2</v>
       </c>
       <c r="C176" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D176" s="1">
         <v>654.99999999999943</v>
@@ -5961,7 +5961,7 @@
         <v>2</v>
       </c>
       <c r="C177" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D177" s="1">
         <v>655.3333333333328</v>
@@ -5981,7 +5981,7 @@
         <v>2</v>
       </c>
       <c r="C178" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D178" s="1">
         <v>655.66666666666617</v>
@@ -6001,7 +6001,7 @@
         <v>2</v>
       </c>
       <c r="C179" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D179" s="1">
         <v>655.99999999999955</v>
@@ -6021,7 +6021,7 @@
         <v>2</v>
       </c>
       <c r="C180" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D180" s="1">
         <v>656.33333333333292</v>
@@ -6041,7 +6041,7 @@
         <v>2</v>
       </c>
       <c r="C181" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D181" s="1">
         <v>656.66666666666629</v>
@@ -6061,7 +6061,7 @@
         <v>2</v>
       </c>
       <c r="C182" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D182" s="1">
         <v>656.99999999999966</v>
@@ -6081,7 +6081,7 @@
         <v>2</v>
       </c>
       <c r="C183" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D183" s="1">
         <v>657.33333333333303</v>
@@ -6101,7 +6101,7 @@
         <v>2</v>
       </c>
       <c r="C184" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D184" s="1">
         <v>657.6666666666664</v>
@@ -6121,7 +6121,7 @@
         <v>2</v>
       </c>
       <c r="C185" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D185" s="1">
         <v>657.99999999999977</v>
@@ -6141,7 +6141,7 @@
         <v>2</v>
       </c>
       <c r="C186" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D186" s="1">
         <v>658.33333333333314</v>
@@ -6161,7 +6161,7 @@
         <v>2</v>
       </c>
       <c r="C187" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D187" s="1">
         <v>658.66666666666652</v>
@@ -6181,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="C188" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D188" s="1">
         <v>658.99999999999989</v>
@@ -6201,7 +6201,7 @@
         <v>2</v>
       </c>
       <c r="C189" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D189" s="1">
         <v>659.33333333333326</v>
@@ -6221,7 +6221,7 @@
         <v>2</v>
       </c>
       <c r="C190" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D190" s="1">
         <v>659.66666666666663</v>
@@ -6241,7 +6241,7 @@
         <v>2</v>
       </c>
       <c r="C191" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D191" s="1">
         <v>660</v>
@@ -6261,7 +6261,7 @@
         <v>2</v>
       </c>
       <c r="C192" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D192" s="1">
         <v>660.33333333333337</v>
@@ -6281,7 +6281,7 @@
         <v>2</v>
       </c>
       <c r="C193" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D193" s="1">
         <v>660.66666666666674</v>
@@ -6301,7 +6301,7 @@
         <v>2</v>
       </c>
       <c r="C194" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D194" s="1">
         <v>661.00000000000011</v>
@@ -6321,7 +6321,7 @@
         <v>2</v>
       </c>
       <c r="C195" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D195" s="1">
         <v>661.33333333333348</v>
@@ -6341,7 +6341,7 @@
         <v>2</v>
       </c>
       <c r="C196" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D196" s="1">
         <v>661.66666666666686</v>
@@ -6361,7 +6361,7 @@
         <v>2</v>
       </c>
       <c r="C197" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D197" s="1">
         <v>662.00000000000023</v>
@@ -6381,7 +6381,7 @@
         <v>2</v>
       </c>
       <c r="C198" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D198" s="1">
         <v>662.3333333333336</v>
@@ -6401,7 +6401,7 @@
         <v>2</v>
       </c>
       <c r="C199" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D199" s="1">
         <v>662.66666666666697</v>
@@ -6421,7 +6421,7 @@
         <v>2</v>
       </c>
       <c r="C200" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D200" s="1">
         <v>663.00000000000034</v>
@@ -6441,7 +6441,7 @@
         <v>2</v>
       </c>
       <c r="C201" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D201" s="1">
         <v>663.33333333333371</v>
@@ -6461,7 +6461,7 @@
         <v>2</v>
       </c>
       <c r="C202" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D202" s="1">
         <v>663.66666666666708</v>
@@ -6481,7 +6481,7 @@
         <v>2</v>
       </c>
       <c r="C203" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D203" s="1">
         <v>664.00000000000045</v>
@@ -6501,7 +6501,7 @@
         <v>2</v>
       </c>
       <c r="C204" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D204" s="1">
         <v>664.33333333333383</v>
@@ -6521,7 +6521,7 @@
         <v>2</v>
       </c>
       <c r="C205" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D205" s="1">
         <v>664.6666666666672</v>
@@ -6541,7 +6541,7 @@
         <v>2</v>
       </c>
       <c r="C206" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D206" s="1">
         <v>665.00000000000057</v>
@@ -6561,7 +6561,7 @@
         <v>2</v>
       </c>
       <c r="C207" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D207" s="1">
         <v>665.33333333333394</v>
@@ -6581,7 +6581,7 @@
         <v>2</v>
       </c>
       <c r="C208" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D208" s="1">
         <v>665.66666666666731</v>
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="C209" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D209" s="1">
         <v>666.00000000000068</v>
@@ -6621,7 +6621,7 @@
         <v>2</v>
       </c>
       <c r="C210" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D210" s="1">
         <v>666.33333333333405</v>
@@ -6641,7 +6641,7 @@
         <v>2</v>
       </c>
       <c r="C211" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D211" s="1">
         <v>666.66666666666742</v>
@@ -6661,7 +6661,7 @@
         <v>2</v>
       </c>
       <c r="C212" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D212" s="1">
         <v>667.0000000000008</v>
@@ -6681,7 +6681,7 @@
         <v>2</v>
       </c>
       <c r="C213" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D213" s="1">
         <v>667.33333333333417</v>
@@ -6701,7 +6701,7 @@
         <v>2</v>
       </c>
       <c r="C214" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D214" s="1">
         <v>667.66666666666754</v>
@@ -6721,7 +6721,7 @@
         <v>2</v>
       </c>
       <c r="C215" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D215" s="1">
         <v>668.00000000000091</v>
@@ -6741,7 +6741,7 @@
         <v>2</v>
       </c>
       <c r="C216" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D216" s="1">
         <v>668.33333333333428</v>
@@ -6761,7 +6761,7 @@
         <v>2</v>
       </c>
       <c r="C217" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D217" s="1">
         <v>668.66666666666765</v>
@@ -6781,7 +6781,7 @@
         <v>2</v>
       </c>
       <c r="C218" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D218" s="1">
         <v>669.00000000000102</v>
@@ -6801,7 +6801,7 @@
         <v>2</v>
       </c>
       <c r="C219" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D219" s="1">
         <v>669.33333333333439</v>
@@ -6821,7 +6821,7 @@
         <v>2</v>
       </c>
       <c r="C220" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D220" s="1">
         <v>669.66666666666777</v>
@@ -6841,7 +6841,7 @@
         <v>2</v>
       </c>
       <c r="C221" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D221" s="1">
         <v>670.00000000000114</v>
@@ -6861,7 +6861,7 @@
         <v>2</v>
       </c>
       <c r="C222" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D222" s="1">
         <v>670.33333333333451</v>
@@ -6881,7 +6881,7 @@
         <v>2</v>
       </c>
       <c r="C223" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D223" s="1">
         <v>670.66666666666788</v>
@@ -6901,7 +6901,7 @@
         <v>2</v>
       </c>
       <c r="C224" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D224" s="1">
         <v>671.00000000000125</v>
@@ -6921,7 +6921,7 @@
         <v>2</v>
       </c>
       <c r="C225" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D225" s="1">
         <v>671.33333333333462</v>
@@ -6941,7 +6941,7 @@
         <v>2</v>
       </c>
       <c r="C226" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D226" s="1">
         <v>671.66666666666799</v>
@@ -6961,7 +6961,7 @@
         <v>2</v>
       </c>
       <c r="C227" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D227" s="1">
         <v>672.00000000000136</v>
@@ -6981,7 +6981,7 @@
         <v>2</v>
       </c>
       <c r="C228" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D228" s="1">
         <v>672.33333333333474</v>
@@ -7001,7 +7001,7 @@
         <v>2</v>
       </c>
       <c r="C229" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D229" s="1">
         <v>672.66666666666811</v>
@@ -7021,7 +7021,7 @@
         <v>2</v>
       </c>
       <c r="C230" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D230" s="1">
         <v>673.00000000000148</v>
@@ -7041,7 +7041,7 @@
         <v>2</v>
       </c>
       <c r="C231" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D231" s="1">
         <v>673.33333333333485</v>
@@ -7061,7 +7061,7 @@
         <v>2</v>
       </c>
       <c r="C232" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D232" s="1">
         <v>673.66666666666822</v>
@@ -7081,7 +7081,7 @@
         <v>2</v>
       </c>
       <c r="C233" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D233" s="1">
         <v>674.00000000000159</v>
@@ -7101,7 +7101,7 @@
         <v>2</v>
       </c>
       <c r="C234" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D234" s="1">
         <v>674.33333333333496</v>
@@ -7121,7 +7121,7 @@
         <v>2</v>
       </c>
       <c r="C235" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D235" s="1">
         <v>674.66666666666833</v>
@@ -7141,7 +7141,7 @@
         <v>2</v>
       </c>
       <c r="C236" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D236" s="1">
         <v>675.00000000000171</v>
@@ -7161,7 +7161,7 @@
         <v>2</v>
       </c>
       <c r="C237" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D237" s="1">
         <v>675.33333333333508</v>
@@ -7181,7 +7181,7 @@
         <v>2</v>
       </c>
       <c r="C238" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D238" s="1">
         <v>675.66666666666845</v>
@@ -7201,7 +7201,7 @@
         <v>2</v>
       </c>
       <c r="C239" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D239" s="1">
         <v>676.00000000000182</v>
@@ -7221,7 +7221,7 @@
         <v>2</v>
       </c>
       <c r="C240" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D240" s="1">
         <v>676.33333333333519</v>
@@ -7241,7 +7241,7 @@
         <v>2</v>
       </c>
       <c r="C241" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D241" s="1">
         <v>676.66666666666856</v>
@@ -7261,7 +7261,7 @@
         <v>2</v>
       </c>
       <c r="C242" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D242" s="1">
         <v>677.00000000000193</v>
@@ -7281,7 +7281,7 @@
         <v>2</v>
       </c>
       <c r="C243" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D243" s="1">
         <v>677.3333333333353</v>
@@ -7301,7 +7301,7 @@
         <v>2</v>
       </c>
       <c r="C244" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D244" s="1">
         <v>677.66666666666868</v>
@@ -7321,7 +7321,7 @@
         <v>2</v>
       </c>
       <c r="C245" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D245" s="1">
         <v>678.00000000000205</v>
@@ -7341,7 +7341,7 @@
         <v>2</v>
       </c>
       <c r="C246" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D246" s="1">
         <v>678.33333333333542</v>
@@ -7361,7 +7361,7 @@
         <v>2</v>
       </c>
       <c r="C247" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D247" s="1">
         <v>678.66666666666879</v>
@@ -7381,7 +7381,7 @@
         <v>2</v>
       </c>
       <c r="C248" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D248" s="1">
         <v>679.00000000000216</v>
@@ -7401,7 +7401,7 @@
         <v>2</v>
       </c>
       <c r="C249" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D249" s="1">
         <v>679.33333333333553</v>
@@ -7421,7 +7421,7 @@
         <v>2</v>
       </c>
       <c r="C250" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D250" s="1">
         <v>679.6666666666689</v>
@@ -7441,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="C251" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D251" s="1">
         <v>679.83333333333553</v>
@@ -7461,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="C252" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D252" s="1">
         <v>680.00000000000216</v>
@@ -7481,7 +7481,7 @@
         <v>1</v>
       </c>
       <c r="C253" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D253" s="1">
         <v>680.16666666666879</v>
@@ -7501,7 +7501,7 @@
         <v>1</v>
       </c>
       <c r="C254" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D254" s="1">
         <v>680.33333333333542</v>
@@ -7521,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="C255" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D255" s="1">
         <v>680.50000000000205</v>
@@ -7541,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="C256" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D256" s="1">
         <v>680.66666666666868</v>
@@ -7561,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="C257" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D257" s="1">
         <v>680.8333333333353</v>
@@ -7581,7 +7581,7 @@
         <v>1</v>
       </c>
       <c r="C258" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D258" s="1">
         <v>681.00000000000193</v>
@@ -7601,7 +7601,7 @@
         <v>1</v>
       </c>
       <c r="C259" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D259" s="1">
         <v>681.16666666666856</v>
@@ -7621,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="C260" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D260" s="1">
         <v>681.33333333333519</v>
@@ -7641,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="C261" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D261" s="1">
         <v>681.50000000000182</v>
@@ -7661,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="C262" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D262" s="1">
         <v>681.66666666666845</v>
@@ -7681,7 +7681,7 @@
         <v>1</v>
       </c>
       <c r="C263" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D263" s="1">
         <v>681.83333333333508</v>
@@ -7701,7 +7701,7 @@
         <v>1</v>
       </c>
       <c r="C264" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D264" s="1">
         <v>682.00000000000171</v>
@@ -7721,7 +7721,7 @@
         <v>1</v>
       </c>
       <c r="C265" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D265" s="1">
         <v>682.16666666666833</v>
@@ -7741,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="C266" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D266" s="1">
         <v>682.33333333333496</v>
@@ -7761,7 +7761,7 @@
         <v>1</v>
       </c>
       <c r="C267" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D267" s="1">
         <v>682.50000000000159</v>
@@ -7781,7 +7781,7 @@
         <v>1</v>
       </c>
       <c r="C268" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D268" s="1">
         <v>682.66666666666822</v>
@@ -7801,7 +7801,7 @@
         <v>1</v>
       </c>
       <c r="C269" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D269" s="1">
         <v>682.83333333333485</v>
@@ -7821,7 +7821,7 @@
         <v>1</v>
       </c>
       <c r="C270" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D270" s="1">
         <v>683.00000000000148</v>
@@ -7841,7 +7841,7 @@
         <v>1</v>
       </c>
       <c r="C271" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D271" s="1">
         <v>683.16666666666811</v>
@@ -7861,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="C272" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D272" s="1">
         <v>683.33333333333474</v>
@@ -7881,7 +7881,7 @@
         <v>1</v>
       </c>
       <c r="C273" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D273" s="1">
         <v>683.50000000000136</v>
@@ -7901,7 +7901,7 @@
         <v>1</v>
       </c>
       <c r="C274" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D274" s="1">
         <v>683.66666666666799</v>
@@ -7921,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="C275" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D275" s="1">
         <v>683.83333333333462</v>
@@ -7941,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="C276" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D276" s="1">
         <v>684.00000000000125</v>
@@ -7961,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="C277" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D277" s="1">
         <v>684.16666666666788</v>
@@ -7981,7 +7981,7 @@
         <v>1</v>
       </c>
       <c r="C278" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D278" s="1">
         <v>684.33333333333451</v>
@@ -8001,7 +8001,7 @@
         <v>1</v>
       </c>
       <c r="C279" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D279" s="1">
         <v>684.50000000000114</v>
@@ -8021,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="C280" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D280" s="1">
         <v>684.66666666666777</v>
@@ -8041,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="C281" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D281" s="1">
         <v>684.83333333333439</v>
@@ -8061,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="C282" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D282" s="1">
         <v>685.00000000000102</v>
@@ -8081,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="C283" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D283" s="1">
         <v>685.16666666666765</v>
@@ -8101,7 +8101,7 @@
         <v>1</v>
       </c>
       <c r="C284" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D284" s="1">
         <v>685.33333333333428</v>
@@ -8121,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="C285" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D285" s="1">
         <v>685.50000000000091</v>
@@ -8141,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="C286" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D286" s="1">
         <v>685.66666666666754</v>
@@ -8161,7 +8161,7 @@
         <v>1</v>
       </c>
       <c r="C287" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D287" s="1">
         <v>685.83333333333417</v>
@@ -8181,7 +8181,7 @@
         <v>1</v>
       </c>
       <c r="C288" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D288" s="1">
         <v>686.0000000000008</v>
@@ -8201,7 +8201,7 @@
         <v>1</v>
       </c>
       <c r="C289" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D289" s="1">
         <v>686.16666666666742</v>
@@ -8221,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="C290" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D290" s="1">
         <v>686.33333333333405</v>
@@ -8241,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="C291" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D291" s="1">
         <v>686.50000000000068</v>
@@ -8261,7 +8261,7 @@
         <v>1</v>
       </c>
       <c r="C292" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D292" s="1">
         <v>686.66666666666731</v>
@@ -8281,7 +8281,7 @@
         <v>1</v>
       </c>
       <c r="C293" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D293" s="1">
         <v>686.83333333333394</v>
@@ -8301,7 +8301,7 @@
         <v>1</v>
       </c>
       <c r="C294" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D294" s="1">
         <v>687.00000000000057</v>
@@ -8321,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="C295" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D295" s="1">
         <v>687.1666666666672</v>
@@ -8341,7 +8341,7 @@
         <v>1</v>
       </c>
       <c r="C296" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D296" s="1">
         <v>687.33333333333383</v>
@@ -8361,7 +8361,7 @@
         <v>1</v>
       </c>
       <c r="C297" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D297" s="1">
         <v>687.50000000000045</v>
@@ -8381,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="C298" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D298" s="1">
         <v>687.66666666666708</v>
@@ -8401,7 +8401,7 @@
         <v>1</v>
       </c>
       <c r="C299" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D299" s="1">
         <v>687.83333333333371</v>
@@ -8421,7 +8421,7 @@
         <v>1</v>
       </c>
       <c r="C300" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D300" s="1">
         <v>688.00000000000034</v>
@@ -8441,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="C301" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D301" s="1">
         <v>688.16666666666697</v>
@@ -8461,7 +8461,7 @@
         <v>1</v>
       </c>
       <c r="C302" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D302" s="1">
         <v>688.3333333333336</v>
@@ -8481,7 +8481,7 @@
         <v>1</v>
       </c>
       <c r="C303" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D303" s="1">
         <v>688.50000000000023</v>
@@ -8501,7 +8501,7 @@
         <v>1</v>
       </c>
       <c r="C304" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D304" s="1">
         <v>688.66666666666686</v>
@@ -8521,7 +8521,7 @@
         <v>1</v>
       </c>
       <c r="C305" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D305" s="1">
         <v>688.83333333333348</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="C306" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D306" s="1">
         <v>689.00000000000011</v>
@@ -8561,7 +8561,7 @@
         <v>1</v>
       </c>
       <c r="C307" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D307" s="1">
         <v>689.16666666666674</v>
@@ -8581,7 +8581,7 @@
         <v>1</v>
       </c>
       <c r="C308" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D308" s="1">
         <v>689.33333333333337</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="C309" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D309" s="1">
         <v>689.5</v>
@@ -8621,7 +8621,7 @@
         <v>1</v>
       </c>
       <c r="C310" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D310" s="1">
         <v>689.66666666666663</v>
@@ -8641,7 +8641,7 @@
         <v>1</v>
       </c>
       <c r="C311" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D311" s="1">
         <v>689.83333333333326</v>
@@ -8661,7 +8661,7 @@
         <v>1</v>
       </c>
       <c r="C312" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D312" s="1">
         <v>689.99999999999989</v>
@@ -8681,7 +8681,7 @@
         <v>1</v>
       </c>
       <c r="C313" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D313" s="1">
         <v>690.16666666666652</v>
@@ -8701,7 +8701,7 @@
         <v>1</v>
       </c>
       <c r="C314" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D314" s="1">
         <v>690.33333333333314</v>
@@ -8721,7 +8721,7 @@
         <v>1</v>
       </c>
       <c r="C315" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D315" s="1">
         <v>690.49999999999977</v>
@@ -8741,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="C316" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D316" s="1">
         <v>690.6666666666664</v>
@@ -8761,7 +8761,7 @@
         <v>1</v>
       </c>
       <c r="C317" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D317" s="1">
         <v>690.83333333333303</v>
@@ -8781,7 +8781,7 @@
         <v>1</v>
       </c>
       <c r="C318" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D318" s="1">
         <v>690.99999999999966</v>
@@ -8801,7 +8801,7 @@
         <v>1</v>
       </c>
       <c r="C319" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D319" s="1">
         <v>691.16666666666629</v>
@@ -8821,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="C320" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D320" s="1">
         <v>691.33333333333292</v>
@@ -8841,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="C321" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D321" s="1">
         <v>691.49999999999955</v>
@@ -8861,7 +8861,7 @@
         <v>1</v>
       </c>
       <c r="C322" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D322" s="1">
         <v>691.66666666666617</v>
@@ -8881,7 +8881,7 @@
         <v>1</v>
       </c>
       <c r="C323" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D323" s="1">
         <v>691.8333333333328</v>
@@ -8901,7 +8901,7 @@
         <v>1</v>
       </c>
       <c r="C324" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D324" s="1">
         <v>691.99999999999943</v>
@@ -8921,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="C325" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D325" s="1">
         <v>692.16666666666606</v>
@@ -8941,7 +8941,7 @@
         <v>1</v>
       </c>
       <c r="C326" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D326" s="1">
         <v>692.33333333333269</v>
@@ -8961,7 +8961,7 @@
         <v>1</v>
       </c>
       <c r="C327" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D327" s="1">
         <v>692.49999999999932</v>
@@ -8981,7 +8981,7 @@
         <v>1</v>
       </c>
       <c r="C328" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D328" s="1">
         <v>692.66666666666595</v>
@@ -9001,7 +9001,7 @@
         <v>1</v>
       </c>
       <c r="C329" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D329" s="1">
         <v>692.83333333333258</v>
@@ -9021,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="C330" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D330" s="1">
         <v>692.9999999999992</v>
@@ -9041,7 +9041,7 @@
         <v>1</v>
       </c>
       <c r="C331" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D331" s="1">
         <v>693.16666666666583</v>
@@ -9061,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="C332" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D332" s="1">
         <v>693.33333333333246</v>
@@ -9081,7 +9081,7 @@
         <v>1</v>
       </c>
       <c r="C333" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D333" s="1">
         <v>693.49999999999909</v>
@@ -9101,7 +9101,7 @@
         <v>1</v>
       </c>
       <c r="C334" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D334" s="1">
         <v>693.66666666666572</v>
@@ -9121,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="C335" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D335" s="1">
         <v>693.83333333333235</v>
@@ -9141,7 +9141,7 @@
         <v>1</v>
       </c>
       <c r="C336" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D336" s="1">
         <v>693.99999999999898</v>
@@ -9161,7 +9161,7 @@
         <v>1</v>
       </c>
       <c r="C337" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D337" s="1">
         <v>694.16666666666561</v>
@@ -9181,7 +9181,7 @@
         <v>1</v>
       </c>
       <c r="C338" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D338" s="1">
         <v>694.33333333333223</v>
@@ -9201,7 +9201,7 @@
         <v>1</v>
       </c>
       <c r="C339" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D339" s="1">
         <v>694.49999999999886</v>
@@ -9221,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="C340" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D340" s="1">
         <v>694.66666666666549</v>
@@ -9241,7 +9241,7 @@
         <v>1</v>
       </c>
       <c r="C341" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D341" s="1">
         <v>694.83333333333212</v>
@@ -9261,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="C342" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D342" s="1">
         <v>694.99999999999875</v>
@@ -9281,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="C343" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D343" s="1">
         <v>695.16666666666538</v>
@@ -9301,7 +9301,7 @@
         <v>1</v>
       </c>
       <c r="C344" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D344" s="1">
         <v>695.33333333333201</v>
@@ -9321,7 +9321,7 @@
         <v>1</v>
       </c>
       <c r="C345" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D345" s="1">
         <v>695.49999999999864</v>
@@ -9341,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="C346" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D346" s="1">
         <v>695.66666666666526</v>
@@ -9361,7 +9361,7 @@
         <v>1</v>
       </c>
       <c r="C347" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D347" s="1">
         <v>695.83333333333189</v>
@@ -9381,7 +9381,7 @@
         <v>1</v>
       </c>
       <c r="C348" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D348" s="1">
         <v>695.99999999999852</v>
@@ -9401,7 +9401,7 @@
         <v>1</v>
       </c>
       <c r="C349" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D349" s="1">
         <v>696.16666666666515</v>
@@ -9421,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="C350" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D350" s="1">
         <v>696.33333333333178</v>
@@ -9441,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="C351" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D351" s="1">
         <v>696.49999999999841</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="C352" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D352" s="1">
         <v>696.66666666666504</v>
@@ -9481,7 +9481,7 @@
         <v>1</v>
       </c>
       <c r="C353" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D353" s="1">
         <v>696.83333333333167</v>
@@ -9501,7 +9501,7 @@
         <v>1</v>
       </c>
       <c r="C354" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D354" s="1">
         <v>696.99999999999829</v>
@@ -9521,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="C355" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D355" s="1">
         <v>697.16666666666492</v>
@@ -9541,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="C356" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D356" s="1">
         <v>697.33333333333155</v>
@@ -9561,7 +9561,7 @@
         <v>1</v>
       </c>
       <c r="C357" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D357" s="1">
         <v>697.49999999999818</v>
@@ -9581,7 +9581,7 @@
         <v>1</v>
       </c>
       <c r="C358" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D358" s="1">
         <v>697.66666666666481</v>
@@ -9601,7 +9601,7 @@
         <v>1</v>
       </c>
       <c r="C359" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D359" s="1">
         <v>697.83333333333144</v>
@@ -9621,7 +9621,7 @@
         <v>1</v>
       </c>
       <c r="C360" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D360" s="1">
         <v>697.99999999999807</v>
@@ -9641,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="C361" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D361" s="1">
         <v>698.1666666666647</v>
@@ -9661,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="C362" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D362" s="1">
         <v>698.33333333333132</v>
@@ -9681,7 +9681,7 @@
         <v>1</v>
       </c>
       <c r="C363" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D363" s="1">
         <v>698.49999999999795</v>
@@ -9701,7 +9701,7 @@
         <v>1</v>
       </c>
       <c r="C364" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D364" s="1">
         <v>698.66666666666458</v>
@@ -9721,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="C365" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D365" s="1">
         <v>698.83333333333121</v>
@@ -9741,7 +9741,7 @@
         <v>1</v>
       </c>
       <c r="C366" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D366" s="1">
         <v>698.99999999999784</v>
@@ -9761,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="C367" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D367" s="1">
         <v>699.16666666666447</v>
@@ -9781,7 +9781,7 @@
         <v>1</v>
       </c>
       <c r="C368" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D368" s="1">
         <v>699.3333333333311</v>
@@ -9801,7 +9801,7 @@
         <v>1</v>
       </c>
       <c r="C369" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D369" s="1">
         <v>699.49999999999773</v>
@@ -9821,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="C370" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D370" s="1">
         <v>699.66666666666436</v>
@@ -9841,7 +9841,7 @@
         <v>1</v>
       </c>
       <c r="C371" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D371" s="1">
         <v>699.83333333333098</v>
@@ -9861,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="C372" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D372" s="1">
         <v>699.99999999999761</v>
@@ -9881,7 +9881,7 @@
         <v>1</v>
       </c>
       <c r="C373" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D373" s="1">
         <v>700.16666666666424</v>
@@ -9901,7 +9901,7 @@
         <v>1</v>
       </c>
       <c r="C374" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D374" s="1">
         <v>700.33333333333087</v>
@@ -9921,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="C375" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D375" s="1">
         <v>700.4999999999975</v>
@@ -9941,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="C376" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D376" s="1">
         <v>700.66666666666413</v>
@@ -9961,7 +9961,7 @@
         <v>1</v>
       </c>
       <c r="C377" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D377" s="1">
         <v>700.83333333333076</v>
@@ -9981,7 +9981,7 @@
         <v>1</v>
       </c>
       <c r="C378" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D378" s="1">
         <v>700.99999999999739</v>
@@ -10001,7 +10001,7 @@
         <v>1</v>
       </c>
       <c r="C379" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D379" s="1">
         <v>701.16666666666401</v>
@@ -10021,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="C380" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D380" s="1">
         <v>701.33333333333064</v>
@@ -10041,7 +10041,7 @@
         <v>1</v>
       </c>
       <c r="C381" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D381" s="1">
         <v>701.49999999999727</v>
@@ -10061,7 +10061,7 @@
         <v>1</v>
       </c>
       <c r="C382" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D382" s="1">
         <v>701.6666666666639</v>
@@ -10081,7 +10081,7 @@
         <v>1</v>
       </c>
       <c r="C383" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D383" s="1">
         <v>701.83333333333053</v>
@@ -10101,7 +10101,7 @@
         <v>1</v>
       </c>
       <c r="C384" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D384" s="1">
         <v>701.99999999999716</v>
@@ -10121,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="C385" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D385" s="1">
         <v>702.16666666666379</v>
@@ -10141,7 +10141,7 @@
         <v>1</v>
       </c>
       <c r="C386" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D386" s="1">
         <v>702.33333333333042</v>
@@ -10161,7 +10161,7 @@
         <v>1</v>
       </c>
       <c r="C387" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D387" s="1">
         <v>702.49999999999704</v>
@@ -10181,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="C388" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D388" s="1">
         <v>702.66666666666367</v>
@@ -10201,7 +10201,7 @@
         <v>1</v>
       </c>
       <c r="C389" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D389" s="1">
         <v>702.8333333333303</v>
@@ -10221,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="C390" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D390" s="1">
         <v>702.99999999999693</v>
@@ -10241,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="C391" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D391" s="1">
         <v>703.16666666666356</v>
@@ -10261,7 +10261,7 @@
         <v>1</v>
       </c>
       <c r="C392" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D392" s="1">
         <v>703.33333333333019</v>
@@ -10281,7 +10281,7 @@
         <v>1</v>
       </c>
       <c r="C393" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D393" s="1">
         <v>703.49999999999682</v>
@@ -10301,7 +10301,7 @@
         <v>1</v>
       </c>
       <c r="C394" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D394" s="1">
         <v>703.66666666666345</v>
@@ -10321,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="C395" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D395" s="1">
         <v>703.83333333333007</v>
@@ -10341,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="C396" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D396" s="1">
         <v>703.9999999999967</v>
@@ -10361,7 +10361,7 @@
         <v>1</v>
       </c>
       <c r="C397" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D397" s="1">
         <v>704.16666666666333</v>
@@ -10381,7 +10381,7 @@
         <v>1</v>
       </c>
       <c r="C398" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D398" s="1">
         <v>704.33333333332996</v>
@@ -10401,7 +10401,7 @@
         <v>1</v>
       </c>
       <c r="C399" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D399" s="1">
         <v>704.49999999999659</v>
@@ -10421,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="C400" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D400" s="1">
         <v>704.66666666666322</v>
@@ -10441,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="C401" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D401" s="1">
         <v>704.83333333332985</v>
@@ -10461,7 +10461,7 @@
         <v>1</v>
       </c>
       <c r="C402" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D402" s="1">
         <v>704.99999999999648</v>
@@ -10481,7 +10481,7 @@
         <v>1</v>
       </c>
       <c r="C403" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D403" s="1">
         <v>705.1666666666631</v>
@@ -10501,7 +10501,7 @@
         <v>1</v>
       </c>
       <c r="C404" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D404" s="1">
         <v>705.33333333332973</v>
@@ -10521,7 +10521,7 @@
         <v>1</v>
       </c>
       <c r="C405" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D405" s="1">
         <v>705.49999999999636</v>
@@ -10541,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="C406" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D406" s="1">
         <v>705.66666666666299</v>
@@ -10561,7 +10561,7 @@
         <v>1</v>
       </c>
       <c r="C407" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D407" s="1">
         <v>705.83333333332962</v>
@@ -10581,7 +10581,7 @@
         <v>1</v>
       </c>
       <c r="C408" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D408" s="1">
         <v>705.99999999999625</v>
@@ -10601,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="C409" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D409" s="1">
         <v>706.16666666666288</v>
@@ -10621,7 +10621,7 @@
         <v>1</v>
       </c>
       <c r="C410" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D410" s="1">
         <v>706.33333333332951</v>
@@ -10641,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="C411" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D411" s="1">
         <v>706.49999999999613</v>
@@ -10661,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="C412" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D412" s="1">
         <v>706.66666666666276</v>
@@ -10681,7 +10681,7 @@
         <v>1</v>
       </c>
       <c r="C413" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D413" s="1">
         <v>706.83333333332939</v>
@@ -10701,7 +10701,7 @@
         <v>1</v>
       </c>
       <c r="C414" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D414" s="1">
         <v>706.99999999999602</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="C415" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D415" s="1">
         <v>707.16666666666265</v>
@@ -10741,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="C416" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D416" s="1">
         <v>707.33333333332928</v>
@@ -10761,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="C417" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D417" s="1">
         <v>707.49999999999591</v>
@@ -10781,7 +10781,7 @@
         <v>1</v>
       </c>
       <c r="C418" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D418" s="1">
         <v>707.66666666666254</v>
@@ -10801,7 +10801,7 @@
         <v>1</v>
       </c>
       <c r="C419" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D419" s="1">
         <v>707.83333333332916</v>
@@ -10821,7 +10821,7 @@
         <v>1</v>
       </c>
       <c r="C420" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D420" s="1">
         <v>707.99999999999579</v>
@@ -10841,7 +10841,7 @@
         <v>1</v>
       </c>
       <c r="C421" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D421" s="1">
         <v>708.16666666666242</v>
@@ -10861,7 +10861,7 @@
         <v>1</v>
       </c>
       <c r="C422" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D422" s="1">
         <v>708.33333333332905</v>
@@ -10881,7 +10881,7 @@
         <v>1</v>
       </c>
       <c r="C423" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D423" s="1">
         <v>708.49999999999568</v>
@@ -10901,7 +10901,7 @@
         <v>1</v>
       </c>
       <c r="C424" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D424" s="1">
         <v>708.66666666666231</v>
@@ -10921,7 +10921,7 @@
         <v>1</v>
       </c>
       <c r="C425" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D425" s="1">
         <v>708.83333333332894</v>
@@ -10941,7 +10941,7 @@
         <v>1</v>
       </c>
       <c r="C426" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D426" s="1">
         <v>708.99999999999557</v>
@@ -10961,7 +10961,7 @@
         <v>1</v>
       </c>
       <c r="C427" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D427" s="1">
         <v>709.16666666666219</v>
@@ -10981,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="C428" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D428" s="1">
         <v>709.33333333332882</v>
@@ -11001,7 +11001,7 @@
         <v>1</v>
       </c>
       <c r="C429" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D429" s="1">
         <v>709.49999999999545</v>
@@ -11021,7 +11021,7 @@
         <v>1</v>
       </c>
       <c r="C430" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D430" s="1">
         <v>709.66666666666208</v>
@@ -11041,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="C431" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D431" s="1">
         <v>709.83333333332871</v>
@@ -11061,7 +11061,7 @@
         <v>1</v>
       </c>
       <c r="C432" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D432" s="1">
         <v>709.99999999999534</v>
@@ -11081,7 +11081,7 @@
         <v>1</v>
       </c>
       <c r="C433" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D433" s="1">
         <v>710.16666666666197</v>
@@ -11101,7 +11101,7 @@
         <v>1</v>
       </c>
       <c r="C434" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D434" s="1">
         <v>710.3333333333286</v>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="C435" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D435" s="1">
         <v>710.49999999999523</v>
@@ -11141,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="C436" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D436" s="1">
         <v>710.66666666666185</v>
@@ -11161,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="C437" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D437" s="1">
         <v>710.83333333332848</v>
@@ -11181,7 +11181,7 @@
         <v>1</v>
       </c>
       <c r="C438" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D438" s="1">
         <v>710.99999999999511</v>
@@ -11201,7 +11201,7 @@
         <v>1</v>
       </c>
       <c r="C439" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D439" s="1">
         <v>711.16666666666174</v>
@@ -11221,7 +11221,7 @@
         <v>1</v>
       </c>
       <c r="C440" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D440" s="1">
         <v>711.33333333332837</v>
@@ -11241,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="C441" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D441" s="1">
         <v>711.499999999995</v>
@@ -11261,7 +11261,7 @@
         <v>1</v>
       </c>
       <c r="C442" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D442" s="1">
         <v>711.66666666666163</v>
@@ -11281,7 +11281,7 @@
         <v>1</v>
       </c>
       <c r="C443" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D443" s="1">
         <v>711.83333333332826</v>
@@ -11301,7 +11301,7 @@
         <v>1</v>
       </c>
       <c r="C444" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D444" s="1">
         <v>711.99999999999488</v>
@@ -11321,7 +11321,7 @@
         <v>1</v>
       </c>
       <c r="C445" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D445" s="1">
         <v>712.16666666666151</v>
@@ -11341,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="C446" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D446" s="1">
         <v>712.33333333332814</v>
@@ -11361,7 +11361,7 @@
         <v>1</v>
       </c>
       <c r="C447" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D447" s="1">
         <v>712.49999999999477</v>
@@ -11381,7 +11381,7 @@
         <v>1</v>
       </c>
       <c r="C448" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D448" s="1">
         <v>712.6666666666614</v>
@@ -11401,7 +11401,7 @@
         <v>1</v>
       </c>
       <c r="C449" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D449" s="1">
         <v>712.83333333332803</v>
@@ -11421,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="C450" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D450" s="1">
         <v>712.99999999999466</v>
@@ -11441,7 +11441,7 @@
         <v>1</v>
       </c>
       <c r="C451" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D451" s="1">
         <v>713.16666666666129</v>
@@ -11461,7 +11461,7 @@
         <v>1</v>
       </c>
       <c r="C452" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D452" s="1">
         <v>713.33333333332791</v>
@@ -11481,7 +11481,7 @@
         <v>1</v>
       </c>
       <c r="C453" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D453" s="1">
         <v>713.49999999999454</v>
@@ -11501,7 +11501,7 @@
         <v>1</v>
       </c>
       <c r="C454" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D454" s="1">
         <v>713.66666666666117</v>
@@ -11521,7 +11521,7 @@
         <v>1</v>
       </c>
       <c r="C455" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D455" s="1">
         <v>713.8333333333278</v>
@@ -11541,7 +11541,7 @@
         <v>1</v>
       </c>
       <c r="C456" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D456" s="1">
         <v>713.99999999999443</v>
@@ -11561,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="C457" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D457" s="1">
         <v>714.16666666666106</v>
@@ -11581,7 +11581,7 @@
         <v>1</v>
       </c>
       <c r="C458" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D458" s="1">
         <v>714.33333333332769</v>
@@ -11601,7 +11601,7 @@
         <v>1</v>
       </c>
       <c r="C459" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D459" s="1">
         <v>714.49999999999432</v>
@@ -11621,7 +11621,7 @@
         <v>1</v>
       </c>
       <c r="C460" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D460" s="1">
         <v>714.66666666666094</v>
@@ -11641,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="C461" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D461" s="1">
         <v>714.83333333332757</v>
@@ -11661,7 +11661,7 @@
         <v>1</v>
       </c>
       <c r="C462" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D462" s="1">
         <v>714.9999999999942</v>
@@ -11681,7 +11681,7 @@
         <v>1</v>
       </c>
       <c r="C463" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D463" s="1">
         <v>715.16666666666083</v>
@@ -11701,7 +11701,7 @@
         <v>1</v>
       </c>
       <c r="C464" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D464" s="1">
         <v>715.33333333332746</v>
@@ -11721,7 +11721,7 @@
         <v>1</v>
       </c>
       <c r="C465" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D465" s="1">
         <v>715.49999999999409</v>
@@ -11741,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="C466" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D466" s="1">
         <v>715.66666666666072</v>
@@ -11761,7 +11761,7 @@
         <v>1</v>
       </c>
       <c r="C467" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D467" s="1">
         <v>715.83333333332735</v>
@@ -11781,7 +11781,7 @@
         <v>1</v>
       </c>
       <c r="C468" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D468" s="1">
         <v>715.99999999999397</v>
@@ -11801,7 +11801,7 @@
         <v>1</v>
       </c>
       <c r="C469" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D469" s="1">
         <v>716.1666666666606</v>
@@ -11821,7 +11821,7 @@
         <v>1</v>
       </c>
       <c r="C470" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D470" s="1">
         <v>716.33333333332723</v>
@@ -11841,7 +11841,7 @@
         <v>1</v>
       </c>
       <c r="C471" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D471" s="1">
         <v>716.49999999999386</v>
@@ -11861,7 +11861,7 @@
         <v>1</v>
       </c>
       <c r="C472" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D472" s="1">
         <v>716.66666666666049</v>
@@ -11881,7 +11881,7 @@
         <v>1</v>
       </c>
       <c r="C473" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D473" s="1">
         <v>716.83333333332712</v>
@@ -11901,7 +11901,7 @@
         <v>1</v>
       </c>
       <c r="C474" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D474" s="1">
         <v>716.99999999999375</v>
@@ -11921,7 +11921,7 @@
         <v>1</v>
       </c>
       <c r="C475" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D475" s="1">
         <v>717.16666666666038</v>
@@ -11941,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="C476" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D476" s="1">
         <v>717.333333333327</v>
@@ -11961,7 +11961,7 @@
         <v>1</v>
       </c>
       <c r="C477" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D477" s="1">
         <v>717.49999999999363</v>
@@ -11981,7 +11981,7 @@
         <v>1</v>
       </c>
       <c r="C478" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D478" s="1">
         <v>717.66666666666026</v>
@@ -12001,7 +12001,7 @@
         <v>1</v>
       </c>
       <c r="C479" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D479" s="1">
         <v>717.83333333332689</v>
@@ -12021,7 +12021,7 @@
         <v>1</v>
       </c>
       <c r="C480" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D480" s="1">
         <v>717.99999999999352</v>
@@ -12041,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="C481" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D481" s="1">
         <v>718.16666666666015</v>
@@ -12061,7 +12061,7 @@
         <v>1</v>
       </c>
       <c r="C482" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D482" s="1">
         <v>718.33333333332678</v>
@@ -12081,7 +12081,7 @@
         <v>1</v>
       </c>
       <c r="C483" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D483" s="1">
         <v>718.49999999999341</v>
@@ -12101,7 +12101,7 @@
         <v>1</v>
       </c>
       <c r="C484" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D484" s="1">
         <v>718.66666666666003</v>
@@ -12121,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="C485" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D485" s="1">
         <v>718.83333333332666</v>
@@ -12141,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="C486" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D486" s="1">
         <v>718.99999999999329</v>
@@ -12161,7 +12161,7 @@
         <v>1</v>
       </c>
       <c r="C487" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D487" s="1">
         <v>719.16666666665992</v>
@@ -12181,7 +12181,7 @@
         <v>1</v>
       </c>
       <c r="C488" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D488" s="1">
         <v>719.33333333332655</v>
@@ -12201,7 +12201,7 @@
         <v>1</v>
       </c>
       <c r="C489" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D489" s="1">
         <v>719.49999999999318</v>
@@ -12221,7 +12221,7 @@
         <v>1</v>
       </c>
       <c r="C490" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D490" s="1">
         <v>719.66666666665981</v>
@@ -12241,7 +12241,7 @@
         <v>1</v>
       </c>
       <c r="C491" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D491" s="1">
         <v>719.83333333332644</v>
@@ -12261,7 +12261,7 @@
         <v>1</v>
       </c>
       <c r="C492" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D492" s="1">
         <v>719.99999999999307</v>
@@ -12281,7 +12281,7 @@
         <v>1</v>
       </c>
       <c r="C493" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D493" s="1">
         <v>720.16666666665969</v>
@@ -12301,7 +12301,7 @@
         <v>1</v>
       </c>
       <c r="C494" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D494" s="1">
         <v>720.33333333332632</v>
@@ -12321,7 +12321,7 @@
         <v>1</v>
       </c>
       <c r="C495" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D495" s="1">
         <v>720.49999999999295</v>
@@ -12341,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="C496" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D496" s="1">
         <v>720.66666666665958</v>
@@ -12361,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="C497" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D497" s="1">
         <v>720.83333333332621</v>
@@ -12381,7 +12381,7 @@
         <v>1</v>
       </c>
       <c r="C498" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D498" s="1">
         <v>720.99999999999284</v>
@@ -12401,7 +12401,7 @@
         <v>1</v>
       </c>
       <c r="C499" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D499" s="1">
         <v>721.16666666665947</v>
@@ -12421,7 +12421,7 @@
         <v>1</v>
       </c>
       <c r="C500" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D500" s="1">
         <v>721.3333333333261</v>
@@ -12441,7 +12441,7 @@
         <v>1</v>
       </c>
       <c r="C501" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D501" s="1">
         <v>721.49999999999272</v>
@@ -12461,7 +12461,7 @@
         <v>1</v>
       </c>
       <c r="C502" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D502" s="1">
         <v>721.66666666665935</v>
@@ -12481,7 +12481,7 @@
         <v>1</v>
       </c>
       <c r="C503" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D503" s="1">
         <v>721.83333333332598</v>
@@ -12501,7 +12501,7 @@
         <v>1</v>
       </c>
       <c r="C504" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D504" s="1">
         <v>721.99999999999261</v>
@@ -12521,7 +12521,7 @@
         <v>1</v>
       </c>
       <c r="C505" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D505" s="1">
         <v>722.16666666665924</v>
@@ -12541,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="C506" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D506" s="1">
         <v>722.33333333332587</v>
@@ -12561,7 +12561,7 @@
         <v>1</v>
       </c>
       <c r="C507" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D507" s="1">
         <v>722.4999999999925</v>
@@ -12581,7 +12581,7 @@
         <v>1</v>
       </c>
       <c r="C508" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D508" s="1">
         <v>722.66666666665913</v>
@@ -12601,7 +12601,7 @@
         <v>1</v>
       </c>
       <c r="C509" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D509" s="1">
         <v>722.83333333332575</v>
@@ -12621,7 +12621,7 @@
         <v>1</v>
       </c>
       <c r="C510" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D510" s="1">
         <v>722.99999999999238</v>
@@ -12641,7 +12641,7 @@
         <v>1</v>
       </c>
       <c r="C511" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D511" s="1">
         <v>723.16666666665901</v>
@@ -12661,7 +12661,7 @@
         <v>1</v>
       </c>
       <c r="C512" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D512" s="1">
         <v>723.33333333332564</v>
@@ -12681,7 +12681,7 @@
         <v>1</v>
       </c>
       <c r="C513" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D513" s="1">
         <v>723.49999999999227</v>
@@ -12701,7 +12701,7 @@
         <v>1</v>
       </c>
       <c r="C514" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D514" s="1">
         <v>723.6666666666589</v>
@@ -12721,7 +12721,7 @@
         <v>1</v>
       </c>
       <c r="C515" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D515" s="1">
         <v>723.83333333332553</v>
@@ -12770,7 +12770,7 @@
         <v>2645</v>
       </c>
       <c r="C2">
-        <v>440.83333333333331</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -12781,7 +12781,7 @@
         <v>1415</v>
       </c>
       <c r="C3">
-        <v>235.83333333333334</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -12792,7 +12792,7 @@
         <v>652</v>
       </c>
       <c r="C4">
-        <v>108.66666666666667</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -12814,7 +12814,7 @@
         <v>625</v>
       </c>
       <c r="C6">
-        <v>104.16666666666667</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -12825,7 +12825,7 @@
         <v>614</v>
       </c>
       <c r="C7">
-        <v>102.33333333333333</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -12836,7 +12836,7 @@
         <v>335</v>
       </c>
       <c r="C8">
-        <v>55.833333333333336</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -12847,7 +12847,7 @@
         <v>287</v>
       </c>
       <c r="C9">
-        <v>47.833333333333336</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -12869,7 +12869,7 @@
         <v>190</v>
       </c>
       <c r="C11">
-        <v>31.666666666666668</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -12880,7 +12880,7 @@
         <v>185</v>
       </c>
       <c r="C12">
-        <v>30.833333333333332</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -12891,7 +12891,7 @@
         <v>135</v>
       </c>
       <c r="C13">
-        <v>22.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -12902,7 +12902,7 @@
         <v>113</v>
       </c>
       <c r="C14">
-        <v>18.833333333333332</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -12913,7 +12913,7 @@
         <v>109</v>
       </c>
       <c r="C15">
-        <v>18.166666666666668</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -12924,7 +12924,7 @@
         <v>103</v>
       </c>
       <c r="C16">
-        <v>17.166666666666668</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -12946,7 +12946,7 @@
         <v>89</v>
       </c>
       <c r="C18">
-        <v>14.833333333333334</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -12957,7 +12957,7 @@
         <v>83</v>
       </c>
       <c r="C19">
-        <v>13.833333333333334</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -12968,7 +12968,7 @@
         <v>81</v>
       </c>
       <c r="C20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -12979,7 +12979,7 @@
         <v>79</v>
       </c>
       <c r="C21">
-        <v>13.166666666666666</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -13001,7 +13001,7 @@
         <v>69</v>
       </c>
       <c r="C23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -13012,7 +13012,7 @@
         <v>67</v>
       </c>
       <c r="C24">
-        <v>11.166666666666666</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -13034,7 +13034,7 @@
         <v>65</v>
       </c>
       <c r="C26">
-        <v>10.833333333333334</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -13045,7 +13045,7 @@
         <v>61</v>
       </c>
       <c r="C27">
-        <v>10.166666666666666</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -13056,7 +13056,7 @@
         <v>61</v>
       </c>
       <c r="C28">
-        <v>10.166666666666666</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -13067,7 +13067,7 @@
         <v>59</v>
       </c>
       <c r="C29">
-        <v>9.8333333333333339</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -13078,7 +13078,7 @@
         <v>56</v>
       </c>
       <c r="C30">
-        <v>9.3333333333333339</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -13089,7 +13089,7 @@
         <v>55</v>
       </c>
       <c r="C31">
-        <v>9.1666666666666661</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -13100,7 +13100,7 @@
         <v>50</v>
       </c>
       <c r="C32">
-        <v>8.3333333333333339</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -13111,7 +13111,7 @@
         <v>49</v>
       </c>
       <c r="C33">
-        <v>8.1666666666666661</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -13122,7 +13122,7 @@
         <v>49</v>
       </c>
       <c r="C34">
-        <v>8.1666666666666661</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
         <v>43</v>
       </c>
       <c r="C35">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -13144,7 +13144,7 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -13155,7 +13155,7 @@
         <v>43</v>
       </c>
       <c r="C37">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -13188,7 +13188,7 @@
         <v>41</v>
       </c>
       <c r="C40">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -13199,7 +13199,7 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>6.666666666666667</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -13210,7 +13210,7 @@
         <v>39</v>
       </c>
       <c r="C42">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -13221,7 +13221,7 @@
         <v>38</v>
       </c>
       <c r="C43">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -13232,7 +13232,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -13243,7 +13243,7 @@
         <v>37</v>
       </c>
       <c r="C45">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -13265,7 +13265,7 @@
         <v>35</v>
       </c>
       <c r="C47">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -13276,7 +13276,7 @@
         <v>31</v>
       </c>
       <c r="C48">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -13287,7 +13287,7 @@
         <v>31</v>
       </c>
       <c r="C49">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -13331,7 +13331,7 @@
         <v>29</v>
       </c>
       <c r="C53">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -13342,7 +13342,7 @@
         <v>29</v>
       </c>
       <c r="C54">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -13353,7 +13353,7 @@
         <v>28</v>
       </c>
       <c r="C55">
-        <v>4.666666666666667</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -13364,7 +13364,7 @@
         <v>27</v>
       </c>
       <c r="C56">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -13375,7 +13375,7 @@
         <v>26</v>
       </c>
       <c r="C57">
-        <v>4.333333333333333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -13386,7 +13386,7 @@
         <v>25</v>
       </c>
       <c r="C58">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -13397,7 +13397,7 @@
         <v>25</v>
       </c>
       <c r="C59">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -13430,7 +13430,7 @@
         <v>23</v>
       </c>
       <c r="C62">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -13441,7 +13441,7 @@
         <v>23</v>
       </c>
       <c r="C63">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -13452,7 +13452,7 @@
         <v>22</v>
       </c>
       <c r="C64">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -13463,7 +13463,7 @@
         <v>22</v>
       </c>
       <c r="C65">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -13474,7 +13474,7 @@
         <v>22</v>
       </c>
       <c r="C66">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -13485,7 +13485,7 @@
         <v>22</v>
       </c>
       <c r="C67">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -13496,7 +13496,7 @@
         <v>22</v>
       </c>
       <c r="C68">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -13507,7 +13507,7 @@
         <v>21</v>
       </c>
       <c r="C69">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -13518,7 +13518,7 @@
         <v>20</v>
       </c>
       <c r="C70">
-        <v>3.3333333333333335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -13529,7 +13529,7 @@
         <v>17</v>
       </c>
       <c r="C71">
-        <v>2.8333333333333335</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -13540,7 +13540,7 @@
         <v>16</v>
       </c>
       <c r="C72">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -13551,7 +13551,7 @@
         <v>16</v>
       </c>
       <c r="C73">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -13562,7 +13562,7 @@
         <v>15</v>
       </c>
       <c r="C74">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -13573,7 +13573,7 @@
         <v>14</v>
       </c>
       <c r="C75">
-        <v>2.3333333333333335</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -13584,7 +13584,7 @@
         <v>13</v>
       </c>
       <c r="C76">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -13595,7 +13595,7 @@
         <v>13</v>
       </c>
       <c r="C77">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -13606,7 +13606,7 @@
         <v>13</v>
       </c>
       <c r="C78">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -13650,7 +13650,7 @@
         <v>11</v>
       </c>
       <c r="C82">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -13661,7 +13661,7 @@
         <v>11</v>
       </c>
       <c r="C83">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -13672,7 +13672,7 @@
         <v>11</v>
       </c>
       <c r="C84">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -13683,7 +13683,7 @@
         <v>11</v>
       </c>
       <c r="C85">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -13694,7 +13694,7 @@
         <v>11</v>
       </c>
       <c r="C86">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -13705,7 +13705,7 @@
         <v>11</v>
       </c>
       <c r="C87">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -13716,7 +13716,7 @@
         <v>10</v>
       </c>
       <c r="C88">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -13727,7 +13727,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -13738,7 +13738,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -13749,7 +13749,7 @@
         <v>9</v>
       </c>
       <c r="C91">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -13760,7 +13760,7 @@
         <v>9</v>
       </c>
       <c r="C92">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -13771,7 +13771,7 @@
         <v>9</v>
       </c>
       <c r="C93">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -13782,7 +13782,7 @@
         <v>9</v>
       </c>
       <c r="C94">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -13793,7 +13793,7 @@
         <v>9</v>
       </c>
       <c r="C95">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -13804,7 +13804,7 @@
         <v>9</v>
       </c>
       <c r="C96">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -13815,7 +13815,7 @@
         <v>9</v>
       </c>
       <c r="C97">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -13826,7 +13826,7 @@
         <v>9</v>
       </c>
       <c r="C98">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -13837,7 +13837,7 @@
         <v>9</v>
       </c>
       <c r="C99">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -13848,7 +13848,7 @@
         <v>8</v>
       </c>
       <c r="C100">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -13859,7 +13859,7 @@
         <v>8</v>
       </c>
       <c r="C101">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -13870,7 +13870,7 @@
         <v>8</v>
       </c>
       <c r="C102">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -13881,7 +13881,7 @@
         <v>8</v>
       </c>
       <c r="C103">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -13892,7 +13892,7 @@
         <v>7</v>
       </c>
       <c r="C104">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -13903,7 +13903,7 @@
         <v>7</v>
       </c>
       <c r="C105">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -13914,7 +13914,7 @@
         <v>7</v>
       </c>
       <c r="C106">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -13925,7 +13925,7 @@
         <v>7</v>
       </c>
       <c r="C107">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -13936,7 +13936,7 @@
         <v>7</v>
       </c>
       <c r="C108">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -13947,7 +13947,7 @@
         <v>7</v>
       </c>
       <c r="C109">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -13958,7 +13958,7 @@
         <v>7</v>
       </c>
       <c r="C110">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -13969,7 +13969,7 @@
         <v>7</v>
       </c>
       <c r="C111">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -13980,7 +13980,7 @@
         <v>7</v>
       </c>
       <c r="C112">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -13991,7 +13991,7 @@
         <v>7</v>
       </c>
       <c r="C113">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -14002,7 +14002,7 @@
         <v>7</v>
       </c>
       <c r="C114">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -14266,7 +14266,7 @@
         <v>5</v>
       </c>
       <c r="C138">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -14277,7 +14277,7 @@
         <v>5</v>
       </c>
       <c r="C139">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -14288,7 +14288,7 @@
         <v>5</v>
       </c>
       <c r="C140">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -14299,7 +14299,7 @@
         <v>5</v>
       </c>
       <c r="C141">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -14310,7 +14310,7 @@
         <v>5</v>
       </c>
       <c r="C142">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -14321,7 +14321,7 @@
         <v>5</v>
       </c>
       <c r="C143">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -14332,7 +14332,7 @@
         <v>5</v>
       </c>
       <c r="C144">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -14343,7 +14343,7 @@
         <v>5</v>
       </c>
       <c r="C145">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -14354,7 +14354,7 @@
         <v>5</v>
       </c>
       <c r="C146">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -14365,7 +14365,7 @@
         <v>5</v>
       </c>
       <c r="C147">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -14376,7 +14376,7 @@
         <v>5</v>
       </c>
       <c r="C148">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -14387,7 +14387,7 @@
         <v>5</v>
       </c>
       <c r="C149">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -14398,7 +14398,7 @@
         <v>5</v>
       </c>
       <c r="C150">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -14409,7 +14409,7 @@
         <v>5</v>
       </c>
       <c r="C151">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -14420,7 +14420,7 @@
         <v>5</v>
       </c>
       <c r="C152">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -14431,7 +14431,7 @@
         <v>4</v>
       </c>
       <c r="C153">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -14442,7 +14442,7 @@
         <v>4</v>
       </c>
       <c r="C154">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -14453,7 +14453,7 @@
         <v>4</v>
       </c>
       <c r="C155">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -14464,7 +14464,7 @@
         <v>4</v>
       </c>
       <c r="C156">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -14475,7 +14475,7 @@
         <v>4</v>
       </c>
       <c r="C157">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -14486,7 +14486,7 @@
         <v>4</v>
       </c>
       <c r="C158">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -14497,7 +14497,7 @@
         <v>4</v>
       </c>
       <c r="C159">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -14508,7 +14508,7 @@
         <v>4</v>
       </c>
       <c r="C160">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -14519,7 +14519,7 @@
         <v>4</v>
       </c>
       <c r="C161">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -14530,7 +14530,7 @@
         <v>4</v>
       </c>
       <c r="C162">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -14541,7 +14541,7 @@
         <v>4</v>
       </c>
       <c r="C163">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -14552,7 +14552,7 @@
         <v>4</v>
       </c>
       <c r="C164">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -14563,7 +14563,7 @@
         <v>4</v>
       </c>
       <c r="C165">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -14574,7 +14574,7 @@
         <v>4</v>
       </c>
       <c r="C166">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -14585,7 +14585,7 @@
         <v>4</v>
       </c>
       <c r="C167">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -14596,7 +14596,7 @@
         <v>4</v>
       </c>
       <c r="C168">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -14607,7 +14607,7 @@
         <v>4</v>
       </c>
       <c r="C169">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -14618,7 +14618,7 @@
         <v>4</v>
       </c>
       <c r="C170">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -14629,7 +14629,7 @@
         <v>4</v>
       </c>
       <c r="C171">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -14640,7 +14640,7 @@
         <v>4</v>
       </c>
       <c r="C172">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -14651,7 +14651,7 @@
         <v>4</v>
       </c>
       <c r="C173">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -14662,7 +14662,7 @@
         <v>4</v>
       </c>
       <c r="C174">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -14673,7 +14673,7 @@
         <v>4</v>
       </c>
       <c r="C175">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -14684,7 +14684,7 @@
         <v>4</v>
       </c>
       <c r="C176">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -14695,7 +14695,7 @@
         <v>4</v>
       </c>
       <c r="C177">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -14706,7 +14706,7 @@
         <v>4</v>
       </c>
       <c r="C178">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -14717,7 +14717,7 @@
         <v>4</v>
       </c>
       <c r="C179">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -14728,7 +14728,7 @@
         <v>4</v>
       </c>
       <c r="C180">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -14739,7 +14739,7 @@
         <v>4</v>
       </c>
       <c r="C181">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -14750,7 +14750,7 @@
         <v>4</v>
       </c>
       <c r="C182">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -14761,7 +14761,7 @@
         <v>4</v>
       </c>
       <c r="C183">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -14772,7 +14772,7 @@
         <v>4</v>
       </c>
       <c r="C184">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -14783,7 +14783,7 @@
         <v>3</v>
       </c>
       <c r="C185">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -14794,7 +14794,7 @@
         <v>3</v>
       </c>
       <c r="C186">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -14805,7 +14805,7 @@
         <v>3</v>
       </c>
       <c r="C187">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -14816,7 +14816,7 @@
         <v>3</v>
       </c>
       <c r="C188">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -14827,7 +14827,7 @@
         <v>3</v>
       </c>
       <c r="C189">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -14838,7 +14838,7 @@
         <v>3</v>
       </c>
       <c r="C190">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -14849,7 +14849,7 @@
         <v>3</v>
       </c>
       <c r="C191">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -14860,7 +14860,7 @@
         <v>3</v>
       </c>
       <c r="C192">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -14871,7 +14871,7 @@
         <v>3</v>
       </c>
       <c r="C193">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -14882,7 +14882,7 @@
         <v>3</v>
       </c>
       <c r="C194">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -14893,7 +14893,7 @@
         <v>3</v>
       </c>
       <c r="C195">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -14904,7 +14904,7 @@
         <v>3</v>
       </c>
       <c r="C196">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -14915,7 +14915,7 @@
         <v>3</v>
       </c>
       <c r="C197">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -14926,7 +14926,7 @@
         <v>3</v>
       </c>
       <c r="C198">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -14937,7 +14937,7 @@
         <v>3</v>
       </c>
       <c r="C199">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -14948,7 +14948,7 @@
         <v>3</v>
       </c>
       <c r="C200">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -14959,7 +14959,7 @@
         <v>3</v>
       </c>
       <c r="C201">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -14970,7 +14970,7 @@
         <v>3</v>
       </c>
       <c r="C202">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -14981,7 +14981,7 @@
         <v>3</v>
       </c>
       <c r="C203">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -14992,7 +14992,7 @@
         <v>3</v>
       </c>
       <c r="C204">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -15003,7 +15003,7 @@
         <v>3</v>
       </c>
       <c r="C205">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -15014,7 +15014,7 @@
         <v>3</v>
       </c>
       <c r="C206">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -15025,7 +15025,7 @@
         <v>3</v>
       </c>
       <c r="C207">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -15036,7 +15036,7 @@
         <v>3</v>
       </c>
       <c r="C208">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -15047,7 +15047,7 @@
         <v>3</v>
       </c>
       <c r="C209">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -15058,7 +15058,7 @@
         <v>3</v>
       </c>
       <c r="C210">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -15069,7 +15069,7 @@
         <v>3</v>
       </c>
       <c r="C211">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -15080,7 +15080,7 @@
         <v>3</v>
       </c>
       <c r="C212">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -15091,7 +15091,7 @@
         <v>3</v>
       </c>
       <c r="C213">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -15102,7 +15102,7 @@
         <v>3</v>
       </c>
       <c r="C214">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -15113,7 +15113,7 @@
         <v>3</v>
       </c>
       <c r="C215">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -15124,7 +15124,7 @@
         <v>3</v>
       </c>
       <c r="C216">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -15135,7 +15135,7 @@
         <v>3</v>
       </c>
       <c r="C217">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -15146,7 +15146,7 @@
         <v>3</v>
       </c>
       <c r="C218">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -15157,7 +15157,7 @@
         <v>3</v>
       </c>
       <c r="C219">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -15168,7 +15168,7 @@
         <v>3</v>
       </c>
       <c r="C220">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -15179,7 +15179,7 @@
         <v>3</v>
       </c>
       <c r="C221">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -15190,7 +15190,7 @@
         <v>3</v>
       </c>
       <c r="C222">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -15201,7 +15201,7 @@
         <v>3</v>
       </c>
       <c r="C223">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -15212,7 +15212,7 @@
         <v>3</v>
       </c>
       <c r="C224">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -15223,7 +15223,7 @@
         <v>3</v>
       </c>
       <c r="C225">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -15234,7 +15234,7 @@
         <v>3</v>
       </c>
       <c r="C226">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -15245,7 +15245,7 @@
         <v>3</v>
       </c>
       <c r="C227">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -15256,7 +15256,7 @@
         <v>3</v>
       </c>
       <c r="C228">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -15267,7 +15267,7 @@
         <v>3</v>
       </c>
       <c r="C229">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -15278,7 +15278,7 @@
         <v>3</v>
       </c>
       <c r="C230">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -15289,7 +15289,7 @@
         <v>2</v>
       </c>
       <c r="C231">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -15300,7 +15300,7 @@
         <v>2</v>
       </c>
       <c r="C232">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -15311,7 +15311,7 @@
         <v>2</v>
       </c>
       <c r="C233">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -15322,7 +15322,7 @@
         <v>2</v>
       </c>
       <c r="C234">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -15333,7 +15333,7 @@
         <v>2</v>
       </c>
       <c r="C235">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -15344,7 +15344,7 @@
         <v>2</v>
       </c>
       <c r="C236">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -15355,7 +15355,7 @@
         <v>2</v>
       </c>
       <c r="C237">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -15366,7 +15366,7 @@
         <v>2</v>
       </c>
       <c r="C238">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -15377,7 +15377,7 @@
         <v>2</v>
       </c>
       <c r="C239">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -15388,7 +15388,7 @@
         <v>2</v>
       </c>
       <c r="C240">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -15399,7 +15399,7 @@
         <v>2</v>
       </c>
       <c r="C241">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -15410,7 +15410,7 @@
         <v>2</v>
       </c>
       <c r="C242">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -15421,7 +15421,7 @@
         <v>2</v>
       </c>
       <c r="C243">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -15432,7 +15432,7 @@
         <v>2</v>
       </c>
       <c r="C244">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -15443,7 +15443,7 @@
         <v>2</v>
       </c>
       <c r="C245">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -15454,7 +15454,7 @@
         <v>2</v>
       </c>
       <c r="C246">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -15465,7 +15465,7 @@
         <v>2</v>
       </c>
       <c r="C247">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -15476,7 +15476,7 @@
         <v>2</v>
       </c>
       <c r="C248">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -15487,7 +15487,7 @@
         <v>2</v>
       </c>
       <c r="C249">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -15498,7 +15498,7 @@
         <v>2</v>
       </c>
       <c r="C250">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -15509,7 +15509,7 @@
         <v>2</v>
       </c>
       <c r="C251">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -15520,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="C252">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -15531,7 +15531,7 @@
         <v>2</v>
       </c>
       <c r="C253">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -15542,7 +15542,7 @@
         <v>2</v>
       </c>
       <c r="C254">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -15553,7 +15553,7 @@
         <v>2</v>
       </c>
       <c r="C255">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -15564,7 +15564,7 @@
         <v>2</v>
       </c>
       <c r="C256">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -15575,7 +15575,7 @@
         <v>2</v>
       </c>
       <c r="C257">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -15586,7 +15586,7 @@
         <v>2</v>
       </c>
       <c r="C258">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -15597,7 +15597,7 @@
         <v>2</v>
       </c>
       <c r="C259">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -15608,7 +15608,7 @@
         <v>2</v>
       </c>
       <c r="C260">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -15619,7 +15619,7 @@
         <v>2</v>
       </c>
       <c r="C261">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -15630,7 +15630,7 @@
         <v>2</v>
       </c>
       <c r="C262">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -15641,7 +15641,7 @@
         <v>2</v>
       </c>
       <c r="C263">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -15652,7 +15652,7 @@
         <v>2</v>
       </c>
       <c r="C264">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -15663,7 +15663,7 @@
         <v>2</v>
       </c>
       <c r="C265">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -15674,7 +15674,7 @@
         <v>2</v>
       </c>
       <c r="C266">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -15685,7 +15685,7 @@
         <v>2</v>
       </c>
       <c r="C267">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -15696,7 +15696,7 @@
         <v>2</v>
       </c>
       <c r="C268">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -15707,7 +15707,7 @@
         <v>2</v>
       </c>
       <c r="C269">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -15718,7 +15718,7 @@
         <v>2</v>
       </c>
       <c r="C270">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -15729,7 +15729,7 @@
         <v>2</v>
       </c>
       <c r="C271">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -15740,7 +15740,7 @@
         <v>2</v>
       </c>
       <c r="C272">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -15751,7 +15751,7 @@
         <v>2</v>
       </c>
       <c r="C273">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -15762,7 +15762,7 @@
         <v>2</v>
       </c>
       <c r="C274">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -15773,7 +15773,7 @@
         <v>2</v>
       </c>
       <c r="C275">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -15784,7 +15784,7 @@
         <v>2</v>
       </c>
       <c r="C276">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -15795,7 +15795,7 @@
         <v>2</v>
       </c>
       <c r="C277">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -15806,7 +15806,7 @@
         <v>2</v>
       </c>
       <c r="C278">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -15817,7 +15817,7 @@
         <v>2</v>
       </c>
       <c r="C279">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -15828,7 +15828,7 @@
         <v>2</v>
       </c>
       <c r="C280">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -15839,7 +15839,7 @@
         <v>2</v>
       </c>
       <c r="C281">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -15850,7 +15850,7 @@
         <v>2</v>
       </c>
       <c r="C282">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -15861,7 +15861,7 @@
         <v>2</v>
       </c>
       <c r="C283">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -15872,7 +15872,7 @@
         <v>2</v>
       </c>
       <c r="C284">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -15883,7 +15883,7 @@
         <v>2</v>
       </c>
       <c r="C285">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -15894,7 +15894,7 @@
         <v>2</v>
       </c>
       <c r="C286">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -15905,7 +15905,7 @@
         <v>2</v>
       </c>
       <c r="C287">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -15916,7 +15916,7 @@
         <v>2</v>
       </c>
       <c r="C288">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -15927,7 +15927,7 @@
         <v>2</v>
       </c>
       <c r="C289">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -15938,7 +15938,7 @@
         <v>2</v>
       </c>
       <c r="C290">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -15949,7 +15949,7 @@
         <v>2</v>
       </c>
       <c r="C291">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -15960,7 +15960,7 @@
         <v>2</v>
       </c>
       <c r="C292">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -15971,7 +15971,7 @@
         <v>2</v>
       </c>
       <c r="C293">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -15982,7 +15982,7 @@
         <v>2</v>
       </c>
       <c r="C294">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -15993,7 +15993,7 @@
         <v>2</v>
       </c>
       <c r="C295">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -16004,7 +16004,7 @@
         <v>2</v>
       </c>
       <c r="C296">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -16015,7 +16015,7 @@
         <v>2</v>
       </c>
       <c r="C297">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -16026,7 +16026,7 @@
         <v>2</v>
       </c>
       <c r="C298">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -16037,7 +16037,7 @@
         <v>2</v>
       </c>
       <c r="C299">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -16048,7 +16048,7 @@
         <v>2</v>
       </c>
       <c r="C300">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -16059,7 +16059,7 @@
         <v>2</v>
       </c>
       <c r="C301">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -16070,7 +16070,7 @@
         <v>2</v>
       </c>
       <c r="C302">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -16081,7 +16081,7 @@
         <v>2</v>
       </c>
       <c r="C303">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -16092,7 +16092,7 @@
         <v>2</v>
       </c>
       <c r="C304">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -16103,7 +16103,7 @@
         <v>2</v>
       </c>
       <c r="C305">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -16114,7 +16114,7 @@
         <v>2</v>
       </c>
       <c r="C306">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -16125,7 +16125,7 @@
         <v>2</v>
       </c>
       <c r="C307">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -16136,7 +16136,7 @@
         <v>2</v>
       </c>
       <c r="C308">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -16147,7 +16147,7 @@
         <v>2</v>
       </c>
       <c r="C309">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -16158,7 +16158,7 @@
         <v>2</v>
       </c>
       <c r="C310">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -16169,7 +16169,7 @@
         <v>2</v>
       </c>
       <c r="C311">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -16180,7 +16180,7 @@
         <v>2</v>
       </c>
       <c r="C312">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -16191,7 +16191,7 @@
         <v>2</v>
       </c>
       <c r="C313">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -16202,7 +16202,7 @@
         <v>2</v>
       </c>
       <c r="C314">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -16213,7 +16213,7 @@
         <v>2</v>
       </c>
       <c r="C315">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -16224,7 +16224,7 @@
         <v>2</v>
       </c>
       <c r="C316">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -16235,7 +16235,7 @@
         <v>2</v>
       </c>
       <c r="C317">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -16246,7 +16246,7 @@
         <v>2</v>
       </c>
       <c r="C318">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -16257,7 +16257,7 @@
         <v>2</v>
       </c>
       <c r="C319">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -16268,7 +16268,7 @@
         <v>2</v>
       </c>
       <c r="C320">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -16279,7 +16279,7 @@
         <v>2</v>
       </c>
       <c r="C321">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -16290,7 +16290,7 @@
         <v>2</v>
       </c>
       <c r="C322">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -16301,7 +16301,7 @@
         <v>2</v>
       </c>
       <c r="C323">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -16312,7 +16312,7 @@
         <v>2</v>
       </c>
       <c r="C324">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -16323,7 +16323,7 @@
         <v>2</v>
       </c>
       <c r="C325">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -16334,7 +16334,7 @@
         <v>2</v>
       </c>
       <c r="C326">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -16345,7 +16345,7 @@
         <v>2</v>
       </c>
       <c r="C327">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -16356,7 +16356,7 @@
         <v>2</v>
       </c>
       <c r="C328">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -16367,7 +16367,7 @@
         <v>2</v>
       </c>
       <c r="C329">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -16378,7 +16378,7 @@
         <v>2</v>
       </c>
       <c r="C330">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="C331">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -16400,7 +16400,7 @@
         <v>1</v>
       </c>
       <c r="C332">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -16411,7 +16411,7 @@
         <v>1</v>
       </c>
       <c r="C333">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -16422,7 +16422,7 @@
         <v>1</v>
       </c>
       <c r="C334">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -16433,7 +16433,7 @@
         <v>1</v>
       </c>
       <c r="C335">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -16444,7 +16444,7 @@
         <v>1</v>
       </c>
       <c r="C336">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -16455,7 +16455,7 @@
         <v>1</v>
       </c>
       <c r="C337">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -16466,7 +16466,7 @@
         <v>1</v>
       </c>
       <c r="C338">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -16477,7 +16477,7 @@
         <v>1</v>
       </c>
       <c r="C339">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -16488,7 +16488,7 @@
         <v>1</v>
       </c>
       <c r="C340">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -16499,7 +16499,7 @@
         <v>1</v>
       </c>
       <c r="C341">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -16510,7 +16510,7 @@
         <v>1</v>
       </c>
       <c r="C342">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -16521,7 +16521,7 @@
         <v>1</v>
       </c>
       <c r="C343">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -16532,7 +16532,7 @@
         <v>1</v>
       </c>
       <c r="C344">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -16543,7 +16543,7 @@
         <v>1</v>
       </c>
       <c r="C345">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -16554,7 +16554,7 @@
         <v>1</v>
       </c>
       <c r="C346">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -16565,7 +16565,7 @@
         <v>1</v>
       </c>
       <c r="C347">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -16576,7 +16576,7 @@
         <v>1</v>
       </c>
       <c r="C348">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -16587,7 +16587,7 @@
         <v>1</v>
       </c>
       <c r="C349">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -16598,7 +16598,7 @@
         <v>1</v>
       </c>
       <c r="C350">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -16609,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="C351">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -16620,7 +16620,7 @@
         <v>1</v>
       </c>
       <c r="C352">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -16631,7 +16631,7 @@
         <v>1</v>
       </c>
       <c r="C353">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -16642,7 +16642,7 @@
         <v>1</v>
       </c>
       <c r="C354">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -16653,7 +16653,7 @@
         <v>1</v>
       </c>
       <c r="C355">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -16664,7 +16664,7 @@
         <v>1</v>
       </c>
       <c r="C356">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -16675,7 +16675,7 @@
         <v>1</v>
       </c>
       <c r="C357">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -16686,7 +16686,7 @@
         <v>1</v>
       </c>
       <c r="C358">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -16697,7 +16697,7 @@
         <v>1</v>
       </c>
       <c r="C359">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -16708,7 +16708,7 @@
         <v>1</v>
       </c>
       <c r="C360">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -16719,7 +16719,7 @@
         <v>1</v>
       </c>
       <c r="C361">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -16730,7 +16730,7 @@
         <v>1</v>
       </c>
       <c r="C362">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -16741,7 +16741,7 @@
         <v>1</v>
       </c>
       <c r="C363">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -16752,7 +16752,7 @@
         <v>1</v>
       </c>
       <c r="C364">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -16763,7 +16763,7 @@
         <v>1</v>
       </c>
       <c r="C365">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -16774,7 +16774,7 @@
         <v>1</v>
       </c>
       <c r="C366">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -16785,7 +16785,7 @@
         <v>1</v>
       </c>
       <c r="C367">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -16796,7 +16796,7 @@
         <v>1</v>
       </c>
       <c r="C368">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -16807,7 +16807,7 @@
         <v>1</v>
       </c>
       <c r="C369">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -16818,7 +16818,7 @@
         <v>1</v>
       </c>
       <c r="C370">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -16829,7 +16829,7 @@
         <v>1</v>
       </c>
       <c r="C371">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -16840,7 +16840,7 @@
         <v>1</v>
       </c>
       <c r="C372">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -16851,7 +16851,7 @@
         <v>1</v>
       </c>
       <c r="C373">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -16862,7 +16862,7 @@
         <v>1</v>
       </c>
       <c r="C374">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -16873,7 +16873,7 @@
         <v>1</v>
       </c>
       <c r="C375">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -16884,7 +16884,7 @@
         <v>1</v>
       </c>
       <c r="C376">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -16895,7 +16895,7 @@
         <v>1</v>
       </c>
       <c r="C377">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -16906,7 +16906,7 @@
         <v>1</v>
       </c>
       <c r="C378">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -16917,7 +16917,7 @@
         <v>1</v>
       </c>
       <c r="C379">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -16928,7 +16928,7 @@
         <v>1</v>
       </c>
       <c r="C380">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -16939,7 +16939,7 @@
         <v>1</v>
       </c>
       <c r="C381">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -16950,7 +16950,7 @@
         <v>1</v>
       </c>
       <c r="C382">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -16961,7 +16961,7 @@
         <v>1</v>
       </c>
       <c r="C383">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -16972,7 +16972,7 @@
         <v>1</v>
       </c>
       <c r="C384">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -16983,7 +16983,7 @@
         <v>1</v>
       </c>
       <c r="C385">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -16994,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="C386">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -17005,7 +17005,7 @@
         <v>1</v>
       </c>
       <c r="C387">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -17016,7 +17016,7 @@
         <v>1</v>
       </c>
       <c r="C388">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -17027,7 +17027,7 @@
         <v>1</v>
       </c>
       <c r="C389">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -17038,7 +17038,7 @@
         <v>1</v>
       </c>
       <c r="C390">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -17049,7 +17049,7 @@
         <v>1</v>
       </c>
       <c r="C391">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
@@ -17060,7 +17060,7 @@
         <v>1</v>
       </c>
       <c r="C392">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -17071,7 +17071,7 @@
         <v>1</v>
       </c>
       <c r="C393">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -17082,7 +17082,7 @@
         <v>1</v>
       </c>
       <c r="C394">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -17093,7 +17093,7 @@
         <v>1</v>
       </c>
       <c r="C395">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -17104,7 +17104,7 @@
         <v>1</v>
       </c>
       <c r="C396">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -17115,7 +17115,7 @@
         <v>1</v>
       </c>
       <c r="C397">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -17126,7 +17126,7 @@
         <v>1</v>
       </c>
       <c r="C398">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -17137,7 +17137,7 @@
         <v>1</v>
       </c>
       <c r="C399">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -17148,7 +17148,7 @@
         <v>1</v>
       </c>
       <c r="C400">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -17159,7 +17159,7 @@
         <v>1</v>
       </c>
       <c r="C401">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -17170,7 +17170,7 @@
         <v>1</v>
       </c>
       <c r="C402">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -17181,7 +17181,7 @@
         <v>1</v>
       </c>
       <c r="C403">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -17192,7 +17192,7 @@
         <v>1</v>
       </c>
       <c r="C404">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -17203,7 +17203,7 @@
         <v>1</v>
       </c>
       <c r="C405">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -17214,7 +17214,7 @@
         <v>1</v>
       </c>
       <c r="C406">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -17225,7 +17225,7 @@
         <v>1</v>
       </c>
       <c r="C407">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -17236,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="C408">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -17247,7 +17247,7 @@
         <v>1</v>
       </c>
       <c r="C409">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -17258,7 +17258,7 @@
         <v>1</v>
       </c>
       <c r="C410">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -17269,7 +17269,7 @@
         <v>1</v>
       </c>
       <c r="C411">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -17280,7 +17280,7 @@
         <v>1</v>
       </c>
       <c r="C412">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -17291,7 +17291,7 @@
         <v>1</v>
       </c>
       <c r="C413">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -17302,7 +17302,7 @@
         <v>1</v>
       </c>
       <c r="C414">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -17313,7 +17313,7 @@
         <v>1</v>
       </c>
       <c r="C415">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -17324,7 +17324,7 @@
         <v>1</v>
       </c>
       <c r="C416">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -17335,7 +17335,7 @@
         <v>1</v>
       </c>
       <c r="C417">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -17346,7 +17346,7 @@
         <v>1</v>
       </c>
       <c r="C418">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -17357,7 +17357,7 @@
         <v>1</v>
       </c>
       <c r="C419">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -17368,7 +17368,7 @@
         <v>1</v>
       </c>
       <c r="C420">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -17379,7 +17379,7 @@
         <v>1</v>
       </c>
       <c r="C421">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -17390,7 +17390,7 @@
         <v>1</v>
       </c>
       <c r="C422">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -17401,7 +17401,7 @@
         <v>1</v>
       </c>
       <c r="C423">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -17412,7 +17412,7 @@
         <v>1</v>
       </c>
       <c r="C424">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -17423,7 +17423,7 @@
         <v>1</v>
       </c>
       <c r="C425">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -17434,7 +17434,7 @@
         <v>1</v>
       </c>
       <c r="C426">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -17445,7 +17445,7 @@
         <v>1</v>
       </c>
       <c r="C427">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -17456,7 +17456,7 @@
         <v>1</v>
       </c>
       <c r="C428">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -17467,7 +17467,7 @@
         <v>1</v>
       </c>
       <c r="C429">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -17478,7 +17478,7 @@
         <v>1</v>
       </c>
       <c r="C430">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -17489,7 +17489,7 @@
         <v>1</v>
       </c>
       <c r="C431">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -17500,7 +17500,7 @@
         <v>1</v>
       </c>
       <c r="C432">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -17511,7 +17511,7 @@
         <v>1</v>
       </c>
       <c r="C433">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -17522,7 +17522,7 @@
         <v>1</v>
       </c>
       <c r="C434">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -17533,7 +17533,7 @@
         <v>1</v>
       </c>
       <c r="C435">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -17544,7 +17544,7 @@
         <v>1</v>
       </c>
       <c r="C436">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -17555,7 +17555,7 @@
         <v>1</v>
       </c>
       <c r="C437">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -17566,7 +17566,7 @@
         <v>1</v>
       </c>
       <c r="C438">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -17577,7 +17577,7 @@
         <v>1</v>
       </c>
       <c r="C439">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -17588,7 +17588,7 @@
         <v>1</v>
       </c>
       <c r="C440">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -17599,7 +17599,7 @@
         <v>1</v>
       </c>
       <c r="C441">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -17610,7 +17610,7 @@
         <v>1</v>
       </c>
       <c r="C442">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -17621,7 +17621,7 @@
         <v>1</v>
       </c>
       <c r="C443">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -17632,7 +17632,7 @@
         <v>1</v>
       </c>
       <c r="C444">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -17643,7 +17643,7 @@
         <v>1</v>
       </c>
       <c r="C445">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -17654,7 +17654,7 @@
         <v>1</v>
       </c>
       <c r="C446">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -17665,7 +17665,7 @@
         <v>1</v>
       </c>
       <c r="C447">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -17676,7 +17676,7 @@
         <v>1</v>
       </c>
       <c r="C448">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -17687,7 +17687,7 @@
         <v>1</v>
       </c>
       <c r="C449">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -17698,7 +17698,7 @@
         <v>1</v>
       </c>
       <c r="C450">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -17709,7 +17709,7 @@
         <v>1</v>
       </c>
       <c r="C451">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -17720,7 +17720,7 @@
         <v>1</v>
       </c>
       <c r="C452">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -17731,7 +17731,7 @@
         <v>1</v>
       </c>
       <c r="C453">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -17742,7 +17742,7 @@
         <v>1</v>
       </c>
       <c r="C454">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -17753,7 +17753,7 @@
         <v>1</v>
       </c>
       <c r="C455">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -17764,7 +17764,7 @@
         <v>1</v>
       </c>
       <c r="C456">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -17775,7 +17775,7 @@
         <v>1</v>
       </c>
       <c r="C457">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -17786,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="C458">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -17797,7 +17797,7 @@
         <v>1</v>
       </c>
       <c r="C459">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -17808,7 +17808,7 @@
         <v>1</v>
       </c>
       <c r="C460">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -17819,7 +17819,7 @@
         <v>1</v>
       </c>
       <c r="C461">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -17830,7 +17830,7 @@
         <v>1</v>
       </c>
       <c r="C462">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -17841,7 +17841,7 @@
         <v>1</v>
       </c>
       <c r="C463">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -17852,7 +17852,7 @@
         <v>1</v>
       </c>
       <c r="C464">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -17863,7 +17863,7 @@
         <v>1</v>
       </c>
       <c r="C465">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -17874,7 +17874,7 @@
         <v>1</v>
       </c>
       <c r="C466">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -17885,7 +17885,7 @@
         <v>1</v>
       </c>
       <c r="C467">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -17896,7 +17896,7 @@
         <v>1</v>
       </c>
       <c r="C468">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -17907,7 +17907,7 @@
         <v>1</v>
       </c>
       <c r="C469">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -17918,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="C470">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -17929,7 +17929,7 @@
         <v>1</v>
       </c>
       <c r="C471">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -17940,7 +17940,7 @@
         <v>1</v>
       </c>
       <c r="C472">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
@@ -17951,7 +17951,7 @@
         <v>1</v>
       </c>
       <c r="C473">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -17962,7 +17962,7 @@
         <v>1</v>
       </c>
       <c r="C474">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -17973,7 +17973,7 @@
         <v>1</v>
       </c>
       <c r="C475">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -17984,7 +17984,7 @@
         <v>1</v>
       </c>
       <c r="C476">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -17995,7 +17995,7 @@
         <v>1</v>
       </c>
       <c r="C477">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -18006,7 +18006,7 @@
         <v>1</v>
       </c>
       <c r="C478">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -18017,7 +18017,7 @@
         <v>1</v>
       </c>
       <c r="C479">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -18028,7 +18028,7 @@
         <v>1</v>
       </c>
       <c r="C480">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -18039,7 +18039,7 @@
         <v>1</v>
       </c>
       <c r="C481">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -18050,7 +18050,7 @@
         <v>1</v>
       </c>
       <c r="C482">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -18061,7 +18061,7 @@
         <v>1</v>
       </c>
       <c r="C483">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -18072,7 +18072,7 @@
         <v>1</v>
       </c>
       <c r="C484">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -18083,7 +18083,7 @@
         <v>1</v>
       </c>
       <c r="C485">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -18094,7 +18094,7 @@
         <v>1</v>
       </c>
       <c r="C486">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -18105,7 +18105,7 @@
         <v>1</v>
       </c>
       <c r="C487">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -18116,7 +18116,7 @@
         <v>1</v>
       </c>
       <c r="C488">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -18127,7 +18127,7 @@
         <v>1</v>
       </c>
       <c r="C489">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -18138,7 +18138,7 @@
         <v>1</v>
       </c>
       <c r="C490">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -18149,7 +18149,7 @@
         <v>1</v>
       </c>
       <c r="C491">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -18160,7 +18160,7 @@
         <v>1</v>
       </c>
       <c r="C492">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -18171,7 +18171,7 @@
         <v>1</v>
       </c>
       <c r="C493">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -18182,7 +18182,7 @@
         <v>1</v>
       </c>
       <c r="C494">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -18193,7 +18193,7 @@
         <v>1</v>
       </c>
       <c r="C495">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -18204,7 +18204,7 @@
         <v>1</v>
       </c>
       <c r="C496">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -18215,7 +18215,7 @@
         <v>1</v>
       </c>
       <c r="C497">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -18226,7 +18226,7 @@
         <v>1</v>
       </c>
       <c r="C498">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -18237,7 +18237,7 @@
         <v>1</v>
       </c>
       <c r="C499">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -18248,7 +18248,7 @@
         <v>1</v>
       </c>
       <c r="C500">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -18259,7 +18259,7 @@
         <v>1</v>
       </c>
       <c r="C501">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -18270,7 +18270,7 @@
         <v>1</v>
       </c>
       <c r="C502">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -18281,7 +18281,7 @@
         <v>1</v>
       </c>
       <c r="C503">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -18292,7 +18292,7 @@
         <v>1</v>
       </c>
       <c r="C504">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -18303,7 +18303,7 @@
         <v>1</v>
       </c>
       <c r="C505">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -18314,7 +18314,7 @@
         <v>1</v>
       </c>
       <c r="C506">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -18325,7 +18325,7 @@
         <v>1</v>
       </c>
       <c r="C507">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -18336,7 +18336,7 @@
         <v>1</v>
       </c>
       <c r="C508">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -18347,7 +18347,7 @@
         <v>1</v>
       </c>
       <c r="C509">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -18358,7 +18358,7 @@
         <v>1</v>
       </c>
       <c r="C510">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -18369,7 +18369,7 @@
         <v>1</v>
       </c>
       <c r="C511">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -18380,7 +18380,7 @@
         <v>1</v>
       </c>
       <c r="C512">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -18391,7 +18391,7 @@
         <v>1</v>
       </c>
       <c r="C513">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -18402,7 +18402,7 @@
         <v>1</v>
       </c>
       <c r="C514">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -18413,7 +18413,7 @@
         <v>1</v>
       </c>
       <c r="C515">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -18424,7 +18424,7 @@
         <v>1</v>
       </c>
       <c r="C516">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -18435,7 +18435,7 @@
         <v>1</v>
       </c>
       <c r="C517">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -18446,7 +18446,7 @@
         <v>1</v>
       </c>
       <c r="C518">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -18457,7 +18457,7 @@
         <v>1</v>
       </c>
       <c r="C519">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -18468,7 +18468,7 @@
         <v>1</v>
       </c>
       <c r="C520">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -18479,7 +18479,7 @@
         <v>1</v>
       </c>
       <c r="C521">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -18490,7 +18490,7 @@
         <v>1</v>
       </c>
       <c r="C522">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -18501,7 +18501,7 @@
         <v>1</v>
       </c>
       <c r="C523">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -18512,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="C524">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -18523,7 +18523,7 @@
         <v>1</v>
       </c>
       <c r="C525">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -18534,7 +18534,7 @@
         <v>1</v>
       </c>
       <c r="C526">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -18545,7 +18545,7 @@
         <v>1</v>
       </c>
       <c r="C527">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -18556,7 +18556,7 @@
         <v>1</v>
       </c>
       <c r="C528">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -18567,7 +18567,7 @@
         <v>1</v>
       </c>
       <c r="C529">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -18578,7 +18578,7 @@
         <v>1</v>
       </c>
       <c r="C530">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -18589,7 +18589,7 @@
         <v>1</v>
       </c>
       <c r="C531">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -18600,7 +18600,7 @@
         <v>1</v>
       </c>
       <c r="C532">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -18611,7 +18611,7 @@
         <v>1</v>
       </c>
       <c r="C533">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -18622,7 +18622,7 @@
         <v>1</v>
       </c>
       <c r="C534">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -18633,7 +18633,7 @@
         <v>1</v>
       </c>
       <c r="C535">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -18644,7 +18644,7 @@
         <v>1</v>
       </c>
       <c r="C536">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -18655,7 +18655,7 @@
         <v>1</v>
       </c>
       <c r="C537">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -18666,7 +18666,7 @@
         <v>1</v>
       </c>
       <c r="C538">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -18677,7 +18677,7 @@
         <v>1</v>
       </c>
       <c r="C539">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -18688,7 +18688,7 @@
         <v>1</v>
       </c>
       <c r="C540">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -18699,7 +18699,7 @@
         <v>1</v>
       </c>
       <c r="C541">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -18710,7 +18710,7 @@
         <v>1</v>
       </c>
       <c r="C542">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -18721,7 +18721,7 @@
         <v>1</v>
       </c>
       <c r="C543">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -18732,7 +18732,7 @@
         <v>1</v>
       </c>
       <c r="C544">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -18743,7 +18743,7 @@
         <v>1</v>
       </c>
       <c r="C545">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -18754,7 +18754,7 @@
         <v>1</v>
       </c>
       <c r="C546">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -18765,7 +18765,7 @@
         <v>1</v>
       </c>
       <c r="C547">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -18776,7 +18776,7 @@
         <v>1</v>
       </c>
       <c r="C548">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -18787,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="C549">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -18798,7 +18798,7 @@
         <v>1</v>
       </c>
       <c r="C550">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -18809,7 +18809,7 @@
         <v>1</v>
       </c>
       <c r="C551">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -18820,7 +18820,7 @@
         <v>1</v>
       </c>
       <c r="C552">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -18831,7 +18831,7 @@
         <v>1</v>
       </c>
       <c r="C553">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -18842,7 +18842,7 @@
         <v>1</v>
       </c>
       <c r="C554">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -18853,7 +18853,7 @@
         <v>1</v>
       </c>
       <c r="C555">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -18864,7 +18864,7 @@
         <v>1</v>
       </c>
       <c r="C556">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -18875,7 +18875,7 @@
         <v>1</v>
       </c>
       <c r="C557">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -18886,7 +18886,7 @@
         <v>1</v>
       </c>
       <c r="C558">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -18897,7 +18897,7 @@
         <v>1</v>
       </c>
       <c r="C559">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -18908,7 +18908,7 @@
         <v>1</v>
       </c>
       <c r="C560">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -18919,7 +18919,7 @@
         <v>1</v>
       </c>
       <c r="C561">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -18930,7 +18930,7 @@
         <v>1</v>
       </c>
       <c r="C562">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -18941,7 +18941,7 @@
         <v>1</v>
       </c>
       <c r="C563">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -18952,7 +18952,7 @@
         <v>1</v>
       </c>
       <c r="C564">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -18963,7 +18963,7 @@
         <v>1</v>
       </c>
       <c r="C565">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -18974,7 +18974,7 @@
         <v>1</v>
       </c>
       <c r="C566">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -18985,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="C567">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -18996,7 +18996,7 @@
         <v>1</v>
       </c>
       <c r="C568">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -19007,7 +19007,7 @@
         <v>1</v>
       </c>
       <c r="C569">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -19018,7 +19018,7 @@
         <v>1</v>
       </c>
       <c r="C570">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -19029,7 +19029,7 @@
         <v>1</v>
       </c>
       <c r="C571">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -19040,7 +19040,7 @@
         <v>1</v>
       </c>
       <c r="C572">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -19051,7 +19051,7 @@
         <v>1</v>
       </c>
       <c r="C573">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -19062,7 +19062,7 @@
         <v>1</v>
       </c>
       <c r="C574">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -19073,7 +19073,7 @@
         <v>1</v>
       </c>
       <c r="C575">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -19084,7 +19084,7 @@
         <v>1</v>
       </c>
       <c r="C576">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -19095,7 +19095,7 @@
         <v>1</v>
       </c>
       <c r="C577">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -19106,7 +19106,7 @@
         <v>1</v>
       </c>
       <c r="C578">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -19117,7 +19117,7 @@
         <v>1</v>
       </c>
       <c r="C579">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -19128,7 +19128,7 @@
         <v>1</v>
       </c>
       <c r="C580">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -19139,7 +19139,7 @@
         <v>1</v>
       </c>
       <c r="C581">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -19150,7 +19150,7 @@
         <v>1</v>
       </c>
       <c r="C582">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -19161,7 +19161,7 @@
         <v>1</v>
       </c>
       <c r="C583">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -19172,7 +19172,7 @@
         <v>1</v>
       </c>
       <c r="C584">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -19183,7 +19183,7 @@
         <v>1</v>
       </c>
       <c r="C585">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -19194,7 +19194,7 @@
         <v>1</v>
       </c>
       <c r="C586">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -19205,7 +19205,7 @@
         <v>1</v>
       </c>
       <c r="C587">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -19216,7 +19216,7 @@
         <v>1</v>
       </c>
       <c r="C588">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -19227,7 +19227,7 @@
         <v>1</v>
       </c>
       <c r="C589">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -19238,7 +19238,7 @@
         <v>1</v>
       </c>
       <c r="C590">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -19249,7 +19249,7 @@
         <v>1</v>
       </c>
       <c r="C591">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -19260,7 +19260,7 @@
         <v>1</v>
       </c>
       <c r="C592">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -19271,7 +19271,7 @@
         <v>1</v>
       </c>
       <c r="C593">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -19282,7 +19282,7 @@
         <v>1</v>
       </c>
       <c r="C594">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -19293,7 +19293,7 @@
         <v>1</v>
       </c>
       <c r="C595">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -19304,7 +19304,7 @@
         <v>1</v>
       </c>
       <c r="C596">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -19315,7 +19315,7 @@
         <v>1</v>
       </c>
       <c r="C597">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -19326,7 +19326,7 @@
         <v>1</v>
       </c>
       <c r="C598">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -19337,7 +19337,7 @@
         <v>1</v>
       </c>
       <c r="C599">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -19348,7 +19348,7 @@
         <v>1</v>
       </c>
       <c r="C600">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -19359,7 +19359,7 @@
         <v>1</v>
       </c>
       <c r="C601">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -19370,7 +19370,7 @@
         <v>1</v>
       </c>
       <c r="C602">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -19381,7 +19381,7 @@
         <v>1</v>
       </c>
       <c r="C603">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -19392,7 +19392,7 @@
         <v>1</v>
       </c>
       <c r="C604">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -19403,7 +19403,7 @@
         <v>1</v>
       </c>
       <c r="C605">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -19414,7 +19414,7 @@
         <v>1</v>
       </c>
       <c r="C606">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -19425,7 +19425,7 @@
         <v>1</v>
       </c>
       <c r="C607">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -19436,7 +19436,7 @@
         <v>1</v>
       </c>
       <c r="C608">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -19447,7 +19447,7 @@
         <v>1</v>
       </c>
       <c r="C609">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -19458,7 +19458,7 @@
         <v>1</v>
       </c>
       <c r="C610">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -19469,7 +19469,7 @@
         <v>1</v>
       </c>
       <c r="C611">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -19480,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="C612">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -19491,7 +19491,7 @@
         <v>1</v>
       </c>
       <c r="C613">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -19502,7 +19502,7 @@
         <v>1</v>
       </c>
       <c r="C614">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -19513,7 +19513,7 @@
         <v>1</v>
       </c>
       <c r="C615">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -19524,7 +19524,7 @@
         <v>1</v>
       </c>
       <c r="C616">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -19535,7 +19535,7 @@
         <v>1</v>
       </c>
       <c r="C617">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -19546,7 +19546,7 @@
         <v>1</v>
       </c>
       <c r="C618">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -19557,7 +19557,7 @@
         <v>1</v>
       </c>
       <c r="C619">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -19568,7 +19568,7 @@
         <v>1</v>
       </c>
       <c r="C620">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -19579,7 +19579,7 @@
         <v>1</v>
       </c>
       <c r="C621">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -19590,7 +19590,7 @@
         <v>1</v>
       </c>
       <c r="C622">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -19601,7 +19601,7 @@
         <v>1</v>
       </c>
       <c r="C623">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -19612,7 +19612,7 @@
         <v>1</v>
       </c>
       <c r="C624">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -19623,7 +19623,7 @@
         <v>1</v>
       </c>
       <c r="C625">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -19634,7 +19634,7 @@
         <v>1</v>
       </c>
       <c r="C626">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -19645,7 +19645,7 @@
         <v>1</v>
       </c>
       <c r="C627">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -19656,7 +19656,7 @@
         <v>1</v>
       </c>
       <c r="C628">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -19667,7 +19667,7 @@
         <v>1</v>
       </c>
       <c r="C629">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -19678,7 +19678,7 @@
         <v>1</v>
       </c>
       <c r="C630">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -19689,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="C631">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -19700,7 +19700,7 @@
         <v>1</v>
       </c>
       <c r="C632">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -19711,7 +19711,7 @@
         <v>1</v>
       </c>
       <c r="C633">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -19722,7 +19722,7 @@
         <v>1</v>
       </c>
       <c r="C634">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -19733,7 +19733,7 @@
         <v>1</v>
       </c>
       <c r="C635">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -19744,7 +19744,7 @@
         <v>1</v>
       </c>
       <c r="C636">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -19755,7 +19755,7 @@
         <v>1</v>
       </c>
       <c r="C637">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
